--- a/summary/no/exposures_meta_analysis_prostate_cancer_combined.xlsx
+++ b/summary/no/exposures_meta_analysis_prostate_cancer_combined.xlsx
@@ -450,7 +450,7 @@
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
   </cols>
-  <sheetData>
+  <sheetData xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
@@ -509,10 +509,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>vitamin_b1</t>
-        </is>
+      <c r="A2" t="str">
+        <v>vitamin_b1</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
@@ -526,12 +524,12 @@
       <c r="E2" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="F2" s="3" t="inlineStr"/>
-      <c r="G2" s="3" t="inlineStr"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
       <c r="H2" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="5" t="inlineStr"/>
+      <c r="I2" s="5"/>
       <c r="J2" s="2" t="n">
         <v>204</v>
       </c>
@@ -540,10 +538,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>natto</t>
-        </is>
+      <c r="A3" t="str">
+        <v>natto</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>1</v>
@@ -557,12 +553,12 @@
       <c r="E3" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
       <c r="H3" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="5" t="inlineStr"/>
+      <c r="I3" s="5"/>
       <c r="J3" s="2" t="n">
         <v>280</v>
       </c>
@@ -571,10 +567,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>papaya</t>
-        </is>
+      <c r="A4" t="str">
+        <v>papaya</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>1</v>
@@ -588,12 +582,12 @@
       <c r="E4" s="3" t="n">
         <v>0.97</v>
       </c>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="3" t="inlineStr"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
       <c r="H4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="5" t="inlineStr"/>
+      <c r="I4" s="5"/>
       <c r="J4" s="2" t="n">
         <v>105</v>
       </c>
@@ -602,29 +596,27 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>inositol</t>
-        </is>
+      <c r="A5" t="str">
+        <v>inositol</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.56</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>0.39</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
+        <v>0.81</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
       <c r="H5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="5" t="inlineStr"/>
+      <c r="I5" s="5"/>
       <c r="J5" s="2" t="n">
         <v>400</v>
       </c>
@@ -633,10 +625,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>early_time_restricted_eating</t>
-        </is>
+      <c r="A6" t="str">
+        <v>early_time_restricted_eating</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>1</v>
@@ -650,12 +640,12 @@
       <c r="E6" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="3" t="inlineStr"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
       <c r="H6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="5" t="inlineStr"/>
+      <c r="I6" s="5"/>
       <c r="J6" s="2" t="n">
         <v>1455</v>
       </c>
@@ -664,10 +654,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>soy</t>
-        </is>
+      <c r="A7" t="str">
+        <v>soy</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>8</v>
@@ -688,7 +676,7 @@
         <v>2.09</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>78.90000000000001</v>
+        <v>78.9</v>
       </c>
       <c r="I7" s="5" t="n">
         <v>0.1010785350953814</v>
@@ -701,10 +689,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>green_tea</t>
-        </is>
+      <c r="A8" t="str">
+        <v>green_tea</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>7</v>
@@ -738,10 +724,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>insoluble_dietary_fiber_intake</t>
-        </is>
+      <c r="A9" t="str">
+        <v>insoluble_dietary_fiber_intake</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>3</v>
@@ -762,7 +746,7 @@
         <v>206.11</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>74.90000000000001</v>
+        <v>74.9</v>
       </c>
       <c r="I9" s="5" t="n">
         <v>0.1151715356999109</v>
@@ -770,13 +754,11 @@
       <c r="J9" s="2" t="n">
         <v>101084</v>
       </c>
-      <c r="K9" s="2" t="inlineStr"/>
+      <c r="K9" s="2"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>low_fat_diet</t>
-        </is>
+      <c r="A10" t="str">
+        <v>low_fat_diet</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>1</v>
@@ -790,12 +772,12 @@
       <c r="E10" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="F10" s="3" t="inlineStr"/>
-      <c r="G10" s="3" t="inlineStr"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
       <c r="H10" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I10" s="5" t="inlineStr"/>
+      <c r="I10" s="5"/>
       <c r="J10" s="2" t="n">
         <v>1170</v>
       </c>
@@ -804,10 +786,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>vitamin_k2</t>
-        </is>
+      <c r="A11" t="str">
+        <v>vitamin_k2</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>1</v>
@@ -821,12 +801,12 @@
       <c r="E11" s="3" t="n">
         <v>1.06</v>
       </c>
-      <c r="F11" s="3" t="inlineStr"/>
-      <c r="G11" s="3" t="inlineStr"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
       <c r="H11" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="5" t="inlineStr"/>
+      <c r="I11" s="5"/>
       <c r="J11" s="2" t="n">
         <v>11319</v>
       </c>
@@ -835,10 +815,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>zeaxanthin</t>
-        </is>
+      <c r="A12" t="str">
+        <v>zeaxanthin</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>4</v>
@@ -872,10 +850,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>quercetin</t>
-        </is>
+      <c r="A13" t="str">
+        <v>quercetin</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>1</v>
@@ -889,12 +865,12 @@
       <c r="E13" s="3" t="n">
         <v>0.93</v>
       </c>
-      <c r="F13" s="3" t="inlineStr"/>
-      <c r="G13" s="3" t="inlineStr"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
       <c r="H13" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="5" t="inlineStr"/>
+      <c r="I13" s="5"/>
       <c r="J13" s="2" t="n">
         <v>971</v>
       </c>
@@ -903,10 +879,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>vegan_diet</t>
-        </is>
+      <c r="A14" t="str">
+        <v>vegan_diet</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>1</v>
@@ -920,12 +894,12 @@
       <c r="E14" s="3" t="n">
         <v>0.86</v>
       </c>
-      <c r="F14" s="3" t="inlineStr"/>
-      <c r="G14" s="3" t="inlineStr"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
       <c r="H14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I14" s="5" t="inlineStr"/>
+      <c r="I14" s="5"/>
       <c r="J14" s="2" t="n">
         <v>26346</v>
       </c>
@@ -934,10 +908,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>pyruvate</t>
-        </is>
+      <c r="A15" t="str">
+        <v>pyruvate</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>1</v>
@@ -951,12 +923,12 @@
       <c r="E15" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="F15" s="3" t="inlineStr"/>
-      <c r="G15" s="3" t="inlineStr"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
       <c r="H15" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="5" t="inlineStr"/>
+      <c r="I15" s="5"/>
       <c r="J15" s="2" t="n">
         <v>666</v>
       </c>
@@ -965,16 +937,14 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>garlic</t>
-        </is>
+      <c r="A16" t="str">
+        <v>garlic</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>3</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.69</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>0.42</v>
@@ -1002,10 +972,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>vegetarian_diet</t>
-        </is>
+      <c r="A17" t="str">
+        <v>vegetarian_diet</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>1</v>
@@ -1014,17 +982,17 @@
         <v>0.7</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.56</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="F17" s="3" t="inlineStr"/>
-      <c r="G17" s="3" t="inlineStr"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
       <c r="H17" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I17" s="5" t="inlineStr"/>
+      <c r="I17" s="5"/>
       <c r="J17" s="2" t="n">
         <v>217937</v>
       </c>
@@ -1033,10 +1001,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>linoleic_acid</t>
-        </is>
+      <c r="A18" t="str">
+        <v>linoleic_acid</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>7</v>
@@ -1070,10 +1036,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>genistein</t>
-        </is>
+      <c r="A19" t="str">
+        <v>genistein</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>9</v>
@@ -1107,10 +1071,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>vitamin_k</t>
-        </is>
+      <c r="A20" t="str">
+        <v>vitamin_k</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>2</v>
@@ -1124,12 +1086,12 @@
       <c r="E20" s="3" t="n">
         <v>0.92</v>
       </c>
-      <c r="F20" s="3" t="inlineStr"/>
-      <c r="G20" s="3" t="inlineStr"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
       <c r="H20" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="5" t="inlineStr"/>
+      <c r="I20" s="5"/>
       <c r="J20" s="2" t="n">
         <v>12063</v>
       </c>
@@ -1138,10 +1100,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>tomato</t>
-        </is>
+      <c r="A21" t="str">
+        <v>tomato</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>11</v>
@@ -1162,10 +1122,10 @@
         <v>1.16</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>78.09999999999999</v>
+        <v>78.1</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>2.045420729252852e-05</v>
+        <v>0.00002045420729252852</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>1057923</v>
@@ -1175,10 +1135,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>melatonin</t>
-        </is>
+      <c r="A22" t="str">
+        <v>melatonin</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>3</v>
@@ -1212,10 +1170,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>tea</t>
-        </is>
+      <c r="A23" t="str">
+        <v>tea</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>10</v>
@@ -1236,7 +1192,7 @@
         <v>1.27</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>84.90000000000001</v>
+        <v>84.9</v>
       </c>
       <c r="I23" s="5" t="n">
         <v>0.04996208468350858</v>
@@ -1249,10 +1205,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>citrulline</t>
-        </is>
+      <c r="A24" t="str">
+        <v>citrulline</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>1</v>
@@ -1266,12 +1220,12 @@
       <c r="E24" s="3" t="n">
         <v>0.88</v>
       </c>
-      <c r="F24" s="3" t="inlineStr"/>
-      <c r="G24" s="3" t="inlineStr"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
       <c r="H24" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I24" s="5" t="inlineStr"/>
+      <c r="I24" s="5"/>
       <c r="J24" s="2" t="n">
         <v>2154</v>
       </c>
@@ -1280,10 +1234,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>potassium</t>
-        </is>
+      <c r="A25" t="str">
+        <v>potassium</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>1</v>
@@ -1297,12 +1249,12 @@
       <c r="E25" s="3" t="n">
         <v>1.08</v>
       </c>
-      <c r="F25" s="3" t="inlineStr"/>
-      <c r="G25" s="3" t="inlineStr"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
       <c r="H25" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I25" s="5" t="inlineStr"/>
+      <c r="I25" s="5"/>
       <c r="J25" s="2" t="n">
         <v>656</v>
       </c>
@@ -1311,10 +1263,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>selenium</t>
-        </is>
+      <c r="A26" t="str">
+        <v>selenium</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>28</v>
@@ -1335,7 +1285,7 @@
         <v>1.48</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>84.90000000000001</v>
+        <v>84.9</v>
       </c>
       <c r="I26" s="5" t="n">
         <v>0.0008136772771022814</v>
@@ -1348,10 +1298,8 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>iodine</t>
-        </is>
+      <c r="A27" t="str">
+        <v>iodine</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>1</v>
@@ -1365,12 +1313,12 @@
       <c r="E27" s="3" t="n">
         <v>1.09</v>
       </c>
-      <c r="F27" s="3" t="inlineStr"/>
-      <c r="G27" s="3" t="inlineStr"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
       <c r="H27" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I27" s="5" t="inlineStr"/>
+      <c r="I27" s="5"/>
       <c r="J27" s="2" t="n">
         <v>656</v>
       </c>
@@ -1379,10 +1327,8 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>time_restricted_eating</t>
-        </is>
+      <c r="A28" t="str">
+        <v>time_restricted_eating</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>1</v>
@@ -1396,12 +1342,12 @@
       <c r="E28" s="3" t="n">
         <v>1.06</v>
       </c>
-      <c r="F28" s="3" t="inlineStr"/>
-      <c r="G28" s="3" t="inlineStr"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
       <c r="H28" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I28" s="5" t="inlineStr"/>
+      <c r="I28" s="5"/>
       <c r="J28" s="2" t="n">
         <v>1455</v>
       </c>
@@ -1410,10 +1356,8 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>oleic_acid</t>
-        </is>
+      <c r="A29" t="str">
+        <v>oleic_acid</v>
       </c>
       <c r="B29" s="2" t="n">
         <v>2</v>
@@ -1427,12 +1371,12 @@
       <c r="E29" s="3" t="n">
         <v>2.64</v>
       </c>
-      <c r="F29" s="3" t="inlineStr"/>
-      <c r="G29" s="3" t="inlineStr"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
       <c r="H29" s="4" t="n">
         <v>82</v>
       </c>
-      <c r="I29" s="5" t="inlineStr"/>
+      <c r="I29" s="5"/>
       <c r="J29" s="2" t="n">
         <v>58714</v>
       </c>
@@ -1441,10 +1385,8 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>mushrooms</t>
-        </is>
+      <c r="A30" t="str">
+        <v>mushrooms</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>1</v>
@@ -1458,12 +1400,12 @@
       <c r="E30" s="3" t="n">
         <v>0.98</v>
       </c>
-      <c r="F30" s="3" t="inlineStr"/>
-      <c r="G30" s="3" t="inlineStr"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
       <c r="H30" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I30" s="5" t="inlineStr"/>
+      <c r="I30" s="5"/>
       <c r="J30" s="2" t="n">
         <v>36499</v>
       </c>
@@ -1472,10 +1414,8 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>lycopene</t>
-        </is>
+      <c r="A31" t="str">
+        <v>lycopene</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>20</v>
@@ -1496,7 +1436,7 @@
         <v>1.15</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>71.40000000000001</v>
+        <v>71.4</v>
       </c>
       <c r="I31" s="5" t="n">
         <v>0.0008787392868700852</v>
@@ -1509,10 +1449,8 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>vitamin_c</t>
-        </is>
+      <c r="A32" t="str">
+        <v>vitamin_c</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>11</v>
@@ -1533,7 +1471,7 @@
         <v>1.49</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>79.09999999999999</v>
+        <v>79.1</v>
       </c>
       <c r="I32" s="5" t="n">
         <v>0.9264859141728315</v>
@@ -1546,10 +1484,8 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>fish_oil</t>
-        </is>
+      <c r="A33" t="str">
+        <v>fish_oil</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>2</v>
@@ -1563,12 +1499,12 @@
       <c r="E33" s="3" t="n">
         <v>1.17</v>
       </c>
-      <c r="F33" s="3" t="inlineStr"/>
-      <c r="G33" s="3" t="inlineStr"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
       <c r="H33" s="4" t="n">
         <v>47.9</v>
       </c>
-      <c r="I33" s="5" t="inlineStr"/>
+      <c r="I33" s="5"/>
       <c r="J33" s="2" t="n">
         <v>37289</v>
       </c>
@@ -1577,10 +1513,8 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>legumes</t>
-        </is>
+      <c r="A34" t="str">
+        <v>legumes</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>8</v>
@@ -1589,7 +1523,7 @@
         <v>0.89</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>0.97</v>
@@ -1614,10 +1548,8 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>soluble_dietary_fiber_intake</t>
-        </is>
+      <c r="A35" t="str">
+        <v>soluble_dietary_fiber_intake</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>3</v>
@@ -1651,10 +1583,8 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>vitamin_b6</t>
-        </is>
+      <c r="A36" t="str">
+        <v>vitamin_b6</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>3</v>
@@ -1688,10 +1618,8 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>plant_based_diet</t>
-        </is>
+      <c r="A37" t="str">
+        <v>plant_based_diet</v>
       </c>
       <c r="B37" s="2" t="n">
         <v>2</v>
@@ -1705,12 +1633,12 @@
       <c r="E37" s="3" t="n">
         <v>0.99</v>
       </c>
-      <c r="F37" s="3" t="inlineStr"/>
-      <c r="G37" s="3" t="inlineStr"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
       <c r="H37" s="4" t="n">
         <v>39.5</v>
       </c>
-      <c r="I37" s="5" t="inlineStr"/>
+      <c r="I37" s="5"/>
       <c r="J37" s="2" t="n">
         <v>211318</v>
       </c>
@@ -1719,10 +1647,8 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>beta_carotene</t>
-        </is>
+      <c r="A38" t="str">
+        <v>beta_carotene</v>
       </c>
       <c r="B38" s="2" t="n">
         <v>15</v>
@@ -1751,13 +1677,11 @@
       <c r="J38" s="2" t="n">
         <v>122141</v>
       </c>
-      <c r="K38" s="2" t="inlineStr"/>
+      <c r="K38" s="2"/>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>caffeine</t>
-        </is>
+      <c r="A39" t="str">
+        <v>caffeine</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>1</v>
@@ -1771,12 +1695,12 @@
       <c r="E39" s="3" t="n">
         <v>1.02</v>
       </c>
-      <c r="F39" s="3" t="inlineStr"/>
-      <c r="G39" s="3" t="inlineStr"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
       <c r="H39" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I39" s="5" t="inlineStr"/>
+      <c r="I39" s="5"/>
       <c r="J39" s="2" t="n">
         <v>46667</v>
       </c>
@@ -1785,10 +1709,8 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>ginseng</t>
-        </is>
+      <c r="A40" t="str">
+        <v>ginseng</v>
       </c>
       <c r="B40" s="2" t="n">
         <v>1</v>
@@ -1802,12 +1724,12 @@
       <c r="E40" s="3" t="n">
         <v>1.15</v>
       </c>
-      <c r="F40" s="3" t="inlineStr"/>
-      <c r="G40" s="3" t="inlineStr"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
       <c r="H40" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I40" s="5" t="inlineStr"/>
+      <c r="I40" s="5"/>
       <c r="J40" s="2" t="n">
         <v>35239</v>
       </c>
@@ -1816,10 +1738,8 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>total_dietary_fiber_intake</t>
-        </is>
+      <c r="A41" t="str">
+        <v>total_dietary_fiber_intake</v>
       </c>
       <c r="B41" s="2" t="n">
         <v>7</v>
@@ -1853,10 +1773,8 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>dash_diet</t>
-        </is>
+      <c r="A42" t="str">
+        <v>dash_diet</v>
       </c>
       <c r="B42" s="2" t="n">
         <v>2</v>
@@ -1870,22 +1788,20 @@
       <c r="E42" s="3" t="n">
         <v>1.06</v>
       </c>
-      <c r="F42" s="3" t="inlineStr"/>
-      <c r="G42" s="3" t="inlineStr"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
       <c r="H42" s="4" t="n">
-        <v>73.90000000000001</v>
-      </c>
-      <c r="I42" s="5" t="inlineStr"/>
+        <v>73.9</v>
+      </c>
+      <c r="I42" s="5"/>
       <c r="J42" s="2" t="n">
         <v>152714</v>
       </c>
-      <c r="K42" s="2" t="inlineStr"/>
+      <c r="K42" s="2"/>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>ginkgo_biloba</t>
-        </is>
+      <c r="A43" t="str">
+        <v>ginkgo_biloba</v>
       </c>
       <c r="B43" s="2" t="n">
         <v>2</v>
@@ -1899,12 +1815,12 @@
       <c r="E43" s="3" t="n">
         <v>1.27</v>
       </c>
-      <c r="F43" s="3" t="inlineStr"/>
-      <c r="G43" s="3" t="inlineStr"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
       <c r="H43" s="4" t="n">
         <v>46.8</v>
       </c>
-      <c r="I43" s="5" t="inlineStr"/>
+      <c r="I43" s="5"/>
       <c r="J43" s="2" t="n">
         <v>38308</v>
       </c>
@@ -1913,16 +1829,14 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>docosahexaenoic_acid</t>
-        </is>
+      <c r="A44" t="str">
+        <v>docosahexaenoic_acid</v>
       </c>
       <c r="B44" s="2" t="n">
         <v>3</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="D44" s="3" t="n">
         <v>0.74</v>
@@ -1931,7 +1845,7 @@
         <v>1.2</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.07</v>
       </c>
       <c r="G44" s="3" t="n">
         <v>12.3</v>
@@ -1950,16 +1864,14 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>vitamin_e</t>
-        </is>
+      <c r="A45" t="str">
+        <v>vitamin_e</v>
       </c>
       <c r="B45" s="2" t="n">
         <v>25</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>0.87</v>
@@ -1974,7 +1886,7 @@
         <v>1.32</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>75.90000000000001</v>
+        <v>75.9</v>
       </c>
       <c r="I45" s="5" t="n">
         <v>0.1015950190265766</v>
@@ -1987,10 +1899,8 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>omega_6_fatty_acids</t>
-        </is>
+      <c r="A46" t="str">
+        <v>omega_6_fatty_acids</v>
       </c>
       <c r="B46" s="2" t="n">
         <v>2</v>
@@ -2004,12 +1914,12 @@
       <c r="E46" s="3" t="n">
         <v>1.17</v>
       </c>
-      <c r="F46" s="3" t="inlineStr"/>
-      <c r="G46" s="3" t="inlineStr"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
       <c r="H46" s="4" t="n">
         <v>40.4</v>
       </c>
-      <c r="I46" s="5" t="inlineStr"/>
+      <c r="I46" s="5"/>
       <c r="J46" s="2" t="n">
         <v>254243</v>
       </c>
@@ -2018,10 +1928,8 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>plant_protein_intake</t>
-        </is>
+      <c r="A47" t="str">
+        <v>plant_protein_intake</v>
       </c>
       <c r="B47" s="2" t="n">
         <v>1</v>
@@ -2035,12 +1943,12 @@
       <c r="E47" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="F47" s="3" t="inlineStr"/>
-      <c r="G47" s="3" t="inlineStr"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
       <c r="H47" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I47" s="5" t="inlineStr"/>
+      <c r="I47" s="5"/>
       <c r="J47" s="2" t="n">
         <v>150671</v>
       </c>
@@ -2049,10 +1957,8 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>animal_protein_intake</t>
-        </is>
+      <c r="A48" t="str">
+        <v>animal_protein_intake</v>
       </c>
       <c r="B48" s="2" t="n">
         <v>1</v>
@@ -2061,17 +1967,17 @@
         <v>0.99</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="F48" s="3" t="inlineStr"/>
-      <c r="G48" s="3" t="inlineStr"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
       <c r="H48" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I48" s="5" t="inlineStr"/>
+      <c r="I48" s="5"/>
       <c r="J48" s="2" t="n">
         <v>159482</v>
       </c>
@@ -2080,10 +1986,8 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>dietary_protein_intake</t>
-        </is>
+      <c r="A49" t="str">
+        <v>dietary_protein_intake</v>
       </c>
       <c r="B49" s="2" t="n">
         <v>2</v>
@@ -2097,12 +2001,12 @@
       <c r="E49" s="3" t="n">
         <v>1.11</v>
       </c>
-      <c r="F49" s="3" t="inlineStr"/>
-      <c r="G49" s="3" t="inlineStr"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
       <c r="H49" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I49" s="5" t="inlineStr"/>
+      <c r="I49" s="5"/>
       <c r="J49" s="2" t="n">
         <v>109557</v>
       </c>
@@ -2111,10 +2015,8 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>eggs</t>
-        </is>
+      <c r="A50" t="str">
+        <v>eggs</v>
       </c>
       <c r="B50" s="2" t="n">
         <v>3</v>
@@ -2129,7 +2031,7 @@
         <v>1.02</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="G50" s="3" t="n">
         <v>1.2</v>
@@ -2148,10 +2050,8 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>eicosapentaenoic_acid</t>
-        </is>
+      <c r="A51" t="str">
+        <v>eicosapentaenoic_acid</v>
       </c>
       <c r="B51" s="2" t="n">
         <v>5</v>
@@ -2185,10 +2085,8 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>docosapentaenoic_acid_omega_3</t>
-        </is>
+      <c r="A52" t="str">
+        <v>docosapentaenoic_acid_omega_3</v>
       </c>
       <c r="B52" s="2" t="n">
         <v>2</v>
@@ -2202,12 +2100,12 @@
       <c r="E52" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="F52" s="3" t="inlineStr"/>
-      <c r="G52" s="3" t="inlineStr"/>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
       <c r="H52" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I52" s="5" t="inlineStr"/>
+      <c r="I52" s="5"/>
       <c r="J52" s="2" t="n">
         <v>143344</v>
       </c>
@@ -2216,10 +2114,8 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>lutein</t>
-        </is>
+      <c r="A53" t="str">
+        <v>lutein</v>
       </c>
       <c r="B53" s="2" t="n">
         <v>5</v>
@@ -2253,10 +2149,8 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>mediterranean_diet</t>
-        </is>
+      <c r="A54" t="str">
+        <v>mediterranean_diet</v>
       </c>
       <c r="B54" s="2" t="n">
         <v>2</v>
@@ -2270,12 +2164,12 @@
       <c r="E54" s="3" t="n">
         <v>1.11</v>
       </c>
-      <c r="F54" s="3" t="inlineStr"/>
-      <c r="G54" s="3" t="inlineStr"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
       <c r="H54" s="4" t="n">
         <v>69.5</v>
       </c>
-      <c r="I54" s="5" t="inlineStr"/>
+      <c r="I54" s="5"/>
       <c r="J54" s="2" t="n">
         <v>106146</v>
       </c>
@@ -2284,10 +2178,8 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>gondoic_acid</t>
-        </is>
+      <c r="A55" t="str">
+        <v>gondoic_acid</v>
       </c>
       <c r="B55" s="2" t="n">
         <v>1</v>
@@ -2301,12 +2193,12 @@
       <c r="E55" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="F55" s="3" t="inlineStr"/>
-      <c r="G55" s="3" t="inlineStr"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
       <c r="H55" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I55" s="5" t="inlineStr"/>
+      <c r="I55" s="5"/>
       <c r="J55" s="2" t="n">
         <v>142239</v>
       </c>
@@ -2315,10 +2207,8 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>folic_acid</t>
-        </is>
+      <c r="A56" t="str">
+        <v>folic_acid</v>
       </c>
       <c r="B56" s="2" t="n">
         <v>10</v>
@@ -2347,13 +2237,11 @@
       <c r="J56" s="2" t="n">
         <v>157607</v>
       </c>
-      <c r="K56" s="2" t="inlineStr"/>
+      <c r="K56" s="2"/>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>multivitamin</t>
-        </is>
+      <c r="A57" t="str">
+        <v>multivitamin</v>
       </c>
       <c r="B57" s="2" t="n">
         <v>6</v>
@@ -2387,128 +2275,126 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>vitamin_k1</t>
-        </is>
+      <c r="A58" t="str">
+        <v>ultra_processed_food_intake</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C58" s="3" t="n">
         <v>1.02</v>
       </c>
       <c r="D58" s="3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="H58" s="4" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>0.4142673366090839</v>
+      </c>
+      <c r="J58" s="2" t="n">
+        <v>248736</v>
+      </c>
+      <c r="K58" s="2" t="n">
+        <v>13760</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>vitamin_k1</v>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="D59" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="E58" s="3" t="n">
+      <c r="E59" s="3" t="n">
         <v>1.48</v>
       </c>
-      <c r="F58" s="3" t="inlineStr"/>
-      <c r="G58" s="3" t="inlineStr"/>
-      <c r="H58" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" s="5" t="inlineStr"/>
-      <c r="J58" s="2" t="n">
+      <c r="F59" s="3"/>
+      <c r="G59" s="3"/>
+      <c r="H59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="5"/>
+      <c r="J59" s="2" t="n">
         <v>11319</v>
       </c>
-      <c r="K58" s="2" t="n">
+      <c r="K59" s="2" t="n">
         <v>268</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>omega_3_fatty_acids</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="n">
+    <row r="60">
+      <c r="A60" t="str">
+        <v>omega_3_fatty_acids</v>
+      </c>
+      <c r="B60" s="2" t="n">
         <v>10</v>
-      </c>
-      <c r="C59" s="3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="D59" s="3" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="E59" s="3" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="F59" s="3" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="G59" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="H59" s="4" t="n">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="I59" s="5" t="n">
-        <v>0.8028884184138011</v>
-      </c>
-      <c r="J59" s="2" t="n">
-        <v>435151</v>
-      </c>
-      <c r="K59" s="2" t="n">
-        <v>22287</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>saw_palmetto</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="C60" s="3" t="n">
         <v>1.03</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="F60" s="3" t="inlineStr"/>
-      <c r="G60" s="3" t="inlineStr"/>
+        <v>1.11</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>0.81</v>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>1.3</v>
+      </c>
       <c r="H60" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" s="5" t="inlineStr"/>
+        <v>75.6</v>
+      </c>
+      <c r="I60" s="5" t="n">
+        <v>0.8028884184138011</v>
+      </c>
       <c r="J60" s="2" t="n">
-        <v>35239</v>
+        <v>435151</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>1602</v>
+        <v>22287</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>chondroitin</t>
-        </is>
+      <c r="A61" t="str">
+        <v>saw_palmetto</v>
       </c>
       <c r="B61" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="F61" s="3" t="inlineStr"/>
-      <c r="G61" s="3" t="inlineStr"/>
+        <v>1.19</v>
+      </c>
+      <c r="F61" s="3"/>
+      <c r="G61" s="3"/>
       <c r="H61" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I61" s="5" t="inlineStr"/>
+      <c r="I61" s="5"/>
       <c r="J61" s="2" t="n">
         <v>35239</v>
       </c>
@@ -2517,249 +2403,227 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>copper</t>
-        </is>
+      <c r="A62" t="str">
+        <v>chondroitin</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C62" s="3" t="n">
         <v>1.05</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="F62" s="3" t="inlineStr"/>
-      <c r="G62" s="3" t="inlineStr"/>
+        <v>1.21</v>
+      </c>
+      <c r="F62" s="3"/>
+      <c r="G62" s="3"/>
       <c r="H62" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I62" s="5" t="inlineStr"/>
+      <c r="I62" s="5"/>
       <c r="J62" s="2" t="n">
-        <v>43360</v>
+        <v>35239</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>6174</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>iron</t>
-        </is>
+      <c r="A63" t="str">
+        <v>copper</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C63" s="3" t="n">
         <v>1.05</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="F63" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="G63" s="3" t="n">
-        <v>1.41</v>
-      </c>
+        <v>1.11</v>
+      </c>
+      <c r="F63" s="3"/>
+      <c r="G63" s="3"/>
       <c r="H63" s="4" t="n">
-        <v>77.7</v>
-      </c>
-      <c r="I63" s="5" t="n">
-        <v>0.8981574513904265</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I63" s="5"/>
       <c r="J63" s="2" t="n">
-        <v>184031</v>
+        <v>43360</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>11578</v>
+        <v>6174</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>magnesium</t>
-        </is>
+      <c r="A64" t="str">
+        <v>iron</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C64" s="3" t="n">
         <v>1.05</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0.88</v>
+        <v>0.94</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0.16</v>
+        <v>0.78</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>6.88</v>
+        <v>1.41</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>69.59999999999999</v>
+        <v>77.7</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>0.5539761826694968</v>
+        <v>0.8981574513904265</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>44056</v>
+        <v>184031</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>6498</v>
+        <v>11578</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>glucosamine</t>
-        </is>
+      <c r="A65" t="str">
+        <v>magnesium</v>
       </c>
       <c r="B65" s="2" t="n">
         <v>3</v>
       </c>
       <c r="C65" s="3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="G65" s="3" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="H65" s="4" t="n">
+        <v>69.6</v>
+      </c>
+      <c r="I65" s="5" t="n">
+        <v>0.5539761826694968</v>
+      </c>
+      <c r="J65" s="2" t="n">
+        <v>44056</v>
+      </c>
+      <c r="K65" s="2" t="n">
+        <v>6498</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>glucosamine</v>
+      </c>
+      <c r="B66" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C66" s="3" t="n">
         <v>1.06</v>
-      </c>
-      <c r="D65" s="3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="E65" s="3" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="F65" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="G65" s="3" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="H65" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" s="5" t="n">
-        <v>0.01558217739312319</v>
-      </c>
-      <c r="J65" s="2" t="n">
-        <v>265129</v>
-      </c>
-      <c r="K65" s="2" t="n">
-        <v>16136</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>butyric_acid</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C66" s="3" t="n">
-        <v>1.08</v>
       </c>
       <c r="D66" s="3" t="n">
         <v>1.01</v>
       </c>
       <c r="E66" s="3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G66" s="3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" s="5" t="n">
+        <v>0.01558217739312319</v>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>265129</v>
+      </c>
+      <c r="K66" s="2" t="n">
+        <v>16136</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>butyric_acid</v>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="E67" s="3" t="n">
         <v>1.15</v>
       </c>
-      <c r="F66" s="3" t="inlineStr"/>
-      <c r="G66" s="3" t="inlineStr"/>
-      <c r="H66" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" s="5" t="inlineStr"/>
-      <c r="J66" s="2" t="n">
+      <c r="F67" s="3"/>
+      <c r="G67" s="3"/>
+      <c r="H67" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="5"/>
+      <c r="J67" s="2" t="n">
         <v>142239</v>
       </c>
-      <c r="K66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>sugar_sweetened_beverage_intake</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C67" s="3" t="n">
+      <c r="K67" s="2"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>sugar_sweetened_beverage_intake</v>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C68" s="3" t="n">
         <v>1.09</v>
       </c>
-      <c r="D67" s="3" t="n">
+      <c r="D68" s="3" t="n">
         <v>0.93</v>
       </c>
-      <c r="E67" s="3" t="n">
+      <c r="E68" s="3" t="n">
         <v>1.28</v>
       </c>
-      <c r="F67" s="3" t="inlineStr"/>
-      <c r="G67" s="3" t="inlineStr"/>
-      <c r="H67" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" s="5" t="inlineStr"/>
-      <c r="J67" s="2" t="n">
+      <c r="F68" s="3"/>
+      <c r="G68" s="3"/>
+      <c r="H68" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" s="5"/>
+      <c r="J68" s="2" t="n">
         <v>21533</v>
       </c>
-      <c r="K67" s="2" t="n">
+      <c r="K68" s="2" t="n">
         <v>291</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>ultra_processed_food_intake</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C68" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D68" s="3" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="E68" s="3" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="F68" s="3" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G68" s="3" t="n">
-        <v>19.09</v>
-      </c>
-      <c r="H68" s="4" t="n">
-        <v>73.7</v>
-      </c>
-      <c r="I68" s="5" t="n">
-        <v>0.5701786686486264</v>
-      </c>
-      <c r="J68" s="2" t="n">
-        <v>4983</v>
-      </c>
-      <c r="K68" s="2" t="n">
-        <v>2932</v>
-      </c>
-    </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>vitamin_b2</t>
-        </is>
+      <c r="A69" t="str">
+        <v>vitamin_b2</v>
       </c>
       <c r="B69" s="2" t="n">
         <v>1</v>
@@ -2773,12 +2637,12 @@
       <c r="E69" s="3" t="n">
         <v>1.23</v>
       </c>
-      <c r="F69" s="3" t="inlineStr"/>
-      <c r="G69" s="3" t="inlineStr"/>
+      <c r="F69" s="3"/>
+      <c r="G69" s="3"/>
       <c r="H69" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I69" s="5" t="inlineStr"/>
+      <c r="I69" s="5"/>
       <c r="J69" s="2" t="n">
         <v>1595</v>
       </c>
@@ -2787,10 +2651,8 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>whole_grain_intake</t>
-        </is>
+      <c r="A70" t="str">
+        <v>whole_grain_intake</v>
       </c>
       <c r="B70" s="2" t="n">
         <v>3</v>
@@ -2824,10 +2686,8 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>phosphorus</t>
-        </is>
+      <c r="A71" t="str">
+        <v>phosphorus</v>
       </c>
       <c r="B71" s="2" t="n">
         <v>1</v>
@@ -2841,12 +2701,12 @@
       <c r="E71" s="3" t="n">
         <v>1.23</v>
       </c>
-      <c r="F71" s="3" t="inlineStr"/>
-      <c r="G71" s="3" t="inlineStr"/>
+      <c r="F71" s="3"/>
+      <c r="G71" s="3"/>
       <c r="H71" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I71" s="5" t="inlineStr"/>
+      <c r="I71" s="5"/>
       <c r="J71" s="2" t="n">
         <v>47885</v>
       </c>
@@ -2855,10 +2715,8 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>vitamin_b12</t>
-        </is>
+      <c r="A72" t="str">
+        <v>vitamin_b12</v>
       </c>
       <c r="B72" s="2" t="n">
         <v>5</v>
@@ -2892,10 +2750,8 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>processed_meat_intake</t>
-        </is>
+      <c r="A73" t="str">
+        <v>processed_meat_intake</v>
       </c>
       <c r="B73" s="2" t="n">
         <v>10</v>
@@ -2929,10 +2785,8 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>vitamin_d</t>
-        </is>
+      <c r="A74" t="str">
+        <v>vitamin_d</v>
       </c>
       <c r="B74" s="2" t="n">
         <v>28</v>
@@ -2961,13 +2815,11 @@
       <c r="J74" s="2" t="n">
         <v>551351</v>
       </c>
-      <c r="K74" s="2" t="inlineStr"/>
+      <c r="K74" s="2"/>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>antioxidants</t>
-        </is>
+      <c r="A75" t="str">
+        <v>antioxidants</v>
       </c>
       <c r="B75" s="2" t="n">
         <v>3</v>
@@ -3001,10 +2853,8 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>vitamin_a</t>
-        </is>
+      <c r="A76" t="str">
+        <v>vitamin_a</v>
       </c>
       <c r="B76" s="2" t="n">
         <v>13</v>
@@ -3025,7 +2875,7 @@
         <v>2.43</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>88.40000000000001</v>
+        <v>88.4</v>
       </c>
       <c r="I76" s="5" t="n">
         <v>0.949064906966266</v>
@@ -3038,10 +2888,8 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>calcium</t>
-        </is>
+      <c r="A77" t="str">
+        <v>calcium</v>
       </c>
       <c r="B77" s="2" t="n">
         <v>28</v>
@@ -3070,13 +2918,11 @@
       <c r="J77" s="2" t="n">
         <v>1049042</v>
       </c>
-      <c r="K77" s="2" t="inlineStr"/>
+      <c r="K77" s="2"/>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>zinc</t>
-        </is>
+      <c r="A78" t="str">
+        <v>zinc</v>
       </c>
       <c r="B78" s="2" t="n">
         <v>12</v>
@@ -3097,7 +2943,7 @@
         <v>3.04</v>
       </c>
       <c r="H78" s="4" t="n">
-        <v>79.90000000000001</v>
+        <v>79.9</v>
       </c>
       <c r="I78" s="5" t="n">
         <v>0.5711938735931297</v>
@@ -3110,10 +2956,8 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>coenzyme_q10</t>
-        </is>
+      <c r="A79" t="str">
+        <v>coenzyme_q10</v>
       </c>
       <c r="B79" s="2" t="n">
         <v>3</v>
@@ -3134,7 +2978,7 @@
         <v>119.97</v>
       </c>
       <c r="H79" s="4" t="n">
-        <v>69.40000000000001</v>
+        <v>69.4</v>
       </c>
       <c r="I79" s="5" t="n">
         <v>0.3692661628018609</v>
@@ -3147,10 +2991,8 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>alcohol</t>
-        </is>
+      <c r="A80" t="str">
+        <v>alcohol</v>
       </c>
       <c r="B80" s="2" t="n">
         <v>29</v>
@@ -3171,7 +3013,7 @@
         <v>1.66</v>
       </c>
       <c r="H80" s="4" t="n">
-        <v>86.59999999999999</v>
+        <v>86.6</v>
       </c>
       <c r="I80" s="5" t="n">
         <v>0.005523619063522766</v>
@@ -3179,13 +3021,11 @@
       <c r="J80" s="2" t="n">
         <v>1934957</v>
       </c>
-      <c r="K80" s="2" t="inlineStr"/>
+      <c r="K80" s="2"/>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>dairy</t>
-        </is>
+      <c r="A81" t="str">
+        <v>dairy</v>
       </c>
       <c r="B81" s="2" t="n">
         <v>24</v>
@@ -3219,10 +3059,8 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>glutamine</t>
-        </is>
+      <c r="A82" t="str">
+        <v>glutamine</v>
       </c>
       <c r="B82" s="2" t="n">
         <v>1</v>
@@ -3236,12 +3074,12 @@
       <c r="E82" s="3" t="n">
         <v>1.56</v>
       </c>
-      <c r="F82" s="3" t="inlineStr"/>
-      <c r="G82" s="3" t="inlineStr"/>
+      <c r="F82" s="3"/>
+      <c r="G82" s="3"/>
       <c r="H82" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I82" s="5" t="inlineStr"/>
+      <c r="I82" s="5"/>
       <c r="J82" s="2" t="n">
         <v>342</v>
       </c>
@@ -3250,10 +3088,8 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>yogurt</t>
-        </is>
+      <c r="A83" t="str">
+        <v>yogurt</v>
       </c>
       <c r="B83" s="2" t="n">
         <v>3</v>
@@ -3287,10 +3123,8 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>betaine</t>
-        </is>
+      <c r="A84" t="str">
+        <v>betaine</v>
       </c>
       <c r="B84" s="2" t="n">
         <v>2</v>
@@ -3304,12 +3138,12 @@
       <c r="E84" s="3" t="n">
         <v>2.32</v>
       </c>
-      <c r="F84" s="3" t="inlineStr"/>
-      <c r="G84" s="3" t="inlineStr"/>
+      <c r="F84" s="3"/>
+      <c r="G84" s="3"/>
       <c r="H84" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="I84" s="5" t="inlineStr"/>
+      <c r="I84" s="5"/>
       <c r="J84" s="2" t="n">
         <v>48588</v>
       </c>
@@ -3318,10 +3152,8 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>alpha_linolenic_acid</t>
-        </is>
+      <c r="A85" t="str">
+        <v>alpha_linolenic_acid</v>
       </c>
       <c r="B85" s="2" t="n">
         <v>8</v>
@@ -3355,10 +3187,8 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>creatine</t>
-        </is>
+      <c r="A86" t="str">
+        <v>creatine</v>
       </c>
       <c r="B86" s="2" t="n">
         <v>1</v>
@@ -3372,12 +3202,12 @@
       <c r="E86" s="3" t="n">
         <v>1.63</v>
       </c>
-      <c r="F86" s="3" t="inlineStr"/>
-      <c r="G86" s="3" t="inlineStr"/>
+      <c r="F86" s="3"/>
+      <c r="G86" s="3"/>
       <c r="H86" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I86" s="5" t="inlineStr"/>
+      <c r="I86" s="5"/>
       <c r="J86" s="2" t="n">
         <v>342</v>
       </c>
@@ -3386,10 +3216,8 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>l_valine</t>
-        </is>
+      <c r="A87" t="str">
+        <v>l_valine</v>
       </c>
       <c r="B87" s="2" t="n">
         <v>1</v>
@@ -3403,12 +3231,12 @@
       <c r="E87" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="F87" s="3" t="inlineStr"/>
-      <c r="G87" s="3" t="inlineStr"/>
+      <c r="F87" s="3"/>
+      <c r="G87" s="3"/>
       <c r="H87" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I87" s="5" t="inlineStr"/>
+      <c r="I87" s="5"/>
       <c r="J87" s="2" t="n">
         <v>342</v>
       </c>
@@ -3417,10 +3245,8 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>l_tyrosine</t>
-        </is>
+      <c r="A88" t="str">
+        <v>l_tyrosine</v>
       </c>
       <c r="B88" s="2" t="n">
         <v>1</v>
@@ -3434,12 +3260,12 @@
       <c r="E88" s="3" t="n">
         <v>1.66</v>
       </c>
-      <c r="F88" s="3" t="inlineStr"/>
-      <c r="G88" s="3" t="inlineStr"/>
+      <c r="F88" s="3"/>
+      <c r="G88" s="3"/>
       <c r="H88" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I88" s="5" t="inlineStr"/>
+      <c r="I88" s="5"/>
       <c r="J88" s="2" t="n">
         <v>342</v>
       </c>
@@ -3448,10 +3274,8 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>mineral_supplements</t>
-        </is>
+      <c r="A89" t="str">
+        <v>mineral_supplements</v>
       </c>
       <c r="B89" s="2" t="n">
         <v>2</v>
@@ -3465,12 +3289,12 @@
       <c r="E89" s="3" t="n">
         <v>2.26</v>
       </c>
-      <c r="F89" s="3" t="inlineStr"/>
-      <c r="G89" s="3" t="inlineStr"/>
+      <c r="F89" s="3"/>
+      <c r="G89" s="3"/>
       <c r="H89" s="4" t="n">
-        <v>80.09999999999999</v>
-      </c>
-      <c r="I89" s="5" t="inlineStr"/>
+        <v>80.1</v>
+      </c>
+      <c r="I89" s="5"/>
       <c r="J89" s="2" t="n">
         <v>57251</v>
       </c>
@@ -3479,10 +3303,8 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>chocolate</t>
-        </is>
+      <c r="A90" t="str">
+        <v>chocolate</v>
       </c>
       <c r="B90" s="2" t="n">
         <v>1</v>
@@ -3496,12 +3318,12 @@
       <c r="E90" s="3" t="n">
         <v>1.64</v>
       </c>
-      <c r="F90" s="3" t="inlineStr"/>
-      <c r="G90" s="3" t="inlineStr"/>
+      <c r="F90" s="3"/>
+      <c r="G90" s="3"/>
       <c r="H90" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I90" s="5" t="inlineStr"/>
+      <c r="I90" s="5"/>
       <c r="J90" s="2" t="n">
         <v>2611</v>
       </c>
@@ -3510,10 +3332,8 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>western_pattern_diet</t>
-        </is>
+      <c r="A91" t="str">
+        <v>western_pattern_diet</v>
       </c>
       <c r="B91" s="2" t="n">
         <v>2</v>
@@ -3527,12 +3347,12 @@
       <c r="E91" s="3" t="n">
         <v>1.82</v>
       </c>
-      <c r="F91" s="3" t="inlineStr"/>
-      <c r="G91" s="3" t="inlineStr"/>
+      <c r="F91" s="3"/>
+      <c r="G91" s="3"/>
       <c r="H91" s="4" t="n">
         <v>57.1</v>
       </c>
-      <c r="I91" s="5" t="inlineStr"/>
+      <c r="I91" s="5"/>
       <c r="J91" s="2" t="n">
         <v>44462</v>
       </c>
@@ -3541,10 +3361,8 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>fermented_foods</t>
-        </is>
+      <c r="A92" t="str">
+        <v>fermented_foods</v>
       </c>
       <c r="B92" s="2" t="n">
         <v>3</v>
@@ -3562,7 +3380,7 @@
         <v>0</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>664.3099999999999</v>
+        <v>664.31</v>
       </c>
       <c r="H92" s="4" t="n">
         <v>62</v>
@@ -3578,10 +3396,8 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>polyunsaturated_fat_pufa</t>
-        </is>
+      <c r="A93" t="str">
+        <v>polyunsaturated_fat_pufa</v>
       </c>
       <c r="B93" s="2" t="n">
         <v>5</v>
@@ -3610,13 +3426,11 @@
       <c r="J93" s="2" t="n">
         <v>64788</v>
       </c>
-      <c r="K93" s="2" t="inlineStr"/>
+      <c r="K93" s="2"/>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>choline</t>
-        </is>
+      <c r="A94" t="str">
+        <v>choline</v>
       </c>
       <c r="B94" s="2" t="n">
         <v>3</v>
@@ -3650,10 +3464,8 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>gamma_linolenic_acid</t>
-        </is>
+      <c r="A95" t="str">
+        <v>gamma_linolenic_acid</v>
       </c>
       <c r="B95" s="2" t="n">
         <v>1</v>
@@ -3662,17 +3474,17 @@
         <v>1.41</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="E95" s="3" t="n">
         <v>2.12</v>
       </c>
-      <c r="F95" s="3" t="inlineStr"/>
-      <c r="G95" s="3" t="inlineStr"/>
+      <c r="F95" s="3"/>
+      <c r="G95" s="3"/>
       <c r="H95" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I95" s="5" t="inlineStr"/>
+      <c r="I95" s="5"/>
       <c r="J95" s="2" t="n">
         <v>952</v>
       </c>
@@ -3681,10 +3493,8 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>dihomo_gamma_linolenic_acid</t>
-        </is>
+      <c r="A96" t="str">
+        <v>dihomo_gamma_linolenic_acid</v>
       </c>
       <c r="B96" s="2" t="n">
         <v>1</v>
@@ -3698,12 +3508,12 @@
       <c r="E96" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="F96" s="3" t="inlineStr"/>
-      <c r="G96" s="3" t="inlineStr"/>
+      <c r="F96" s="3"/>
+      <c r="G96" s="3"/>
       <c r="H96" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I96" s="5" t="inlineStr"/>
+      <c r="I96" s="5"/>
       <c r="J96" s="2" t="n">
         <v>952</v>
       </c>
@@ -3712,10 +3522,8 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>monounsaturated_fat_mufa</t>
-        </is>
+      <c r="A97" t="str">
+        <v>monounsaturated_fat_mufa</v>
       </c>
       <c r="B97" s="2" t="n">
         <v>7</v>
@@ -3736,7 +3544,7 @@
         <v>3.31</v>
       </c>
       <c r="H97" s="4" t="n">
-        <v>86.40000000000001</v>
+        <v>86.4</v>
       </c>
       <c r="I97" s="5" t="n">
         <v>0.014204608998772</v>
@@ -3744,13 +3552,11 @@
       <c r="J97" s="2" t="n">
         <v>56815</v>
       </c>
-      <c r="K97" s="2" t="inlineStr"/>
+      <c r="K97" s="2"/>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>red_meat</t>
-        </is>
+      <c r="A98" t="str">
+        <v>red_meat</v>
       </c>
       <c r="B98" s="2" t="n">
         <v>14</v>
@@ -3771,7 +3577,7 @@
         <v>4.51</v>
       </c>
       <c r="H98" s="4" t="n">
-        <v>89.59999999999999</v>
+        <v>89.6</v>
       </c>
       <c r="I98" s="5" t="n">
         <v>0.01959176169058006</v>
@@ -3784,10 +3590,8 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>phosphatidylcholine</t>
-        </is>
+      <c r="A99" t="str">
+        <v>phosphatidylcholine</v>
       </c>
       <c r="B99" s="2" t="n">
         <v>1</v>
@@ -3801,12 +3605,12 @@
       <c r="E99" s="3" t="n">
         <v>2.87</v>
       </c>
-      <c r="F99" s="3" t="inlineStr"/>
-      <c r="G99" s="3" t="inlineStr"/>
+      <c r="F99" s="3"/>
+      <c r="G99" s="3"/>
       <c r="H99" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I99" s="5" t="inlineStr"/>
+      <c r="I99" s="5"/>
       <c r="J99" s="2" t="n">
         <v>310</v>
       </c>
@@ -3815,10 +3619,8 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>glycine</t>
-        </is>
+      <c r="A100" t="str">
+        <v>glycine</v>
       </c>
       <c r="B100" s="2" t="n">
         <v>1</v>
@@ -3832,12 +3634,12 @@
       <c r="E100" s="3" t="n">
         <v>2.72</v>
       </c>
-      <c r="F100" s="3" t="inlineStr"/>
-      <c r="G100" s="3" t="inlineStr"/>
+      <c r="F100" s="3"/>
+      <c r="G100" s="3"/>
       <c r="H100" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I100" s="5" t="inlineStr"/>
+      <c r="I100" s="5"/>
       <c r="J100" s="2" t="n">
         <v>666</v>
       </c>
@@ -3846,10 +3648,8 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>carnitine</t>
-        </is>
+      <c r="A101" t="str">
+        <v>carnitine</v>
       </c>
       <c r="B101" s="2" t="n">
         <v>1</v>
@@ -3863,12 +3663,12 @@
       <c r="E101" s="3" t="n">
         <v>3.56</v>
       </c>
-      <c r="F101" s="3" t="inlineStr"/>
-      <c r="G101" s="3" t="inlineStr"/>
+      <c r="F101" s="3"/>
+      <c r="G101" s="3"/>
       <c r="H101" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I101" s="5" t="inlineStr"/>
+      <c r="I101" s="5"/>
       <c r="J101" s="2" t="n">
         <v>692</v>
       </c>
@@ -3877,10 +3677,8 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>pickled_vegetables</t>
-        </is>
+      <c r="A102" t="str">
+        <v>pickled_vegetables</v>
       </c>
       <c r="B102" s="2" t="n">
         <v>1</v>
@@ -3894,12 +3692,12 @@
       <c r="E102" s="3" t="n">
         <v>5.94</v>
       </c>
-      <c r="F102" s="3" t="inlineStr"/>
-      <c r="G102" s="3" t="inlineStr"/>
+      <c r="F102" s="3"/>
+      <c r="G102" s="3"/>
       <c r="H102" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I102" s="5" t="inlineStr"/>
+      <c r="I102" s="5"/>
       <c r="J102" s="2" t="n">
         <v>404</v>
       </c>

--- a/summary/no/exposures_meta_analysis_prostate_cancer_combined.xlsx
+++ b/summary/no/exposures_meta_analysis_prostate_cancer_combined.xlsx
@@ -450,7 +450,7 @@
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
   </cols>
-  <sheetData xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
@@ -509,8 +509,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>vitamin_b1</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>vitamin_b1</t>
+        </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
@@ -524,12 +526,12 @@
       <c r="E2" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
       <c r="H2" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="5"/>
+      <c r="I2" s="5" t="inlineStr"/>
       <c r="J2" s="2" t="n">
         <v>204</v>
       </c>
@@ -538,8 +540,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>natto</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>natto</t>
+        </is>
       </c>
       <c r="B3" s="2" t="n">
         <v>1</v>
@@ -553,12 +557,12 @@
       <c r="E3" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="5"/>
+      <c r="I3" s="5" t="inlineStr"/>
       <c r="J3" s="2" t="n">
         <v>280</v>
       </c>
@@ -567,8 +571,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>papaya</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>papaya</t>
+        </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>1</v>
@@ -582,12 +588,12 @@
       <c r="E4" s="3" t="n">
         <v>0.97</v>
       </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr"/>
       <c r="H4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="5"/>
+      <c r="I4" s="5" t="inlineStr"/>
       <c r="J4" s="2" t="n">
         <v>105</v>
       </c>
@@ -596,27 +602,29 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>inositol</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>inositol</t>
+        </is>
       </c>
       <c r="B5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.56</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>0.39</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0.81</v>
-      </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="5"/>
+      <c r="I5" s="5" t="inlineStr"/>
       <c r="J5" s="2" t="n">
         <v>400</v>
       </c>
@@ -625,8 +633,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
-        <v>early_time_restricted_eating</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>early_time_restricted_eating</t>
+        </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>1</v>
@@ -640,12 +650,12 @@
       <c r="E6" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="5"/>
+      <c r="I6" s="5" t="inlineStr"/>
       <c r="J6" s="2" t="n">
         <v>1455</v>
       </c>
@@ -654,8 +664,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="str">
-        <v>soy</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>soy</t>
+        </is>
       </c>
       <c r="B7" s="2" t="n">
         <v>8</v>
@@ -676,7 +688,7 @@
         <v>2.09</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>78.9</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I7" s="5" t="n">
         <v>0.1010785350953814</v>
@@ -689,8 +701,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="str">
-        <v>green_tea</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>green_tea</t>
+        </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>7</v>
@@ -714,7 +728,7 @@
         <v>72.7</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>0.1767576153047421</v>
+        <v>0.1767576153047418</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>99090</v>
@@ -724,8 +738,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="str">
-        <v>insoluble_dietary_fiber_intake</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>insoluble_dietary_fiber_intake</t>
+        </is>
       </c>
       <c r="B9" s="2" t="n">
         <v>3</v>
@@ -746,7 +762,7 @@
         <v>206.11</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>74.9</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I9" s="5" t="n">
         <v>0.1151715356999109</v>
@@ -754,11 +770,13 @@
       <c r="J9" s="2" t="n">
         <v>101084</v>
       </c>
-      <c r="K9" s="2"/>
+      <c r="K9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="str">
-        <v>low_fat_diet</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>low_fat_diet</t>
+        </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>1</v>
@@ -772,12 +790,12 @@
       <c r="E10" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
+      <c r="F10" s="3" t="inlineStr"/>
+      <c r="G10" s="3" t="inlineStr"/>
       <c r="H10" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I10" s="5"/>
+      <c r="I10" s="5" t="inlineStr"/>
       <c r="J10" s="2" t="n">
         <v>1170</v>
       </c>
@@ -786,8 +804,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="str">
-        <v>vitamin_k2</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>vitamin_k2</t>
+        </is>
       </c>
       <c r="B11" s="2" t="n">
         <v>1</v>
@@ -801,12 +821,12 @@
       <c r="E11" s="3" t="n">
         <v>1.06</v>
       </c>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
+      <c r="F11" s="3" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr"/>
       <c r="H11" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="5"/>
+      <c r="I11" s="5" t="inlineStr"/>
       <c r="J11" s="2" t="n">
         <v>11319</v>
       </c>
@@ -815,8 +835,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="str">
-        <v>zeaxanthin</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>zeaxanthin</t>
+        </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>4</v>
@@ -840,7 +862,7 @@
         <v>62.9</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.8236639670954936</v>
+        <v>0.8236639670954935</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>2106</v>
@@ -850,8 +872,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="str">
-        <v>quercetin</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>quercetin</t>
+        </is>
       </c>
       <c r="B13" s="2" t="n">
         <v>1</v>
@@ -865,12 +889,12 @@
       <c r="E13" s="3" t="n">
         <v>0.93</v>
       </c>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
+      <c r="F13" s="3" t="inlineStr"/>
+      <c r="G13" s="3" t="inlineStr"/>
       <c r="H13" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="5"/>
+      <c r="I13" s="5" t="inlineStr"/>
       <c r="J13" s="2" t="n">
         <v>971</v>
       </c>
@@ -879,8 +903,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="str">
-        <v>vegan_diet</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>vegan_diet</t>
+        </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>1</v>
@@ -894,12 +920,12 @@
       <c r="E14" s="3" t="n">
         <v>0.86</v>
       </c>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
+      <c r="F14" s="3" t="inlineStr"/>
+      <c r="G14" s="3" t="inlineStr"/>
       <c r="H14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I14" s="5"/>
+      <c r="I14" s="5" t="inlineStr"/>
       <c r="J14" s="2" t="n">
         <v>26346</v>
       </c>
@@ -908,8 +934,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="str">
-        <v>pyruvate</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>pyruvate</t>
+        </is>
       </c>
       <c r="B15" s="2" t="n">
         <v>1</v>
@@ -923,12 +951,12 @@
       <c r="E15" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
+      <c r="F15" s="3" t="inlineStr"/>
+      <c r="G15" s="3" t="inlineStr"/>
       <c r="H15" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="5"/>
+      <c r="I15" s="5" t="inlineStr"/>
       <c r="J15" s="2" t="n">
         <v>666</v>
       </c>
@@ -937,14 +965,16 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="str">
-        <v>garlic</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>garlic</t>
+        </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>3</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.69</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>0.42</v>
@@ -972,8 +1002,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="str">
-        <v>vegetarian_diet</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>vegetarian_diet</t>
+        </is>
       </c>
       <c r="B17" s="2" t="n">
         <v>1</v>
@@ -982,17 +1014,17 @@
         <v>0.7</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.56</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
+      <c r="F17" s="3" t="inlineStr"/>
+      <c r="G17" s="3" t="inlineStr"/>
       <c r="H17" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I17" s="5"/>
+      <c r="I17" s="5" t="inlineStr"/>
       <c r="J17" s="2" t="n">
         <v>217937</v>
       </c>
@@ -1001,8 +1033,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="str">
-        <v>linoleic_acid</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>linoleic_acid</t>
+        </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>7</v>
@@ -1026,7 +1060,7 @@
         <v>70.5</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>0.4789848163683072</v>
+        <v>0.4789848163683078</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>8735</v>
@@ -1036,8 +1070,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="str">
-        <v>genistein</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>genistein</t>
+        </is>
       </c>
       <c r="B19" s="2" t="n">
         <v>9</v>
@@ -1061,7 +1097,7 @@
         <v>67.8</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>0.04176805723275343</v>
+        <v>0.04176805723275333</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>91302</v>
@@ -1071,8 +1107,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="str">
-        <v>vitamin_k</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>vitamin_k</t>
+        </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>2</v>
@@ -1086,12 +1124,12 @@
       <c r="E20" s="3" t="n">
         <v>0.92</v>
       </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" s="3" t="inlineStr"/>
       <c r="H20" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="5"/>
+      <c r="I20" s="5" t="inlineStr"/>
       <c r="J20" s="2" t="n">
         <v>12063</v>
       </c>
@@ -1100,8 +1138,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="str">
-        <v>tomato</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>tomato</t>
+        </is>
       </c>
       <c r="B21" s="2" t="n">
         <v>11</v>
@@ -1122,10 +1162,10 @@
         <v>1.16</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>78.1</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>0.00002045420729252852</v>
+        <v>2.045420729252859e-05</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>1057923</v>
@@ -1135,8 +1175,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="str">
-        <v>melatonin</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>melatonin</t>
+        </is>
       </c>
       <c r="B22" s="2" t="n">
         <v>3</v>
@@ -1170,8 +1212,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="str">
-        <v>tea</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>tea</t>
+        </is>
       </c>
       <c r="B23" s="2" t="n">
         <v>10</v>
@@ -1192,10 +1236,10 @@
         <v>1.27</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>84.9</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>0.04996208468350858</v>
+        <v>0.04996208468350857</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>314398</v>
@@ -1205,8 +1249,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="str">
-        <v>citrulline</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>citrulline</t>
+        </is>
       </c>
       <c r="B24" s="2" t="n">
         <v>1</v>
@@ -1220,12 +1266,12 @@
       <c r="E24" s="3" t="n">
         <v>0.88</v>
       </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
+      <c r="F24" s="3" t="inlineStr"/>
+      <c r="G24" s="3" t="inlineStr"/>
       <c r="H24" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I24" s="5"/>
+      <c r="I24" s="5" t="inlineStr"/>
       <c r="J24" s="2" t="n">
         <v>2154</v>
       </c>
@@ -1234,8 +1280,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="str">
-        <v>potassium</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>potassium</t>
+        </is>
       </c>
       <c r="B25" s="2" t="n">
         <v>1</v>
@@ -1249,12 +1297,12 @@
       <c r="E25" s="3" t="n">
         <v>1.08</v>
       </c>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr"/>
       <c r="H25" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I25" s="5"/>
+      <c r="I25" s="5" t="inlineStr"/>
       <c r="J25" s="2" t="n">
         <v>656</v>
       </c>
@@ -1263,8 +1311,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="str">
-        <v>selenium</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>selenium</t>
+        </is>
       </c>
       <c r="B26" s="2" t="n">
         <v>28</v>
@@ -1285,10 +1335,10 @@
         <v>1.48</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>84.9</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>0.0008136772771022814</v>
+        <v>0.0008136772771022832</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>382643</v>
@@ -1298,8 +1348,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="str">
-        <v>iodine</v>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>iodine</t>
+        </is>
       </c>
       <c r="B27" s="2" t="n">
         <v>1</v>
@@ -1313,12 +1365,12 @@
       <c r="E27" s="3" t="n">
         <v>1.09</v>
       </c>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
+      <c r="F27" s="3" t="inlineStr"/>
+      <c r="G27" s="3" t="inlineStr"/>
       <c r="H27" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I27" s="5"/>
+      <c r="I27" s="5" t="inlineStr"/>
       <c r="J27" s="2" t="n">
         <v>656</v>
       </c>
@@ -1327,8 +1379,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="str">
-        <v>time_restricted_eating</v>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>time_restricted_eating</t>
+        </is>
       </c>
       <c r="B28" s="2" t="n">
         <v>1</v>
@@ -1342,12 +1396,12 @@
       <c r="E28" s="3" t="n">
         <v>1.06</v>
       </c>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
+      <c r="F28" s="3" t="inlineStr"/>
+      <c r="G28" s="3" t="inlineStr"/>
       <c r="H28" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I28" s="5"/>
+      <c r="I28" s="5" t="inlineStr"/>
       <c r="J28" s="2" t="n">
         <v>1455</v>
       </c>
@@ -1356,8 +1410,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="str">
-        <v>oleic_acid</v>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>oleic_acid</t>
+        </is>
       </c>
       <c r="B29" s="2" t="n">
         <v>2</v>
@@ -1371,12 +1427,12 @@
       <c r="E29" s="3" t="n">
         <v>2.64</v>
       </c>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
+      <c r="F29" s="3" t="inlineStr"/>
+      <c r="G29" s="3" t="inlineStr"/>
       <c r="H29" s="4" t="n">
         <v>82</v>
       </c>
-      <c r="I29" s="5"/>
+      <c r="I29" s="5" t="inlineStr"/>
       <c r="J29" s="2" t="n">
         <v>58714</v>
       </c>
@@ -1385,8 +1441,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="str">
-        <v>mushrooms</v>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>mushrooms</t>
+        </is>
       </c>
       <c r="B30" s="2" t="n">
         <v>1</v>
@@ -1400,12 +1458,12 @@
       <c r="E30" s="3" t="n">
         <v>0.98</v>
       </c>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
+      <c r="F30" s="3" t="inlineStr"/>
+      <c r="G30" s="3" t="inlineStr"/>
       <c r="H30" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I30" s="5"/>
+      <c r="I30" s="5" t="inlineStr"/>
       <c r="J30" s="2" t="n">
         <v>36499</v>
       </c>
@@ -1414,8 +1472,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="str">
-        <v>lycopene</v>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>lycopene</t>
+        </is>
       </c>
       <c r="B31" s="2" t="n">
         <v>20</v>
@@ -1436,7 +1496,7 @@
         <v>1.15</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>71.4</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="I31" s="5" t="n">
         <v>0.0008787392868700852</v>
@@ -1449,8 +1509,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="str">
-        <v>vitamin_c</v>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>vitamin_c</t>
+        </is>
       </c>
       <c r="B32" s="2" t="n">
         <v>11</v>
@@ -1471,10 +1533,10 @@
         <v>1.49</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>79.1</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>0.9264859141728315</v>
+        <v>0.926485914172831</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>68944</v>
@@ -1484,8 +1546,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="str">
-        <v>fish_oil</v>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>fish_oil</t>
+        </is>
       </c>
       <c r="B33" s="2" t="n">
         <v>2</v>
@@ -1499,12 +1563,12 @@
       <c r="E33" s="3" t="n">
         <v>1.17</v>
       </c>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
+      <c r="F33" s="3" t="inlineStr"/>
+      <c r="G33" s="3" t="inlineStr"/>
       <c r="H33" s="4" t="n">
         <v>47.9</v>
       </c>
-      <c r="I33" s="5"/>
+      <c r="I33" s="5" t="inlineStr"/>
       <c r="J33" s="2" t="n">
         <v>37289</v>
       </c>
@@ -1513,8 +1577,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="str">
-        <v>legumes</v>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>legumes</t>
+        </is>
       </c>
       <c r="B34" s="2" t="n">
         <v>8</v>
@@ -1523,7 +1589,7 @@
         <v>0.89</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0.81</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>0.97</v>
@@ -1538,7 +1604,7 @@
         <v>62.4</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>0.006170430008920979</v>
+        <v>0.00617043000892098</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>1155076</v>
@@ -1548,8 +1614,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="str">
-        <v>soluble_dietary_fiber_intake</v>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>soluble_dietary_fiber_intake</t>
+        </is>
       </c>
       <c r="B35" s="2" t="n">
         <v>3</v>
@@ -1573,7 +1641,7 @@
         <v>0</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>0.188399637329524</v>
+        <v>0.1883996373295245</v>
       </c>
       <c r="J35" s="2" t="n">
         <v>80888</v>
@@ -1583,8 +1651,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="str">
-        <v>vitamin_b6</v>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>vitamin_b6</t>
+        </is>
       </c>
       <c r="B36" s="2" t="n">
         <v>3</v>
@@ -1618,8 +1688,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="str">
-        <v>plant_based_diet</v>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>plant_based_diet</t>
+        </is>
       </c>
       <c r="B37" s="2" t="n">
         <v>2</v>
@@ -1633,12 +1705,12 @@
       <c r="E37" s="3" t="n">
         <v>0.99</v>
       </c>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
+      <c r="F37" s="3" t="inlineStr"/>
+      <c r="G37" s="3" t="inlineStr"/>
       <c r="H37" s="4" t="n">
         <v>39.5</v>
       </c>
-      <c r="I37" s="5"/>
+      <c r="I37" s="5" t="inlineStr"/>
       <c r="J37" s="2" t="n">
         <v>211318</v>
       </c>
@@ -1647,8 +1719,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="str">
-        <v>beta_carotene</v>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>beta_carotene</t>
+        </is>
       </c>
       <c r="B38" s="2" t="n">
         <v>15</v>
@@ -1672,16 +1746,18 @@
         <v>76</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>0.375241327694828</v>
+        <v>0.3752413276948279</v>
       </c>
       <c r="J38" s="2" t="n">
         <v>122141</v>
       </c>
-      <c r="K38" s="2"/>
+      <c r="K38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" t="str">
-        <v>caffeine</v>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>caffeine</t>
+        </is>
       </c>
       <c r="B39" s="2" t="n">
         <v>1</v>
@@ -1695,12 +1771,12 @@
       <c r="E39" s="3" t="n">
         <v>1.02</v>
       </c>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
+      <c r="F39" s="3" t="inlineStr"/>
+      <c r="G39" s="3" t="inlineStr"/>
       <c r="H39" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I39" s="5"/>
+      <c r="I39" s="5" t="inlineStr"/>
       <c r="J39" s="2" t="n">
         <v>46667</v>
       </c>
@@ -1709,8 +1785,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="str">
-        <v>ginseng</v>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ginseng</t>
+        </is>
       </c>
       <c r="B40" s="2" t="n">
         <v>1</v>
@@ -1724,12 +1802,12 @@
       <c r="E40" s="3" t="n">
         <v>1.15</v>
       </c>
-      <c r="F40" s="3"/>
-      <c r="G40" s="3"/>
+      <c r="F40" s="3" t="inlineStr"/>
+      <c r="G40" s="3" t="inlineStr"/>
       <c r="H40" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I40" s="5"/>
+      <c r="I40" s="5" t="inlineStr"/>
       <c r="J40" s="2" t="n">
         <v>35239</v>
       </c>
@@ -1738,8 +1816,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="str">
-        <v>total_dietary_fiber_intake</v>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>total_dietary_fiber_intake</t>
+        </is>
       </c>
       <c r="B41" s="2" t="n">
         <v>7</v>
@@ -1763,7 +1843,7 @@
         <v>42.9</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>0.07744276379719466</v>
+        <v>0.0774427637971946</v>
       </c>
       <c r="J41" s="2" t="n">
         <v>972077</v>
@@ -1773,8 +1853,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="str">
-        <v>dash_diet</v>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>dash_diet</t>
+        </is>
       </c>
       <c r="B42" s="2" t="n">
         <v>2</v>
@@ -1788,20 +1870,22 @@
       <c r="E42" s="3" t="n">
         <v>1.06</v>
       </c>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3"/>
+      <c r="F42" s="3" t="inlineStr"/>
+      <c r="G42" s="3" t="inlineStr"/>
       <c r="H42" s="4" t="n">
-        <v>73.9</v>
-      </c>
-      <c r="I42" s="5"/>
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I42" s="5" t="inlineStr"/>
       <c r="J42" s="2" t="n">
         <v>152714</v>
       </c>
-      <c r="K42" s="2"/>
+      <c r="K42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" t="str">
-        <v>ginkgo_biloba</v>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ginkgo_biloba</t>
+        </is>
       </c>
       <c r="B43" s="2" t="n">
         <v>2</v>
@@ -1815,12 +1899,12 @@
       <c r="E43" s="3" t="n">
         <v>1.27</v>
       </c>
-      <c r="F43" s="3"/>
-      <c r="G43" s="3"/>
+      <c r="F43" s="3" t="inlineStr"/>
+      <c r="G43" s="3" t="inlineStr"/>
       <c r="H43" s="4" t="n">
         <v>46.8</v>
       </c>
-      <c r="I43" s="5"/>
+      <c r="I43" s="5" t="inlineStr"/>
       <c r="J43" s="2" t="n">
         <v>38308</v>
       </c>
@@ -1829,14 +1913,16 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="str">
-        <v>docosahexaenoic_acid</v>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>docosahexaenoic_acid</t>
+        </is>
       </c>
       <c r="B44" s="2" t="n">
         <v>3</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>0.94</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D44" s="3" t="n">
         <v>0.74</v>
@@ -1845,7 +1931,7 @@
         <v>1.2</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.07</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G44" s="3" t="n">
         <v>12.3</v>
@@ -1854,7 +1940,7 @@
         <v>55.4</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>0.6285558694668993</v>
+        <v>0.6285558694668995</v>
       </c>
       <c r="J44" s="2" t="n">
         <v>144141</v>
@@ -1864,14 +1950,16 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="str">
-        <v>vitamin_e</v>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>vitamin_e</t>
+        </is>
       </c>
       <c r="B45" s="2" t="n">
         <v>25</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>0.94</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>0.87</v>
@@ -1886,10 +1974,10 @@
         <v>1.32</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>75.9</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>0.1015950190265766</v>
+        <v>0.1015950190265765</v>
       </c>
       <c r="J45" s="2" t="n">
         <v>404649</v>
@@ -1899,8 +1987,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="str">
-        <v>omega_6_fatty_acids</v>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>omega_6_fatty_acids</t>
+        </is>
       </c>
       <c r="B46" s="2" t="n">
         <v>2</v>
@@ -1914,12 +2004,12 @@
       <c r="E46" s="3" t="n">
         <v>1.17</v>
       </c>
-      <c r="F46" s="3"/>
-      <c r="G46" s="3"/>
+      <c r="F46" s="3" t="inlineStr"/>
+      <c r="G46" s="3" t="inlineStr"/>
       <c r="H46" s="4" t="n">
         <v>40.4</v>
       </c>
-      <c r="I46" s="5"/>
+      <c r="I46" s="5" t="inlineStr"/>
       <c r="J46" s="2" t="n">
         <v>254243</v>
       </c>
@@ -1928,8 +2018,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="str">
-        <v>plant_protein_intake</v>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>plant_protein_intake</t>
+        </is>
       </c>
       <c r="B47" s="2" t="n">
         <v>1</v>
@@ -1943,12 +2035,12 @@
       <c r="E47" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="F47" s="3"/>
-      <c r="G47" s="3"/>
+      <c r="F47" s="3" t="inlineStr"/>
+      <c r="G47" s="3" t="inlineStr"/>
       <c r="H47" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I47" s="5"/>
+      <c r="I47" s="5" t="inlineStr"/>
       <c r="J47" s="2" t="n">
         <v>150671</v>
       </c>
@@ -1957,8 +2049,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="str">
-        <v>animal_protein_intake</v>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>animal_protein_intake</t>
+        </is>
       </c>
       <c r="B48" s="2" t="n">
         <v>1</v>
@@ -1967,17 +2061,17 @@
         <v>0.99</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.94</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="F48" s="3"/>
-      <c r="G48" s="3"/>
+      <c r="F48" s="3" t="inlineStr"/>
+      <c r="G48" s="3" t="inlineStr"/>
       <c r="H48" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I48" s="5"/>
+      <c r="I48" s="5" t="inlineStr"/>
       <c r="J48" s="2" t="n">
         <v>159482</v>
       </c>
@@ -1986,8 +2080,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="str">
-        <v>dietary_protein_intake</v>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>dietary_protein_intake</t>
+        </is>
       </c>
       <c r="B49" s="2" t="n">
         <v>2</v>
@@ -2001,12 +2097,12 @@
       <c r="E49" s="3" t="n">
         <v>1.11</v>
       </c>
-      <c r="F49" s="3"/>
-      <c r="G49" s="3"/>
+      <c r="F49" s="3" t="inlineStr"/>
+      <c r="G49" s="3" t="inlineStr"/>
       <c r="H49" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I49" s="5"/>
+      <c r="I49" s="5" t="inlineStr"/>
       <c r="J49" s="2" t="n">
         <v>109557</v>
       </c>
@@ -2015,8 +2111,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="str">
-        <v>eggs</v>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>eggs</t>
+        </is>
       </c>
       <c r="B50" s="2" t="n">
         <v>3</v>
@@ -2031,7 +2129,7 @@
         <v>1.02</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>0.81</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G50" s="3" t="n">
         <v>1.2</v>
@@ -2050,8 +2148,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="str">
-        <v>eicosapentaenoic_acid</v>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>eicosapentaenoic_acid</t>
+        </is>
       </c>
       <c r="B51" s="2" t="n">
         <v>5</v>
@@ -2075,7 +2175,7 @@
         <v>65.2</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>0.5746798036256721</v>
+        <v>0.5746798036256719</v>
       </c>
       <c r="J51" s="2" t="n">
         <v>444156</v>
@@ -2085,8 +2185,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="str">
-        <v>docosapentaenoic_acid_omega_3</v>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>docosapentaenoic_acid_omega_3</t>
+        </is>
       </c>
       <c r="B52" s="2" t="n">
         <v>2</v>
@@ -2100,12 +2202,12 @@
       <c r="E52" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="F52" s="3"/>
-      <c r="G52" s="3"/>
+      <c r="F52" s="3" t="inlineStr"/>
+      <c r="G52" s="3" t="inlineStr"/>
       <c r="H52" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I52" s="5"/>
+      <c r="I52" s="5" t="inlineStr"/>
       <c r="J52" s="2" t="n">
         <v>143344</v>
       </c>
@@ -2114,8 +2216,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="str">
-        <v>lutein</v>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>lutein</t>
+        </is>
       </c>
       <c r="B53" s="2" t="n">
         <v>5</v>
@@ -2139,7 +2243,7 @@
         <v>84.2</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>0.9535391069907841</v>
+        <v>0.9535391069907844</v>
       </c>
       <c r="J53" s="2" t="n">
         <v>3128</v>
@@ -2149,8 +2253,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="str">
-        <v>mediterranean_diet</v>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>mediterranean_diet</t>
+        </is>
       </c>
       <c r="B54" s="2" t="n">
         <v>2</v>
@@ -2164,12 +2270,12 @@
       <c r="E54" s="3" t="n">
         <v>1.11</v>
       </c>
-      <c r="F54" s="3"/>
-      <c r="G54" s="3"/>
+      <c r="F54" s="3" t="inlineStr"/>
+      <c r="G54" s="3" t="inlineStr"/>
       <c r="H54" s="4" t="n">
         <v>69.5</v>
       </c>
-      <c r="I54" s="5"/>
+      <c r="I54" s="5" t="inlineStr"/>
       <c r="J54" s="2" t="n">
         <v>106146</v>
       </c>
@@ -2178,8 +2284,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="str">
-        <v>gondoic_acid</v>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>gondoic_acid</t>
+        </is>
       </c>
       <c r="B55" s="2" t="n">
         <v>1</v>
@@ -2193,12 +2301,12 @@
       <c r="E55" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="F55" s="3"/>
-      <c r="G55" s="3"/>
+      <c r="F55" s="3" t="inlineStr"/>
+      <c r="G55" s="3" t="inlineStr"/>
       <c r="H55" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I55" s="5"/>
+      <c r="I55" s="5" t="inlineStr"/>
       <c r="J55" s="2" t="n">
         <v>142239</v>
       </c>
@@ -2207,8 +2315,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="str">
-        <v>folic_acid</v>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>folic_acid</t>
+        </is>
       </c>
       <c r="B56" s="2" t="n">
         <v>10</v>
@@ -2232,16 +2342,18 @@
         <v>49</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>0.09195795349035613</v>
+        <v>0.09195795349035596</v>
       </c>
       <c r="J56" s="2" t="n">
         <v>157607</v>
       </c>
-      <c r="K56" s="2"/>
+      <c r="K56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" t="str">
-        <v>multivitamin</v>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>multivitamin</t>
+        </is>
       </c>
       <c r="B57" s="2" t="n">
         <v>6</v>
@@ -2275,8 +2387,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="str">
-        <v>ultra_processed_food_intake</v>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ultra_processed_food_intake</t>
+        </is>
       </c>
       <c r="B58" s="2" t="n">
         <v>6</v>
@@ -2300,7 +2414,7 @@
         <v>38.1</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>0.4142673366090839</v>
+        <v>0.4142673366090832</v>
       </c>
       <c r="J58" s="2" t="n">
         <v>248736</v>
@@ -2310,8 +2424,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="str">
-        <v>vitamin_k1</v>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>vitamin_k1</t>
+        </is>
       </c>
       <c r="B59" s="2" t="n">
         <v>1</v>
@@ -2325,12 +2441,12 @@
       <c r="E59" s="3" t="n">
         <v>1.48</v>
       </c>
-      <c r="F59" s="3"/>
-      <c r="G59" s="3"/>
+      <c r="F59" s="3" t="inlineStr"/>
+      <c r="G59" s="3" t="inlineStr"/>
       <c r="H59" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I59" s="5"/>
+      <c r="I59" s="5" t="inlineStr"/>
       <c r="J59" s="2" t="n">
         <v>11319</v>
       </c>
@@ -2339,8 +2455,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="str">
-        <v>omega_3_fatty_acids</v>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>omega_3_fatty_acids</t>
+        </is>
       </c>
       <c r="B60" s="2" t="n">
         <v>10</v>
@@ -2355,16 +2473,16 @@
         <v>1.11</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0.81</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G60" s="3" t="n">
         <v>1.3</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>75.6</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>0.8028884184138011</v>
+        <v>0.8028884184138012</v>
       </c>
       <c r="J60" s="2" t="n">
         <v>435151</v>
@@ -2374,8 +2492,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="str">
-        <v>saw_palmetto</v>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>saw_palmetto</t>
+        </is>
       </c>
       <c r="B61" s="2" t="n">
         <v>1</v>
@@ -2389,12 +2509,12 @@
       <c r="E61" s="3" t="n">
         <v>1.19</v>
       </c>
-      <c r="F61" s="3"/>
-      <c r="G61" s="3"/>
+      <c r="F61" s="3" t="inlineStr"/>
+      <c r="G61" s="3" t="inlineStr"/>
       <c r="H61" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I61" s="5"/>
+      <c r="I61" s="5" t="inlineStr"/>
       <c r="J61" s="2" t="n">
         <v>35239</v>
       </c>
@@ -2403,8 +2523,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="str">
-        <v>chondroitin</v>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>chondroitin</t>
+        </is>
       </c>
       <c r="B62" s="2" t="n">
         <v>1</v>
@@ -2418,12 +2540,12 @@
       <c r="E62" s="3" t="n">
         <v>1.21</v>
       </c>
-      <c r="F62" s="3"/>
-      <c r="G62" s="3"/>
+      <c r="F62" s="3" t="inlineStr"/>
+      <c r="G62" s="3" t="inlineStr"/>
       <c r="H62" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I62" s="5"/>
+      <c r="I62" s="5" t="inlineStr"/>
       <c r="J62" s="2" t="n">
         <v>35239</v>
       </c>
@@ -2432,8 +2554,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="str">
-        <v>copper</v>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>copper</t>
+        </is>
       </c>
       <c r="B63" s="2" t="n">
         <v>2</v>
@@ -2447,12 +2571,12 @@
       <c r="E63" s="3" t="n">
         <v>1.11</v>
       </c>
-      <c r="F63" s="3"/>
-      <c r="G63" s="3"/>
+      <c r="F63" s="3" t="inlineStr"/>
+      <c r="G63" s="3" t="inlineStr"/>
       <c r="H63" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I63" s="5"/>
+      <c r="I63" s="5" t="inlineStr"/>
       <c r="J63" s="2" t="n">
         <v>43360</v>
       </c>
@@ -2461,8 +2585,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="str">
-        <v>iron</v>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
       </c>
       <c r="B64" s="2" t="n">
         <v>5</v>
@@ -2471,7 +2597,7 @@
         <v>1.05</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0.94</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E64" s="3" t="n">
         <v>1.16</v>
@@ -2486,7 +2612,7 @@
         <v>77.7</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>0.8981574513904265</v>
+        <v>0.8981574513904264</v>
       </c>
       <c r="J64" s="2" t="n">
         <v>184031</v>
@@ -2496,8 +2622,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="str">
-        <v>magnesium</v>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>magnesium</t>
+        </is>
       </c>
       <c r="B65" s="2" t="n">
         <v>3</v>
@@ -2518,7 +2646,7 @@
         <v>6.88</v>
       </c>
       <c r="H65" s="4" t="n">
-        <v>69.6</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="I65" s="5" t="n">
         <v>0.5539761826694968</v>
@@ -2531,8 +2659,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="str">
-        <v>glucosamine</v>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>glucosamine</t>
+        </is>
       </c>
       <c r="B66" s="2" t="n">
         <v>3</v>
@@ -2566,8 +2696,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="str">
-        <v>butyric_acid</v>
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>butyric_acid</t>
+        </is>
       </c>
       <c r="B67" s="2" t="n">
         <v>1</v>
@@ -2581,20 +2713,22 @@
       <c r="E67" s="3" t="n">
         <v>1.15</v>
       </c>
-      <c r="F67" s="3"/>
-      <c r="G67" s="3"/>
+      <c r="F67" s="3" t="inlineStr"/>
+      <c r="G67" s="3" t="inlineStr"/>
       <c r="H67" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I67" s="5"/>
+      <c r="I67" s="5" t="inlineStr"/>
       <c r="J67" s="2" t="n">
         <v>142239</v>
       </c>
-      <c r="K67" s="2"/>
+      <c r="K67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" t="str">
-        <v>sugar_sweetened_beverage_intake</v>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>sugar_sweetened_beverage_intake</t>
+        </is>
       </c>
       <c r="B68" s="2" t="n">
         <v>1</v>
@@ -2608,12 +2742,12 @@
       <c r="E68" s="3" t="n">
         <v>1.28</v>
       </c>
-      <c r="F68" s="3"/>
-      <c r="G68" s="3"/>
+      <c r="F68" s="3" t="inlineStr"/>
+      <c r="G68" s="3" t="inlineStr"/>
       <c r="H68" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I68" s="5"/>
+      <c r="I68" s="5" t="inlineStr"/>
       <c r="J68" s="2" t="n">
         <v>21533</v>
       </c>
@@ -2622,8 +2756,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="str">
-        <v>vitamin_b2</v>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>vitamin_b2</t>
+        </is>
       </c>
       <c r="B69" s="2" t="n">
         <v>1</v>
@@ -2637,12 +2773,12 @@
       <c r="E69" s="3" t="n">
         <v>1.23</v>
       </c>
-      <c r="F69" s="3"/>
-      <c r="G69" s="3"/>
+      <c r="F69" s="3" t="inlineStr"/>
+      <c r="G69" s="3" t="inlineStr"/>
       <c r="H69" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I69" s="5"/>
+      <c r="I69" s="5" t="inlineStr"/>
       <c r="J69" s="2" t="n">
         <v>1595</v>
       </c>
@@ -2651,8 +2787,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="str">
-        <v>whole_grain_intake</v>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>whole_grain_intake</t>
+        </is>
       </c>
       <c r="B70" s="2" t="n">
         <v>3</v>
@@ -2686,8 +2824,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="str">
-        <v>phosphorus</v>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>phosphorus</t>
+        </is>
       </c>
       <c r="B71" s="2" t="n">
         <v>1</v>
@@ -2701,12 +2841,12 @@
       <c r="E71" s="3" t="n">
         <v>1.23</v>
       </c>
-      <c r="F71" s="3"/>
-      <c r="G71" s="3"/>
+      <c r="F71" s="3" t="inlineStr"/>
+      <c r="G71" s="3" t="inlineStr"/>
       <c r="H71" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I71" s="5"/>
+      <c r="I71" s="5" t="inlineStr"/>
       <c r="J71" s="2" t="n">
         <v>47885</v>
       </c>
@@ -2715,8 +2855,10 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="str">
-        <v>vitamin_b12</v>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>vitamin_b12</t>
+        </is>
       </c>
       <c r="B72" s="2" t="n">
         <v>5</v>
@@ -2750,8 +2892,10 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="str">
-        <v>processed_meat_intake</v>
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>processed_meat_intake</t>
+        </is>
       </c>
       <c r="B73" s="2" t="n">
         <v>10</v>
@@ -2775,7 +2919,7 @@
         <v>71.2</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>0.002637956795546257</v>
+        <v>0.002637956795546261</v>
       </c>
       <c r="J73" s="2" t="n">
         <v>1091655</v>
@@ -2785,8 +2929,10 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="str">
-        <v>vitamin_d</v>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>vitamin_d</t>
+        </is>
       </c>
       <c r="B74" s="2" t="n">
         <v>28</v>
@@ -2810,16 +2956,18 @@
         <v>72.8</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>0.1064622161384286</v>
+        <v>0.1064622161384289</v>
       </c>
       <c r="J74" s="2" t="n">
         <v>551351</v>
       </c>
-      <c r="K74" s="2"/>
+      <c r="K74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" t="str">
-        <v>antioxidants</v>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>antioxidants</t>
+        </is>
       </c>
       <c r="B75" s="2" t="n">
         <v>3</v>
@@ -2853,8 +3001,10 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="str">
-        <v>vitamin_a</v>
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>vitamin_a</t>
+        </is>
       </c>
       <c r="B76" s="2" t="n">
         <v>13</v>
@@ -2875,10 +3025,10 @@
         <v>2.43</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>88.4</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I76" s="5" t="n">
-        <v>0.949064906966266</v>
+        <v>0.9490649069662659</v>
       </c>
       <c r="J76" s="2" t="n">
         <v>70012</v>
@@ -2888,8 +3038,10 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="str">
-        <v>calcium</v>
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>calcium</t>
+        </is>
       </c>
       <c r="B77" s="2" t="n">
         <v>28</v>
@@ -2913,16 +3065,18 @@
         <v>80.7</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>0.00672767540667003</v>
+        <v>0.006727675406670032</v>
       </c>
       <c r="J77" s="2" t="n">
         <v>1049042</v>
       </c>
-      <c r="K77" s="2"/>
+      <c r="K77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" t="str">
-        <v>zinc</v>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>zinc</t>
+        </is>
       </c>
       <c r="B78" s="2" t="n">
         <v>12</v>
@@ -2943,7 +3097,7 @@
         <v>3.04</v>
       </c>
       <c r="H78" s="4" t="n">
-        <v>79.9</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I78" s="5" t="n">
         <v>0.5711938735931297</v>
@@ -2956,8 +3110,10 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="str">
-        <v>coenzyme_q10</v>
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>coenzyme_q10</t>
+        </is>
       </c>
       <c r="B79" s="2" t="n">
         <v>3</v>
@@ -2978,7 +3134,7 @@
         <v>119.97</v>
       </c>
       <c r="H79" s="4" t="n">
-        <v>69.4</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="I79" s="5" t="n">
         <v>0.3692661628018609</v>
@@ -2991,8 +3147,10 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="str">
-        <v>alcohol</v>
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>alcohol</t>
+        </is>
       </c>
       <c r="B80" s="2" t="n">
         <v>29</v>
@@ -3013,19 +3171,21 @@
         <v>1.66</v>
       </c>
       <c r="H80" s="4" t="n">
-        <v>86.6</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>0.005523619063522766</v>
+        <v>0.00552361906352278</v>
       </c>
       <c r="J80" s="2" t="n">
         <v>1934957</v>
       </c>
-      <c r="K80" s="2"/>
+      <c r="K80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" t="str">
-        <v>dairy</v>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
       </c>
       <c r="B81" s="2" t="n">
         <v>24</v>
@@ -3049,7 +3209,7 @@
         <v>82.7</v>
       </c>
       <c r="I81" s="5" t="n">
-        <v>0.09941545468620652</v>
+        <v>0.09941545468620654</v>
       </c>
       <c r="J81" s="2" t="n">
         <v>739672</v>
@@ -3059,8 +3219,10 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="str">
-        <v>glutamine</v>
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>glutamine</t>
+        </is>
       </c>
       <c r="B82" s="2" t="n">
         <v>1</v>
@@ -3074,12 +3236,12 @@
       <c r="E82" s="3" t="n">
         <v>1.56</v>
       </c>
-      <c r="F82" s="3"/>
-      <c r="G82" s="3"/>
+      <c r="F82" s="3" t="inlineStr"/>
+      <c r="G82" s="3" t="inlineStr"/>
       <c r="H82" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I82" s="5"/>
+      <c r="I82" s="5" t="inlineStr"/>
       <c r="J82" s="2" t="n">
         <v>342</v>
       </c>
@@ -3088,8 +3250,10 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="str">
-        <v>yogurt</v>
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>yogurt</t>
+        </is>
       </c>
       <c r="B83" s="2" t="n">
         <v>3</v>
@@ -3123,8 +3287,10 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="str">
-        <v>betaine</v>
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>betaine</t>
+        </is>
       </c>
       <c r="B84" s="2" t="n">
         <v>2</v>
@@ -3138,12 +3304,12 @@
       <c r="E84" s="3" t="n">
         <v>2.32</v>
       </c>
-      <c r="F84" s="3"/>
-      <c r="G84" s="3"/>
+      <c r="F84" s="3" t="inlineStr"/>
+      <c r="G84" s="3" t="inlineStr"/>
       <c r="H84" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="I84" s="5"/>
+      <c r="I84" s="5" t="inlineStr"/>
       <c r="J84" s="2" t="n">
         <v>48588</v>
       </c>
@@ -3152,8 +3318,10 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="str">
-        <v>alpha_linolenic_acid</v>
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>alpha_linolenic_acid</t>
+        </is>
       </c>
       <c r="B85" s="2" t="n">
         <v>8</v>
@@ -3177,7 +3345,7 @@
         <v>85.2</v>
       </c>
       <c r="I85" s="5" t="n">
-        <v>0.02434834414134602</v>
+        <v>0.02434834414134598</v>
       </c>
       <c r="J85" s="2" t="n">
         <v>557816</v>
@@ -3187,8 +3355,10 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="str">
-        <v>creatine</v>
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>creatine</t>
+        </is>
       </c>
       <c r="B86" s="2" t="n">
         <v>1</v>
@@ -3202,12 +3372,12 @@
       <c r="E86" s="3" t="n">
         <v>1.63</v>
       </c>
-      <c r="F86" s="3"/>
-      <c r="G86" s="3"/>
+      <c r="F86" s="3" t="inlineStr"/>
+      <c r="G86" s="3" t="inlineStr"/>
       <c r="H86" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I86" s="5"/>
+      <c r="I86" s="5" t="inlineStr"/>
       <c r="J86" s="2" t="n">
         <v>342</v>
       </c>
@@ -3216,8 +3386,10 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="str">
-        <v>l_valine</v>
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>l_valine</t>
+        </is>
       </c>
       <c r="B87" s="2" t="n">
         <v>1</v>
@@ -3231,12 +3403,12 @@
       <c r="E87" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="F87" s="3"/>
-      <c r="G87" s="3"/>
+      <c r="F87" s="3" t="inlineStr"/>
+      <c r="G87" s="3" t="inlineStr"/>
       <c r="H87" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I87" s="5"/>
+      <c r="I87" s="5" t="inlineStr"/>
       <c r="J87" s="2" t="n">
         <v>342</v>
       </c>
@@ -3245,8 +3417,10 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="str">
-        <v>l_tyrosine</v>
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>l_tyrosine</t>
+        </is>
       </c>
       <c r="B88" s="2" t="n">
         <v>1</v>
@@ -3260,12 +3434,12 @@
       <c r="E88" s="3" t="n">
         <v>1.66</v>
       </c>
-      <c r="F88" s="3"/>
-      <c r="G88" s="3"/>
+      <c r="F88" s="3" t="inlineStr"/>
+      <c r="G88" s="3" t="inlineStr"/>
       <c r="H88" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I88" s="5"/>
+      <c r="I88" s="5" t="inlineStr"/>
       <c r="J88" s="2" t="n">
         <v>342</v>
       </c>
@@ -3274,8 +3448,10 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="str">
-        <v>mineral_supplements</v>
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>mineral_supplements</t>
+        </is>
       </c>
       <c r="B89" s="2" t="n">
         <v>2</v>
@@ -3289,12 +3465,12 @@
       <c r="E89" s="3" t="n">
         <v>2.26</v>
       </c>
-      <c r="F89" s="3"/>
-      <c r="G89" s="3"/>
+      <c r="F89" s="3" t="inlineStr"/>
+      <c r="G89" s="3" t="inlineStr"/>
       <c r="H89" s="4" t="n">
-        <v>80.1</v>
-      </c>
-      <c r="I89" s="5"/>
+        <v>80.09999999999999</v>
+      </c>
+      <c r="I89" s="5" t="inlineStr"/>
       <c r="J89" s="2" t="n">
         <v>57251</v>
       </c>
@@ -3303,8 +3479,10 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="str">
-        <v>chocolate</v>
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>chocolate</t>
+        </is>
       </c>
       <c r="B90" s="2" t="n">
         <v>1</v>
@@ -3318,12 +3496,12 @@
       <c r="E90" s="3" t="n">
         <v>1.64</v>
       </c>
-      <c r="F90" s="3"/>
-      <c r="G90" s="3"/>
+      <c r="F90" s="3" t="inlineStr"/>
+      <c r="G90" s="3" t="inlineStr"/>
       <c r="H90" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I90" s="5"/>
+      <c r="I90" s="5" t="inlineStr"/>
       <c r="J90" s="2" t="n">
         <v>2611</v>
       </c>
@@ -3332,8 +3510,10 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="str">
-        <v>western_pattern_diet</v>
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>western_pattern_diet</t>
+        </is>
       </c>
       <c r="B91" s="2" t="n">
         <v>2</v>
@@ -3347,12 +3527,12 @@
       <c r="E91" s="3" t="n">
         <v>1.82</v>
       </c>
-      <c r="F91" s="3"/>
-      <c r="G91" s="3"/>
+      <c r="F91" s="3" t="inlineStr"/>
+      <c r="G91" s="3" t="inlineStr"/>
       <c r="H91" s="4" t="n">
         <v>57.1</v>
       </c>
-      <c r="I91" s="5"/>
+      <c r="I91" s="5" t="inlineStr"/>
       <c r="J91" s="2" t="n">
         <v>44462</v>
       </c>
@@ -3361,8 +3541,10 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="str">
-        <v>fermented_foods</v>
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>fermented_foods</t>
+        </is>
       </c>
       <c r="B92" s="2" t="n">
         <v>3</v>
@@ -3380,13 +3562,13 @@
         <v>0</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>664.31</v>
+        <v>664.3099999999999</v>
       </c>
       <c r="H92" s="4" t="n">
         <v>62</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>0.1814798483236068</v>
+        <v>0.1814798483236069</v>
       </c>
       <c r="J92" s="2" t="n">
         <v>3460</v>
@@ -3396,8 +3578,10 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="str">
-        <v>polyunsaturated_fat_pufa</v>
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>polyunsaturated_fat_pufa</t>
+        </is>
       </c>
       <c r="B93" s="2" t="n">
         <v>5</v>
@@ -3421,16 +3605,18 @@
         <v>88.7</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>0.5930181744853597</v>
+        <v>0.5930181744853599</v>
       </c>
       <c r="J93" s="2" t="n">
         <v>64788</v>
       </c>
-      <c r="K93" s="2"/>
+      <c r="K93" s="2" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" t="str">
-        <v>choline</v>
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>choline</t>
+        </is>
       </c>
       <c r="B94" s="2" t="n">
         <v>3</v>
@@ -3454,7 +3640,7 @@
         <v>77</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>0.03888700959299776</v>
+        <v>0.03888700959299778</v>
       </c>
       <c r="J94" s="2" t="n">
         <v>8815</v>
@@ -3464,8 +3650,10 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="str">
-        <v>gamma_linolenic_acid</v>
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>gamma_linolenic_acid</t>
+        </is>
       </c>
       <c r="B95" s="2" t="n">
         <v>1</v>
@@ -3474,17 +3662,17 @@
         <v>1.41</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.94</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E95" s="3" t="n">
         <v>2.12</v>
       </c>
-      <c r="F95" s="3"/>
-      <c r="G95" s="3"/>
+      <c r="F95" s="3" t="inlineStr"/>
+      <c r="G95" s="3" t="inlineStr"/>
       <c r="H95" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I95" s="5"/>
+      <c r="I95" s="5" t="inlineStr"/>
       <c r="J95" s="2" t="n">
         <v>952</v>
       </c>
@@ -3493,8 +3681,10 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="str">
-        <v>dihomo_gamma_linolenic_acid</v>
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>dihomo_gamma_linolenic_acid</t>
+        </is>
       </c>
       <c r="B96" s="2" t="n">
         <v>1</v>
@@ -3508,12 +3698,12 @@
       <c r="E96" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="F96" s="3"/>
-      <c r="G96" s="3"/>
+      <c r="F96" s="3" t="inlineStr"/>
+      <c r="G96" s="3" t="inlineStr"/>
       <c r="H96" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I96" s="5"/>
+      <c r="I96" s="5" t="inlineStr"/>
       <c r="J96" s="2" t="n">
         <v>952</v>
       </c>
@@ -3522,8 +3712,10 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="str">
-        <v>monounsaturated_fat_mufa</v>
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>monounsaturated_fat_mufa</t>
+        </is>
       </c>
       <c r="B97" s="2" t="n">
         <v>7</v>
@@ -3544,19 +3736,21 @@
         <v>3.31</v>
       </c>
       <c r="H97" s="4" t="n">
-        <v>86.4</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I97" s="5" t="n">
-        <v>0.014204608998772</v>
+        <v>0.01420460899877199</v>
       </c>
       <c r="J97" s="2" t="n">
         <v>56815</v>
       </c>
-      <c r="K97" s="2"/>
+      <c r="K97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" t="str">
-        <v>red_meat</v>
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>red_meat</t>
+        </is>
       </c>
       <c r="B98" s="2" t="n">
         <v>14</v>
@@ -3577,10 +3771,10 @@
         <v>4.51</v>
       </c>
       <c r="H98" s="4" t="n">
-        <v>89.6</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="I98" s="5" t="n">
-        <v>0.01959176169058006</v>
+        <v>0.01959176169058002</v>
       </c>
       <c r="J98" s="2" t="n">
         <v>974550</v>
@@ -3590,8 +3784,10 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="str">
-        <v>phosphatidylcholine</v>
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>phosphatidylcholine</t>
+        </is>
       </c>
       <c r="B99" s="2" t="n">
         <v>1</v>
@@ -3605,12 +3801,12 @@
       <c r="E99" s="3" t="n">
         <v>2.87</v>
       </c>
-      <c r="F99" s="3"/>
-      <c r="G99" s="3"/>
+      <c r="F99" s="3" t="inlineStr"/>
+      <c r="G99" s="3" t="inlineStr"/>
       <c r="H99" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I99" s="5"/>
+      <c r="I99" s="5" t="inlineStr"/>
       <c r="J99" s="2" t="n">
         <v>310</v>
       </c>
@@ -3619,8 +3815,10 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="str">
-        <v>glycine</v>
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>glycine</t>
+        </is>
       </c>
       <c r="B100" s="2" t="n">
         <v>1</v>
@@ -3634,12 +3832,12 @@
       <c r="E100" s="3" t="n">
         <v>2.72</v>
       </c>
-      <c r="F100" s="3"/>
-      <c r="G100" s="3"/>
+      <c r="F100" s="3" t="inlineStr"/>
+      <c r="G100" s="3" t="inlineStr"/>
       <c r="H100" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I100" s="5"/>
+      <c r="I100" s="5" t="inlineStr"/>
       <c r="J100" s="2" t="n">
         <v>666</v>
       </c>
@@ -3648,8 +3846,10 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="str">
-        <v>carnitine</v>
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>carnitine</t>
+        </is>
       </c>
       <c r="B101" s="2" t="n">
         <v>1</v>
@@ -3663,12 +3863,12 @@
       <c r="E101" s="3" t="n">
         <v>3.56</v>
       </c>
-      <c r="F101" s="3"/>
-      <c r="G101" s="3"/>
+      <c r="F101" s="3" t="inlineStr"/>
+      <c r="G101" s="3" t="inlineStr"/>
       <c r="H101" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I101" s="5"/>
+      <c r="I101" s="5" t="inlineStr"/>
       <c r="J101" s="2" t="n">
         <v>692</v>
       </c>
@@ -3677,8 +3877,10 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="str">
-        <v>pickled_vegetables</v>
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>pickled_vegetables</t>
+        </is>
       </c>
       <c r="B102" s="2" t="n">
         <v>1</v>
@@ -3692,12 +3894,12 @@
       <c r="E102" s="3" t="n">
         <v>5.94</v>
       </c>
-      <c r="F102" s="3"/>
-      <c r="G102" s="3"/>
+      <c r="F102" s="3" t="inlineStr"/>
+      <c r="G102" s="3" t="inlineStr"/>
       <c r="H102" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I102" s="5"/>
+      <c r="I102" s="5" t="inlineStr"/>
       <c r="J102" s="2" t="n">
         <v>404</v>
       </c>

--- a/summary/no/exposures_meta_analysis_prostate_cancer_combined.xlsx
+++ b/summary/no/exposures_meta_analysis_prostate_cancer_combined.xlsx
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -49,7 +52,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -57,13 +60,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -452,57 +464,57 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Exposure</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>number studies</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Pooled RR</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>lower CI RR</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>upper CI RR</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>lower PI RR</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>upper PI RR</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>I^2 (%)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>eggers p-value</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>total N</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>total Cases</t>
         </is>
@@ -514,28 +526,28 @@
           <t>vitamin_b1</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="3" t="n">
+      <c r="B2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="n">
         <v>0.03</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="4" t="n">
         <v>0.01</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="4" t="n">
         <v>0.1</v>
       </c>
-      <c r="F2" s="3" t="inlineStr"/>
-      <c r="G2" s="3" t="inlineStr"/>
-      <c r="H2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="5" t="inlineStr"/>
-      <c r="J2" s="2" t="n">
+      <c r="F2" s="4" t="inlineStr"/>
+      <c r="G2" s="4" t="inlineStr"/>
+      <c r="H2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="6" t="inlineStr"/>
+      <c r="J2" s="3" t="n">
         <v>204</v>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="K2" s="3" t="n">
         <v>102</v>
       </c>
     </row>
@@ -545,28 +557,28 @@
           <t>natto</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="3" t="n">
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="4" t="n">
         <v>0.28</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="4" t="n">
         <v>0.06</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="4" t="n">
         <v>1.2</v>
       </c>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="5" t="inlineStr"/>
-      <c r="J3" s="2" t="n">
+      <c r="F3" s="4" t="inlineStr"/>
+      <c r="G3" s="4" t="inlineStr"/>
+      <c r="H3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="6" t="inlineStr"/>
+      <c r="J3" s="3" t="n">
         <v>280</v>
       </c>
-      <c r="K3" s="2" t="n">
+      <c r="K3" s="3" t="n">
         <v>140</v>
       </c>
     </row>
@@ -576,28 +588,28 @@
           <t>papaya</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="3" t="n">
+      <c r="B4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="4" t="n">
         <v>0.4</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="4" t="n">
         <v>0.15</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="4" t="n">
         <v>0.97</v>
       </c>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="2" t="n">
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="3" t="n">
         <v>105</v>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="K4" s="3" t="n">
         <v>35</v>
       </c>
     </row>
@@ -607,28 +619,28 @@
           <t>inositol</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="3" t="n">
+      <c r="B5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="4" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="4" t="n">
         <v>0.39</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="4" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="2" t="n">
+      <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="3" t="n">
         <v>400</v>
       </c>
-      <c r="K5" s="2" t="n">
+      <c r="K5" s="3" t="n">
         <v>100</v>
       </c>
     </row>
@@ -638,28 +650,28 @@
           <t>early_time_restricted_eating</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="3" t="n">
+      <c r="B6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="4" t="n">
         <v>0.57</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="4" t="n">
         <v>0.3</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="4" t="n">
         <v>1.03</v>
       </c>
-      <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="2" t="n">
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="3" t="n">
         <v>1455</v>
       </c>
-      <c r="K6" s="2" t="n">
+      <c r="K6" s="3" t="n">
         <v>607</v>
       </c>
     </row>
@@ -669,34 +681,34 @@
           <t>soy</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B7" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C7" s="4" t="n">
         <v>0.6</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="4" t="n">
         <v>0.41</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="4" t="n">
         <v>0.89</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="F7" s="4" t="n">
         <v>0.17</v>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="G7" s="4" t="n">
         <v>2.09</v>
       </c>
-      <c r="H7" s="4" t="n">
+      <c r="H7" s="5" t="n">
         <v>78.90000000000001</v>
       </c>
-      <c r="I7" s="5" t="n">
-        <v>0.1010785350953814</v>
-      </c>
-      <c r="J7" s="2" t="n">
+      <c r="I7" s="6" t="n">
+        <v>0.1010785350953813</v>
+      </c>
+      <c r="J7" s="3" t="n">
         <v>85059</v>
       </c>
-      <c r="K7" s="2" t="n">
+      <c r="K7" s="3" t="n">
         <v>5399</v>
       </c>
     </row>
@@ -706,34 +718,34 @@
           <t>green_tea</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B8" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="C8" s="4" t="n">
         <v>0.62</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="4" t="n">
         <v>0.43</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="4" t="n">
         <v>0.89</v>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="F8" s="4" t="n">
         <v>0.2</v>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="G8" s="4" t="n">
         <v>1.92</v>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="H8" s="5" t="n">
         <v>72.7</v>
       </c>
-      <c r="I8" s="5" t="n">
-        <v>0.1767576153047418</v>
-      </c>
-      <c r="J8" s="2" t="n">
+      <c r="I8" s="6" t="n">
+        <v>0.1767576153047416</v>
+      </c>
+      <c r="J8" s="3" t="n">
         <v>99090</v>
       </c>
-      <c r="K8" s="2" t="n">
+      <c r="K8" s="3" t="n">
         <v>1577</v>
       </c>
     </row>
@@ -743,34 +755,34 @@
           <t>insoluble_dietary_fiber_intake</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n">
+      <c r="B9" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="C9" s="4" t="n">
         <v>0.62</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" s="4" t="n">
         <v>0.38</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" s="4" t="n">
         <v>1.03</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="3" t="n">
+      <c r="F9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="n">
         <v>206.11</v>
       </c>
-      <c r="H9" s="4" t="n">
+      <c r="H9" s="5" t="n">
         <v>74.90000000000001</v>
       </c>
-      <c r="I9" s="5" t="n">
+      <c r="I9" s="6" t="n">
         <v>0.1151715356999109</v>
       </c>
-      <c r="J9" s="2" t="n">
+      <c r="J9" s="3" t="n">
         <v>101084</v>
       </c>
-      <c r="K9" s="2" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -778,28 +790,28 @@
           <t>low_fat_diet</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" s="3" t="n">
+      <c r="B10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="4" t="n">
         <v>0.62</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D10" s="4" t="n">
         <v>0.33</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E10" s="4" t="n">
         <v>1.1</v>
       </c>
-      <c r="F10" s="3" t="inlineStr"/>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="2" t="n">
+      <c r="F10" s="4" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr"/>
+      <c r="H10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="6" t="inlineStr"/>
+      <c r="J10" s="3" t="n">
         <v>1170</v>
       </c>
-      <c r="K10" s="2" t="n">
+      <c r="K10" s="3" t="n">
         <v>390</v>
       </c>
     </row>
@@ -809,28 +821,28 @@
           <t>vitamin_k2</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="3" t="n">
+      <c r="B11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="4" t="n">
         <v>0.65</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D11" s="4" t="n">
         <v>0.39</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="E11" s="4" t="n">
         <v>1.06</v>
       </c>
-      <c r="F11" s="3" t="inlineStr"/>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="2" t="n">
+      <c r="F11" s="4" t="inlineStr"/>
+      <c r="G11" s="4" t="inlineStr"/>
+      <c r="H11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="3" t="n">
         <v>11319</v>
       </c>
-      <c r="K11" s="2" t="n">
+      <c r="K11" s="3" t="n">
         <v>268</v>
       </c>
     </row>
@@ -840,34 +852,34 @@
           <t>zeaxanthin</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n">
+      <c r="B12" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="C12" s="4" t="n">
         <v>0.66</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" s="4" t="n">
         <v>0.4</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="E12" s="4" t="n">
         <v>1.08</v>
       </c>
-      <c r="F12" s="3" t="n">
+      <c r="F12" s="4" t="n">
         <v>0.09</v>
       </c>
-      <c r="G12" s="3" t="n">
+      <c r="G12" s="4" t="n">
         <v>4.89</v>
       </c>
-      <c r="H12" s="4" t="n">
+      <c r="H12" s="5" t="n">
         <v>62.9</v>
       </c>
-      <c r="I12" s="5" t="n">
-        <v>0.8236639670954935</v>
-      </c>
-      <c r="J12" s="2" t="n">
+      <c r="I12" s="6" t="n">
+        <v>0.8236639670954942</v>
+      </c>
+      <c r="J12" s="3" t="n">
         <v>2106</v>
       </c>
-      <c r="K12" s="2" t="n">
+      <c r="K12" s="3" t="n">
         <v>808</v>
       </c>
     </row>
@@ -877,28 +889,28 @@
           <t>quercetin</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="3" t="n">
+      <c r="B13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="4" t="n">
         <v>0.67</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" s="4" t="n">
         <v>0.48</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="E13" s="4" t="n">
         <v>0.93</v>
       </c>
-      <c r="F13" s="3" t="inlineStr"/>
-      <c r="G13" s="3" t="inlineStr"/>
-      <c r="H13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="5" t="inlineStr"/>
-      <c r="J13" s="2" t="n">
+      <c r="F13" s="4" t="inlineStr"/>
+      <c r="G13" s="4" t="inlineStr"/>
+      <c r="H13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="6" t="inlineStr"/>
+      <c r="J13" s="3" t="n">
         <v>971</v>
       </c>
-      <c r="K13" s="2" t="n">
+      <c r="K13" s="3" t="n">
         <v>433</v>
       </c>
     </row>
@@ -908,28 +920,28 @@
           <t>vegan_diet</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" s="3" t="n">
+      <c r="B14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="4" t="n">
         <v>0.67</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D14" s="4" t="n">
         <v>0.51</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="E14" s="4" t="n">
         <v>0.86</v>
       </c>
-      <c r="F14" s="3" t="inlineStr"/>
-      <c r="G14" s="3" t="inlineStr"/>
-      <c r="H14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="5" t="inlineStr"/>
-      <c r="J14" s="2" t="n">
+      <c r="F14" s="4" t="inlineStr"/>
+      <c r="G14" s="4" t="inlineStr"/>
+      <c r="H14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="6" t="inlineStr"/>
+      <c r="J14" s="3" t="n">
         <v>26346</v>
       </c>
-      <c r="K14" s="2" t="n">
+      <c r="K14" s="3" t="n">
         <v>1079</v>
       </c>
     </row>
@@ -939,28 +951,28 @@
           <t>pyruvate</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" s="3" t="n">
+      <c r="B15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="4" t="n">
         <v>0.68</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="D15" s="4" t="n">
         <v>0.52</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="E15" s="4" t="n">
         <v>0.9</v>
       </c>
-      <c r="F15" s="3" t="inlineStr"/>
-      <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="5" t="inlineStr"/>
-      <c r="J15" s="2" t="n">
+      <c r="F15" s="4" t="inlineStr"/>
+      <c r="G15" s="4" t="inlineStr"/>
+      <c r="H15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="6" t="inlineStr"/>
+      <c r="J15" s="3" t="n">
         <v>666</v>
       </c>
-      <c r="K15" s="2" t="n">
+      <c r="K15" s="3" t="n">
         <v>333</v>
       </c>
     </row>
@@ -970,34 +982,34 @@
           <t>garlic</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n">
+      <c r="B16" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="C16" s="4" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D16" s="4" t="n">
         <v>0.42</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="E16" s="4" t="n">
         <v>1.13</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="3" t="n">
+      <c r="F16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4" t="n">
         <v>265.07</v>
       </c>
-      <c r="H16" s="4" t="n">
+      <c r="H16" s="5" t="n">
         <v>85</v>
       </c>
-      <c r="I16" s="5" t="n">
+      <c r="I16" s="6" t="n">
         <v>0.2044018200861738</v>
       </c>
-      <c r="J16" s="2" t="n">
+      <c r="J16" s="3" t="n">
         <v>36604</v>
       </c>
-      <c r="K16" s="2" t="n">
+      <c r="K16" s="3" t="n">
         <v>2168</v>
       </c>
     </row>
@@ -1007,28 +1019,28 @@
           <t>vegetarian_diet</t>
         </is>
       </c>
-      <c r="B17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" s="3" t="n">
+      <c r="B17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="4" t="n">
         <v>0.7</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="D17" s="4" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="E17" s="4" t="n">
         <v>0.9</v>
       </c>
-      <c r="F17" s="3" t="inlineStr"/>
-      <c r="G17" s="3" t="inlineStr"/>
-      <c r="H17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="2" t="n">
+      <c r="F17" s="4" t="inlineStr"/>
+      <c r="G17" s="4" t="inlineStr"/>
+      <c r="H17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="6" t="inlineStr"/>
+      <c r="J17" s="3" t="n">
         <v>217937</v>
       </c>
-      <c r="K17" s="2" t="n">
+      <c r="K17" s="3" t="n">
         <v>9501</v>
       </c>
     </row>
@@ -1038,34 +1050,34 @@
           <t>linoleic_acid</t>
         </is>
       </c>
-      <c r="B18" s="2" t="n">
+      <c r="B18" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="C18" s="4" t="n">
         <v>0.71</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="D18" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="E18" s="4" t="n">
         <v>0.99</v>
       </c>
-      <c r="F18" s="3" t="n">
+      <c r="F18" s="4" t="n">
         <v>0.26</v>
       </c>
-      <c r="G18" s="3" t="n">
+      <c r="G18" s="4" t="n">
         <v>1.9</v>
       </c>
-      <c r="H18" s="4" t="n">
+      <c r="H18" s="5" t="n">
         <v>70.5</v>
       </c>
-      <c r="I18" s="5" t="n">
-        <v>0.4789848163683078</v>
-      </c>
-      <c r="J18" s="2" t="n">
+      <c r="I18" s="6" t="n">
+        <v>0.4789848163683069</v>
+      </c>
+      <c r="J18" s="3" t="n">
         <v>8735</v>
       </c>
-      <c r="K18" s="2" t="n">
+      <c r="K18" s="3" t="n">
         <v>3057</v>
       </c>
     </row>
@@ -1075,34 +1087,34 @@
           <t>genistein</t>
         </is>
       </c>
-      <c r="B19" s="2" t="n">
+      <c r="B19" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="C19" s="4" t="n">
         <v>0.72</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="D19" s="4" t="n">
         <v>0.54</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="E19" s="4" t="n">
         <v>0.95</v>
       </c>
-      <c r="F19" s="3" t="n">
+      <c r="F19" s="4" t="n">
         <v>0.31</v>
       </c>
-      <c r="G19" s="3" t="n">
+      <c r="G19" s="4" t="n">
         <v>1.67</v>
       </c>
-      <c r="H19" s="4" t="n">
+      <c r="H19" s="5" t="n">
         <v>67.8</v>
       </c>
-      <c r="I19" s="5" t="n">
-        <v>0.04176805723275333</v>
-      </c>
-      <c r="J19" s="2" t="n">
+      <c r="I19" s="6" t="n">
+        <v>0.04176805723275343</v>
+      </c>
+      <c r="J19" s="3" t="n">
         <v>91302</v>
       </c>
-      <c r="K19" s="2" t="n">
+      <c r="K19" s="3" t="n">
         <v>3818</v>
       </c>
     </row>
@@ -1112,28 +1124,28 @@
           <t>vitamin_k</t>
         </is>
       </c>
-      <c r="B20" s="2" t="n">
+      <c r="B20" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="C20" s="4" t="n">
         <v>0.73</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="D20" s="4" t="n">
         <v>0.58</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="E20" s="4" t="n">
         <v>0.92</v>
       </c>
-      <c r="F20" s="3" t="inlineStr"/>
-      <c r="G20" s="3" t="inlineStr"/>
-      <c r="H20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="5" t="inlineStr"/>
-      <c r="J20" s="2" t="n">
+      <c r="F20" s="4" t="inlineStr"/>
+      <c r="G20" s="4" t="inlineStr"/>
+      <c r="H20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="6" t="inlineStr"/>
+      <c r="J20" s="3" t="n">
         <v>12063</v>
       </c>
-      <c r="K20" s="2" t="n">
+      <c r="K20" s="3" t="n">
         <v>518</v>
       </c>
     </row>
@@ -1143,34 +1155,34 @@
           <t>tomato</t>
         </is>
       </c>
-      <c r="B21" s="2" t="n">
+      <c r="B21" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="C21" s="4" t="n">
         <v>0.74</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="D21" s="4" t="n">
         <v>0.64</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="E21" s="4" t="n">
         <v>0.85</v>
       </c>
-      <c r="F21" s="3" t="n">
+      <c r="F21" s="4" t="n">
         <v>0.47</v>
       </c>
-      <c r="G21" s="3" t="n">
+      <c r="G21" s="4" t="n">
         <v>1.16</v>
       </c>
-      <c r="H21" s="4" t="n">
+      <c r="H21" s="5" t="n">
         <v>78.09999999999999</v>
       </c>
-      <c r="I21" s="5" t="n">
+      <c r="I21" s="6" t="n">
         <v>2.045420729252859e-05</v>
       </c>
-      <c r="J21" s="2" t="n">
+      <c r="J21" s="3" t="n">
         <v>1057923</v>
       </c>
-      <c r="K21" s="2" t="n">
+      <c r="K21" s="3" t="n">
         <v>67108</v>
       </c>
     </row>
@@ -1180,34 +1192,34 @@
           <t>melatonin</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n">
+      <c r="B22" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="C22" s="4" t="n">
         <v>0.75</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="D22" s="4" t="n">
         <v>0.45</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="E22" s="4" t="n">
         <v>1.23</v>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3" t="n">
+      <c r="F22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4" t="n">
         <v>196.29</v>
       </c>
-      <c r="H22" s="4" t="n">
+      <c r="H22" s="5" t="n">
         <v>73</v>
       </c>
-      <c r="I22" s="5" t="n">
+      <c r="I22" s="6" t="n">
         <v>0.0645864721910966</v>
       </c>
-      <c r="J22" s="2" t="n">
+      <c r="J22" s="3" t="n">
         <v>4618</v>
       </c>
-      <c r="K22" s="2" t="n">
+      <c r="K22" s="3" t="n">
         <v>1414</v>
       </c>
     </row>
@@ -1217,34 +1229,34 @@
           <t>tea</t>
         </is>
       </c>
-      <c r="B23" s="2" t="n">
+      <c r="B23" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="C23" s="4" t="n">
         <v>0.75</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="D23" s="4" t="n">
         <v>0.64</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="E23" s="4" t="n">
         <v>0.89</v>
       </c>
-      <c r="F23" s="3" t="n">
+      <c r="F23" s="4" t="n">
         <v>0.45</v>
       </c>
-      <c r="G23" s="3" t="n">
+      <c r="G23" s="4" t="n">
         <v>1.27</v>
       </c>
-      <c r="H23" s="4" t="n">
+      <c r="H23" s="5" t="n">
         <v>84.90000000000001</v>
       </c>
-      <c r="I23" s="5" t="n">
-        <v>0.04996208468350857</v>
-      </c>
-      <c r="J23" s="2" t="n">
+      <c r="I23" s="6" t="n">
+        <v>0.0499620846835085</v>
+      </c>
+      <c r="J23" s="3" t="n">
         <v>314398</v>
       </c>
-      <c r="K23" s="2" t="n">
+      <c r="K23" s="3" t="n">
         <v>15389</v>
       </c>
     </row>
@@ -1254,28 +1266,28 @@
           <t>citrulline</t>
         </is>
       </c>
-      <c r="B24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C24" s="3" t="n">
+      <c r="B24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="4" t="n">
         <v>0.76</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="D24" s="4" t="n">
         <v>0.65</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="E24" s="4" t="n">
         <v>0.88</v>
       </c>
-      <c r="F24" s="3" t="inlineStr"/>
-      <c r="G24" s="3" t="inlineStr"/>
-      <c r="H24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="2" t="n">
+      <c r="F24" s="4" t="inlineStr"/>
+      <c r="G24" s="4" t="inlineStr"/>
+      <c r="H24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="6" t="inlineStr"/>
+      <c r="J24" s="3" t="n">
         <v>2154</v>
       </c>
-      <c r="K24" s="2" t="n">
+      <c r="K24" s="3" t="n">
         <v>1077</v>
       </c>
     </row>
@@ -1285,28 +1297,28 @@
           <t>potassium</t>
         </is>
       </c>
-      <c r="B25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" s="3" t="n">
+      <c r="B25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="4" t="n">
         <v>0.77</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="D25" s="4" t="n">
         <v>0.55</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="E25" s="4" t="n">
         <v>1.08</v>
       </c>
-      <c r="F25" s="3" t="inlineStr"/>
-      <c r="G25" s="3" t="inlineStr"/>
-      <c r="H25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="5" t="inlineStr"/>
-      <c r="J25" s="2" t="n">
+      <c r="F25" s="4" t="inlineStr"/>
+      <c r="G25" s="4" t="inlineStr"/>
+      <c r="H25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="6" t="inlineStr"/>
+      <c r="J25" s="3" t="n">
         <v>656</v>
       </c>
-      <c r="K25" s="2" t="n">
+      <c r="K25" s="3" t="n">
         <v>328</v>
       </c>
     </row>
@@ -1316,34 +1328,34 @@
           <t>selenium</t>
         </is>
       </c>
-      <c r="B26" s="2" t="n">
+      <c r="B26" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="C26" s="4" t="n">
         <v>0.77</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="D26" s="4" t="n">
         <v>0.67</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="E26" s="4" t="n">
         <v>0.89</v>
       </c>
-      <c r="F26" s="3" t="n">
+      <c r="F26" s="4" t="n">
         <v>0.4</v>
       </c>
-      <c r="G26" s="3" t="n">
+      <c r="G26" s="4" t="n">
         <v>1.48</v>
       </c>
-      <c r="H26" s="4" t="n">
+      <c r="H26" s="5" t="n">
         <v>84.90000000000001</v>
       </c>
-      <c r="I26" s="5" t="n">
-        <v>0.0008136772771022832</v>
-      </c>
-      <c r="J26" s="2" t="n">
+      <c r="I26" s="6" t="n">
+        <v>0.0008136772771022829</v>
+      </c>
+      <c r="J26" s="3" t="n">
         <v>382643</v>
       </c>
-      <c r="K26" s="2" t="n">
+      <c r="K26" s="3" t="n">
         <v>29947</v>
       </c>
     </row>
@@ -1353,28 +1365,28 @@
           <t>iodine</t>
         </is>
       </c>
-      <c r="B27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" s="3" t="n">
+      <c r="B27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="4" t="n">
         <v>0.78</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="D27" s="4" t="n">
         <v>0.55</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="E27" s="4" t="n">
         <v>1.09</v>
       </c>
-      <c r="F27" s="3" t="inlineStr"/>
-      <c r="G27" s="3" t="inlineStr"/>
-      <c r="H27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="5" t="inlineStr"/>
-      <c r="J27" s="2" t="n">
+      <c r="F27" s="4" t="inlineStr"/>
+      <c r="G27" s="4" t="inlineStr"/>
+      <c r="H27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="6" t="inlineStr"/>
+      <c r="J27" s="3" t="n">
         <v>656</v>
       </c>
-      <c r="K27" s="2" t="n">
+      <c r="K27" s="3" t="n">
         <v>328</v>
       </c>
     </row>
@@ -1384,28 +1396,28 @@
           <t>time_restricted_eating</t>
         </is>
       </c>
-      <c r="B28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C28" s="3" t="n">
+      <c r="B28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="4" t="n">
         <v>0.79</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="D28" s="4" t="n">
         <v>0.57</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="E28" s="4" t="n">
         <v>1.06</v>
       </c>
-      <c r="F28" s="3" t="inlineStr"/>
-      <c r="G28" s="3" t="inlineStr"/>
-      <c r="H28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="2" t="n">
+      <c r="F28" s="4" t="inlineStr"/>
+      <c r="G28" s="4" t="inlineStr"/>
+      <c r="H28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="6" t="inlineStr"/>
+      <c r="J28" s="3" t="n">
         <v>1455</v>
       </c>
-      <c r="K28" s="2" t="n">
+      <c r="K28" s="3" t="n">
         <v>607</v>
       </c>
     </row>
@@ -1415,28 +1427,28 @@
           <t>oleic_acid</t>
         </is>
       </c>
-      <c r="B29" s="2" t="n">
+      <c r="B29" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="C29" s="4" t="n">
         <v>0.8</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="D29" s="4" t="n">
         <v>0.24</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="E29" s="4" t="n">
         <v>2.64</v>
       </c>
-      <c r="F29" s="3" t="inlineStr"/>
-      <c r="G29" s="3" t="inlineStr"/>
-      <c r="H29" s="4" t="n">
+      <c r="F29" s="4" t="inlineStr"/>
+      <c r="G29" s="4" t="inlineStr"/>
+      <c r="H29" s="5" t="n">
         <v>82</v>
       </c>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="2" t="n">
+      <c r="I29" s="6" t="inlineStr"/>
+      <c r="J29" s="3" t="n">
         <v>58714</v>
       </c>
-      <c r="K29" s="2" t="n">
+      <c r="K29" s="3" t="n">
         <v>851</v>
       </c>
     </row>
@@ -1446,28 +1458,28 @@
           <t>mushrooms</t>
         </is>
       </c>
-      <c r="B30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" s="3" t="n">
+      <c r="B30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="4" t="n">
         <v>0.84</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="D30" s="4" t="n">
         <v>0.71</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="E30" s="4" t="n">
         <v>0.98</v>
       </c>
-      <c r="F30" s="3" t="inlineStr"/>
-      <c r="G30" s="3" t="inlineStr"/>
-      <c r="H30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="2" t="n">
+      <c r="F30" s="4" t="inlineStr"/>
+      <c r="G30" s="4" t="inlineStr"/>
+      <c r="H30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="6" t="inlineStr"/>
+      <c r="J30" s="3" t="n">
         <v>36499</v>
       </c>
-      <c r="K30" s="2" t="n">
+      <c r="K30" s="3" t="n">
         <v>1204</v>
       </c>
     </row>
@@ -1477,34 +1489,34 @@
           <t>lycopene</t>
         </is>
       </c>
-      <c r="B31" s="2" t="n">
+      <c r="B31" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="C31" s="4" t="n">
         <v>0.85</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="D31" s="4" t="n">
         <v>0.78</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="E31" s="4" t="n">
         <v>0.93</v>
       </c>
-      <c r="F31" s="3" t="n">
+      <c r="F31" s="4" t="n">
         <v>0.62</v>
       </c>
-      <c r="G31" s="3" t="n">
+      <c r="G31" s="4" t="n">
         <v>1.15</v>
       </c>
-      <c r="H31" s="4" t="n">
+      <c r="H31" s="5" t="n">
         <v>71.40000000000001</v>
       </c>
-      <c r="I31" s="5" t="n">
-        <v>0.0008787392868700852</v>
-      </c>
-      <c r="J31" s="2" t="n">
+      <c r="I31" s="6" t="n">
+        <v>0.0008787392868700854</v>
+      </c>
+      <c r="J31" s="3" t="n">
         <v>321509</v>
       </c>
-      <c r="K31" s="2" t="n">
+      <c r="K31" s="3" t="n">
         <v>28185</v>
       </c>
     </row>
@@ -1514,34 +1526,34 @@
           <t>vitamin_c</t>
         </is>
       </c>
-      <c r="B32" s="2" t="n">
+      <c r="B32" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="C32" s="4" t="n">
         <v>0.87</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="D32" s="4" t="n">
         <v>0.75</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="E32" s="4" t="n">
         <v>1.03</v>
       </c>
-      <c r="F32" s="3" t="n">
+      <c r="F32" s="4" t="n">
         <v>0.51</v>
       </c>
-      <c r="G32" s="3" t="n">
+      <c r="G32" s="4" t="n">
         <v>1.49</v>
       </c>
-      <c r="H32" s="4" t="n">
+      <c r="H32" s="5" t="n">
         <v>79.09999999999999</v>
       </c>
-      <c r="I32" s="5" t="n">
-        <v>0.926485914172831</v>
-      </c>
-      <c r="J32" s="2" t="n">
+      <c r="I32" s="6" t="n">
+        <v>0.9264859141728312</v>
+      </c>
+      <c r="J32" s="3" t="n">
         <v>68944</v>
       </c>
-      <c r="K32" s="2" t="n">
+      <c r="K32" s="3" t="n">
         <v>7699</v>
       </c>
     </row>
@@ -1551,28 +1563,28 @@
           <t>fish_oil</t>
         </is>
       </c>
-      <c r="B33" s="2" t="n">
+      <c r="B33" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="C33" s="4" t="n">
         <v>0.89</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="D33" s="4" t="n">
         <v>0.68</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="E33" s="4" t="n">
         <v>1.17</v>
       </c>
-      <c r="F33" s="3" t="inlineStr"/>
-      <c r="G33" s="3" t="inlineStr"/>
-      <c r="H33" s="4" t="n">
+      <c r="F33" s="4" t="inlineStr"/>
+      <c r="G33" s="4" t="inlineStr"/>
+      <c r="H33" s="5" t="n">
         <v>47.9</v>
       </c>
-      <c r="I33" s="5" t="inlineStr"/>
-      <c r="J33" s="2" t="n">
+      <c r="I33" s="6" t="inlineStr"/>
+      <c r="J33" s="3" t="n">
         <v>37289</v>
       </c>
-      <c r="K33" s="2" t="n">
+      <c r="K33" s="3" t="n">
         <v>1735</v>
       </c>
     </row>
@@ -1582,34 +1594,34 @@
           <t>legumes</t>
         </is>
       </c>
-      <c r="B34" s="2" t="n">
+      <c r="B34" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="C34" s="4" t="n">
         <v>0.89</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="D34" s="4" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="E34" s="4" t="n">
         <v>0.97</v>
       </c>
-      <c r="F34" s="3" t="n">
+      <c r="F34" s="4" t="n">
         <v>0.7</v>
       </c>
-      <c r="G34" s="3" t="n">
+      <c r="G34" s="4" t="n">
         <v>1.12</v>
       </c>
-      <c r="H34" s="4" t="n">
+      <c r="H34" s="5" t="n">
         <v>62.4</v>
       </c>
-      <c r="I34" s="5" t="n">
-        <v>0.00617043000892098</v>
-      </c>
-      <c r="J34" s="2" t="n">
+      <c r="I34" s="6" t="n">
+        <v>0.006170430008920973</v>
+      </c>
+      <c r="J34" s="3" t="n">
         <v>1155076</v>
       </c>
-      <c r="K34" s="2" t="n">
+      <c r="K34" s="3" t="n">
         <v>79072</v>
       </c>
     </row>
@@ -1619,34 +1631,34 @@
           <t>soluble_dietary_fiber_intake</t>
         </is>
       </c>
-      <c r="B35" s="2" t="n">
+      <c r="B35" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="C35" s="4" t="n">
         <v>0.89</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="D35" s="4" t="n">
         <v>0.83</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="E35" s="4" t="n">
         <v>0.96</v>
       </c>
-      <c r="F35" s="3" t="n">
+      <c r="F35" s="4" t="n">
         <v>0.57</v>
       </c>
-      <c r="G35" s="3" t="n">
+      <c r="G35" s="4" t="n">
         <v>1.39</v>
       </c>
-      <c r="H35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" s="5" t="n">
-        <v>0.1883996373295245</v>
-      </c>
-      <c r="J35" s="2" t="n">
+      <c r="H35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="6" t="n">
+        <v>0.188399637329524</v>
+      </c>
+      <c r="J35" s="3" t="n">
         <v>80888</v>
       </c>
-      <c r="K35" s="2" t="n">
+      <c r="K35" s="3" t="n">
         <v>10851</v>
       </c>
     </row>
@@ -1656,34 +1668,34 @@
           <t>vitamin_b6</t>
         </is>
       </c>
-      <c r="B36" s="2" t="n">
+      <c r="B36" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="C36" s="4" t="n">
         <v>0.89</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="D36" s="4" t="n">
         <v>0.83</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="E36" s="4" t="n">
         <v>0.96</v>
       </c>
-      <c r="F36" s="3" t="n">
+      <c r="F36" s="4" t="n">
         <v>0.57</v>
       </c>
-      <c r="G36" s="3" t="n">
+      <c r="G36" s="4" t="n">
         <v>1.41</v>
       </c>
-      <c r="H36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" s="5" t="n">
-        <v>0.2443574036478494</v>
-      </c>
-      <c r="J36" s="2" t="n">
+      <c r="H36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="6" t="n">
+        <v>0.2443574036478493</v>
+      </c>
+      <c r="J36" s="3" t="n">
         <v>70879</v>
       </c>
-      <c r="K36" s="2" t="n">
+      <c r="K36" s="3" t="n">
         <v>7656</v>
       </c>
     </row>
@@ -1693,28 +1705,28 @@
           <t>plant_based_diet</t>
         </is>
       </c>
-      <c r="B37" s="2" t="n">
+      <c r="B37" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="C37" s="4" t="n">
         <v>0.91</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="D37" s="4" t="n">
         <v>0.84</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="E37" s="4" t="n">
         <v>0.99</v>
       </c>
-      <c r="F37" s="3" t="inlineStr"/>
-      <c r="G37" s="3" t="inlineStr"/>
-      <c r="H37" s="4" t="n">
+      <c r="F37" s="4" t="inlineStr"/>
+      <c r="G37" s="4" t="inlineStr"/>
+      <c r="H37" s="5" t="n">
         <v>39.5</v>
       </c>
-      <c r="I37" s="5" t="inlineStr"/>
-      <c r="J37" s="2" t="n">
+      <c r="I37" s="6" t="inlineStr"/>
+      <c r="J37" s="3" t="n">
         <v>211318</v>
       </c>
-      <c r="K37" s="2" t="n">
+      <c r="K37" s="3" t="n">
         <v>24516</v>
       </c>
     </row>
@@ -1724,34 +1736,34 @@
           <t>beta_carotene</t>
         </is>
       </c>
-      <c r="B38" s="2" t="n">
+      <c r="B38" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="C38" s="4" t="n">
         <v>0.92</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="D38" s="4" t="n">
         <v>0.76</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="E38" s="4" t="n">
         <v>1.11</v>
       </c>
-      <c r="F38" s="3" t="n">
+      <c r="F38" s="4" t="n">
         <v>0.49</v>
       </c>
-      <c r="G38" s="3" t="n">
+      <c r="G38" s="4" t="n">
         <v>1.73</v>
       </c>
-      <c r="H38" s="4" t="n">
+      <c r="H38" s="5" t="n">
         <v>76</v>
       </c>
-      <c r="I38" s="5" t="n">
-        <v>0.3752413276948279</v>
-      </c>
-      <c r="J38" s="2" t="n">
+      <c r="I38" s="6" t="n">
+        <v>0.375241327694828</v>
+      </c>
+      <c r="J38" s="3" t="n">
         <v>122141</v>
       </c>
-      <c r="K38" s="2" t="inlineStr"/>
+      <c r="K38" s="3" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1759,28 +1771,28 @@
           <t>caffeine</t>
         </is>
       </c>
-      <c r="B39" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C39" s="3" t="n">
+      <c r="B39" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" s="4" t="n">
         <v>0.92</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="D39" s="4" t="n">
         <v>0.84</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="E39" s="4" t="n">
         <v>1.02</v>
       </c>
-      <c r="F39" s="3" t="inlineStr"/>
-      <c r="G39" s="3" t="inlineStr"/>
-      <c r="H39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="5" t="inlineStr"/>
-      <c r="J39" s="2" t="n">
+      <c r="F39" s="4" t="inlineStr"/>
+      <c r="G39" s="4" t="inlineStr"/>
+      <c r="H39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="6" t="inlineStr"/>
+      <c r="J39" s="3" t="n">
         <v>46667</v>
       </c>
-      <c r="K39" s="2" t="n">
+      <c r="K39" s="3" t="n">
         <v>3037</v>
       </c>
     </row>
@@ -1790,28 +1802,28 @@
           <t>ginseng</t>
         </is>
       </c>
-      <c r="B40" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" s="3" t="n">
+      <c r="B40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" s="4" t="n">
         <v>0.92</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="D40" s="4" t="n">
         <v>0.72</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="E40" s="4" t="n">
         <v>1.15</v>
       </c>
-      <c r="F40" s="3" t="inlineStr"/>
-      <c r="G40" s="3" t="inlineStr"/>
-      <c r="H40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" s="5" t="inlineStr"/>
-      <c r="J40" s="2" t="n">
+      <c r="F40" s="4" t="inlineStr"/>
+      <c r="G40" s="4" t="inlineStr"/>
+      <c r="H40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="6" t="inlineStr"/>
+      <c r="J40" s="3" t="n">
         <v>35239</v>
       </c>
-      <c r="K40" s="2" t="n">
+      <c r="K40" s="3" t="n">
         <v>1602</v>
       </c>
     </row>
@@ -1821,34 +1833,34 @@
           <t>total_dietary_fiber_intake</t>
         </is>
       </c>
-      <c r="B41" s="2" t="n">
+      <c r="B41" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="C41" s="4" t="n">
         <v>0.92</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="D41" s="4" t="n">
         <v>0.86</v>
       </c>
-      <c r="E41" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" s="3" t="n">
+      <c r="E41" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="4" t="n">
         <v>0.77</v>
       </c>
-      <c r="G41" s="3" t="n">
+      <c r="G41" s="4" t="n">
         <v>1.1</v>
       </c>
-      <c r="H41" s="4" t="n">
+      <c r="H41" s="5" t="n">
         <v>42.9</v>
       </c>
-      <c r="I41" s="5" t="n">
-        <v>0.0774427637971946</v>
-      </c>
-      <c r="J41" s="2" t="n">
+      <c r="I41" s="6" t="n">
+        <v>0.07744276379719461</v>
+      </c>
+      <c r="J41" s="3" t="n">
         <v>972077</v>
       </c>
-      <c r="K41" s="2" t="n">
+      <c r="K41" s="3" t="n">
         <v>64899</v>
       </c>
     </row>
@@ -1858,28 +1870,28 @@
           <t>dash_diet</t>
         </is>
       </c>
-      <c r="B42" s="2" t="n">
+      <c r="B42" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="C42" s="4" t="n">
         <v>0.93</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="D42" s="4" t="n">
         <v>0.82</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="E42" s="4" t="n">
         <v>1.06</v>
       </c>
-      <c r="F42" s="3" t="inlineStr"/>
-      <c r="G42" s="3" t="inlineStr"/>
-      <c r="H42" s="4" t="n">
+      <c r="F42" s="4" t="inlineStr"/>
+      <c r="G42" s="4" t="inlineStr"/>
+      <c r="H42" s="5" t="n">
         <v>73.90000000000001</v>
       </c>
-      <c r="I42" s="5" t="inlineStr"/>
-      <c r="J42" s="2" t="n">
+      <c r="I42" s="6" t="inlineStr"/>
+      <c r="J42" s="3" t="n">
         <v>152714</v>
       </c>
-      <c r="K42" s="2" t="inlineStr"/>
+      <c r="K42" s="3" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1887,28 +1899,28 @@
           <t>ginkgo_biloba</t>
         </is>
       </c>
-      <c r="B43" s="2" t="n">
+      <c r="B43" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="C43" s="4" t="n">
         <v>0.93</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="D43" s="4" t="n">
         <v>0.68</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="E43" s="4" t="n">
         <v>1.27</v>
       </c>
-      <c r="F43" s="3" t="inlineStr"/>
-      <c r="G43" s="3" t="inlineStr"/>
-      <c r="H43" s="4" t="n">
+      <c r="F43" s="4" t="inlineStr"/>
+      <c r="G43" s="4" t="inlineStr"/>
+      <c r="H43" s="5" t="n">
         <v>46.8</v>
       </c>
-      <c r="I43" s="5" t="inlineStr"/>
-      <c r="J43" s="2" t="n">
+      <c r="I43" s="6" t="inlineStr"/>
+      <c r="J43" s="3" t="n">
         <v>38308</v>
       </c>
-      <c r="K43" s="2" t="n">
+      <c r="K43" s="3" t="n">
         <v>1665</v>
       </c>
     </row>
@@ -1918,34 +1930,34 @@
           <t>docosahexaenoic_acid</t>
         </is>
       </c>
-      <c r="B44" s="2" t="n">
+      <c r="B44" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="C44" s="4" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="D44" s="4" t="n">
         <v>0.74</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="E44" s="4" t="n">
         <v>1.2</v>
       </c>
-      <c r="F44" s="3" t="n">
+      <c r="F44" s="4" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="G44" s="3" t="n">
+      <c r="G44" s="4" t="n">
         <v>12.3</v>
       </c>
-      <c r="H44" s="4" t="n">
+      <c r="H44" s="5" t="n">
         <v>55.4</v>
       </c>
-      <c r="I44" s="5" t="n">
+      <c r="I44" s="6" t="n">
         <v>0.6285558694668995</v>
       </c>
-      <c r="J44" s="2" t="n">
+      <c r="J44" s="3" t="n">
         <v>144141</v>
       </c>
-      <c r="K44" s="2" t="n">
+      <c r="K44" s="3" t="n">
         <v>7729</v>
       </c>
     </row>
@@ -1955,34 +1967,34 @@
           <t>vitamin_e</t>
         </is>
       </c>
-      <c r="B45" s="2" t="n">
+      <c r="B45" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="C45" s="4" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="D45" s="4" t="n">
         <v>0.87</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="E45" s="4" t="n">
         <v>1.02</v>
       </c>
-      <c r="F45" s="3" t="n">
+      <c r="F45" s="4" t="n">
         <v>0.67</v>
       </c>
-      <c r="G45" s="3" t="n">
+      <c r="G45" s="4" t="n">
         <v>1.32</v>
       </c>
-      <c r="H45" s="4" t="n">
+      <c r="H45" s="5" t="n">
         <v>75.90000000000001</v>
       </c>
-      <c r="I45" s="5" t="n">
+      <c r="I45" s="6" t="n">
         <v>0.1015950190265765</v>
       </c>
-      <c r="J45" s="2" t="n">
+      <c r="J45" s="3" t="n">
         <v>404649</v>
       </c>
-      <c r="K45" s="2" t="n">
+      <c r="K45" s="3" t="n">
         <v>36660</v>
       </c>
     </row>
@@ -1992,28 +2004,28 @@
           <t>omega_6_fatty_acids</t>
         </is>
       </c>
-      <c r="B46" s="2" t="n">
+      <c r="B46" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="C46" s="4" t="n">
         <v>0.96</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="D46" s="4" t="n">
         <v>0.79</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="E46" s="4" t="n">
         <v>1.17</v>
       </c>
-      <c r="F46" s="3" t="inlineStr"/>
-      <c r="G46" s="3" t="inlineStr"/>
-      <c r="H46" s="4" t="n">
+      <c r="F46" s="4" t="inlineStr"/>
+      <c r="G46" s="4" t="inlineStr"/>
+      <c r="H46" s="5" t="n">
         <v>40.4</v>
       </c>
-      <c r="I46" s="5" t="inlineStr"/>
-      <c r="J46" s="2" t="n">
+      <c r="I46" s="6" t="inlineStr"/>
+      <c r="J46" s="3" t="n">
         <v>254243</v>
       </c>
-      <c r="K46" s="2" t="n">
+      <c r="K46" s="3" t="n">
         <v>1931</v>
       </c>
     </row>
@@ -2023,28 +2035,28 @@
           <t>plant_protein_intake</t>
         </is>
       </c>
-      <c r="B47" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C47" s="3" t="n">
+      <c r="B47" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" s="4" t="n">
         <v>0.98</v>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="D47" s="4" t="n">
         <v>0.93</v>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="E47" s="4" t="n">
         <v>1.05</v>
       </c>
-      <c r="F47" s="3" t="inlineStr"/>
-      <c r="G47" s="3" t="inlineStr"/>
-      <c r="H47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" s="5" t="inlineStr"/>
-      <c r="J47" s="2" t="n">
+      <c r="F47" s="4" t="inlineStr"/>
+      <c r="G47" s="4" t="inlineStr"/>
+      <c r="H47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="6" t="inlineStr"/>
+      <c r="J47" s="3" t="n">
         <v>150671</v>
       </c>
-      <c r="K47" s="2" t="n">
+      <c r="K47" s="3" t="n">
         <v>14238</v>
       </c>
     </row>
@@ -2054,28 +2066,28 @@
           <t>animal_protein_intake</t>
         </is>
       </c>
-      <c r="B48" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C48" s="3" t="n">
+      <c r="B48" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" s="4" t="n">
         <v>0.99</v>
       </c>
-      <c r="D48" s="3" t="n">
+      <c r="D48" s="4" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="E48" s="3" t="n">
+      <c r="E48" s="4" t="n">
         <v>1.03</v>
       </c>
-      <c r="F48" s="3" t="inlineStr"/>
-      <c r="G48" s="3" t="inlineStr"/>
-      <c r="H48" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" s="5" t="inlineStr"/>
-      <c r="J48" s="2" t="n">
+      <c r="F48" s="4" t="inlineStr"/>
+      <c r="G48" s="4" t="inlineStr"/>
+      <c r="H48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="6" t="inlineStr"/>
+      <c r="J48" s="3" t="n">
         <v>159482</v>
       </c>
-      <c r="K48" s="2" t="n">
+      <c r="K48" s="3" t="n">
         <v>17349</v>
       </c>
     </row>
@@ -2085,28 +2097,28 @@
           <t>dietary_protein_intake</t>
         </is>
       </c>
-      <c r="B49" s="2" t="n">
+      <c r="B49" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C49" s="3" t="n">
+      <c r="C49" s="4" t="n">
         <v>0.99</v>
       </c>
-      <c r="D49" s="3" t="n">
+      <c r="D49" s="4" t="n">
         <v>0.89</v>
       </c>
-      <c r="E49" s="3" t="n">
+      <c r="E49" s="4" t="n">
         <v>1.11</v>
       </c>
-      <c r="F49" s="3" t="inlineStr"/>
-      <c r="G49" s="3" t="inlineStr"/>
-      <c r="H49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" s="5" t="inlineStr"/>
-      <c r="J49" s="2" t="n">
+      <c r="F49" s="4" t="inlineStr"/>
+      <c r="G49" s="4" t="inlineStr"/>
+      <c r="H49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="6" t="inlineStr"/>
+      <c r="J49" s="3" t="n">
         <v>109557</v>
       </c>
-      <c r="K49" s="2" t="n">
+      <c r="K49" s="3" t="n">
         <v>3064</v>
       </c>
     </row>
@@ -2116,34 +2128,34 @@
           <t>eggs</t>
         </is>
       </c>
-      <c r="B50" s="2" t="n">
+      <c r="B50" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C50" s="3" t="n">
+      <c r="C50" s="4" t="n">
         <v>0.99</v>
       </c>
-      <c r="D50" s="3" t="n">
+      <c r="D50" s="4" t="n">
         <v>0.96</v>
       </c>
-      <c r="E50" s="3" t="n">
+      <c r="E50" s="4" t="n">
         <v>1.02</v>
       </c>
-      <c r="F50" s="3" t="n">
+      <c r="F50" s="4" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="G50" s="3" t="n">
+      <c r="G50" s="4" t="n">
         <v>1.2</v>
       </c>
-      <c r="H50" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" s="5" t="n">
+      <c r="H50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="6" t="n">
         <v>0.8121269612161565</v>
       </c>
-      <c r="J50" s="2" t="n">
+      <c r="J50" s="3" t="n">
         <v>900752</v>
       </c>
-      <c r="K50" s="2" t="n">
+      <c r="K50" s="3" t="n">
         <v>53381</v>
       </c>
     </row>
@@ -2153,34 +2165,34 @@
           <t>eicosapentaenoic_acid</t>
         </is>
       </c>
-      <c r="B51" s="2" t="n">
+      <c r="B51" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C51" s="3" t="n">
+      <c r="C51" s="4" t="n">
         <v>0.99</v>
       </c>
-      <c r="D51" s="3" t="n">
+      <c r="D51" s="4" t="n">
         <v>0.89</v>
       </c>
-      <c r="E51" s="3" t="n">
+      <c r="E51" s="4" t="n">
         <v>1.11</v>
       </c>
-      <c r="F51" s="3" t="n">
+      <c r="F51" s="4" t="n">
         <v>0.7</v>
       </c>
-      <c r="G51" s="3" t="n">
+      <c r="G51" s="4" t="n">
         <v>1.4</v>
       </c>
-      <c r="H51" s="4" t="n">
+      <c r="H51" s="5" t="n">
         <v>65.2</v>
       </c>
-      <c r="I51" s="5" t="n">
-        <v>0.5746798036256719</v>
-      </c>
-      <c r="J51" s="2" t="n">
+      <c r="I51" s="6" t="n">
+        <v>0.5746798036256722</v>
+      </c>
+      <c r="J51" s="3" t="n">
         <v>444156</v>
       </c>
-      <c r="K51" s="2" t="n">
+      <c r="K51" s="3" t="n">
         <v>13552</v>
       </c>
     </row>
@@ -2190,28 +2202,28 @@
           <t>docosapentaenoic_acid_omega_3</t>
         </is>
       </c>
-      <c r="B52" s="2" t="n">
+      <c r="B52" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C52" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D52" s="3" t="n">
+      <c r="C52" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" s="4" t="n">
         <v>0.97</v>
       </c>
-      <c r="E52" s="3" t="n">
+      <c r="E52" s="4" t="n">
         <v>1.03</v>
       </c>
-      <c r="F52" s="3" t="inlineStr"/>
-      <c r="G52" s="3" t="inlineStr"/>
-      <c r="H52" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" s="5" t="inlineStr"/>
-      <c r="J52" s="2" t="n">
+      <c r="F52" s="4" t="inlineStr"/>
+      <c r="G52" s="4" t="inlineStr"/>
+      <c r="H52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="6" t="inlineStr"/>
+      <c r="J52" s="3" t="n">
         <v>143344</v>
       </c>
-      <c r="K52" s="2" t="n">
+      <c r="K52" s="3" t="n">
         <v>7412</v>
       </c>
     </row>
@@ -2221,34 +2233,34 @@
           <t>lutein</t>
         </is>
       </c>
-      <c r="B53" s="2" t="n">
+      <c r="B53" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C53" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D53" s="3" t="n">
+      <c r="C53" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" s="4" t="n">
         <v>0.63</v>
       </c>
-      <c r="E53" s="3" t="n">
+      <c r="E53" s="4" t="n">
         <v>1.61</v>
       </c>
-      <c r="F53" s="3" t="n">
+      <c r="F53" s="4" t="n">
         <v>0.18</v>
       </c>
-      <c r="G53" s="3" t="n">
+      <c r="G53" s="4" t="n">
         <v>5.71</v>
       </c>
-      <c r="H53" s="4" t="n">
+      <c r="H53" s="5" t="n">
         <v>84.2</v>
       </c>
-      <c r="I53" s="5" t="n">
-        <v>0.9535391069907844</v>
-      </c>
-      <c r="J53" s="2" t="n">
+      <c r="I53" s="6" t="n">
+        <v>0.9535391069907841</v>
+      </c>
+      <c r="J53" s="3" t="n">
         <v>3128</v>
       </c>
-      <c r="K53" s="2" t="n">
+      <c r="K53" s="3" t="n">
         <v>1292</v>
       </c>
     </row>
@@ -2258,28 +2270,28 @@
           <t>mediterranean_diet</t>
         </is>
       </c>
-      <c r="B54" s="2" t="n">
+      <c r="B54" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C54" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D54" s="3" t="n">
+      <c r="C54" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" s="4" t="n">
         <v>0.9</v>
       </c>
-      <c r="E54" s="3" t="n">
+      <c r="E54" s="4" t="n">
         <v>1.11</v>
       </c>
-      <c r="F54" s="3" t="inlineStr"/>
-      <c r="G54" s="3" t="inlineStr"/>
-      <c r="H54" s="4" t="n">
+      <c r="F54" s="4" t="inlineStr"/>
+      <c r="G54" s="4" t="inlineStr"/>
+      <c r="H54" s="5" t="n">
         <v>69.5</v>
       </c>
-      <c r="I54" s="5" t="inlineStr"/>
-      <c r="J54" s="2" t="n">
+      <c r="I54" s="6" t="inlineStr"/>
+      <c r="J54" s="3" t="n">
         <v>106146</v>
       </c>
-      <c r="K54" s="2" t="n">
+      <c r="K54" s="3" t="n">
         <v>7476</v>
       </c>
     </row>
@@ -2289,28 +2301,28 @@
           <t>gondoic_acid</t>
         </is>
       </c>
-      <c r="B55" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C55" s="3" t="n">
+      <c r="B55" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" s="4" t="n">
         <v>1.01</v>
       </c>
-      <c r="D55" s="3" t="n">
+      <c r="D55" s="4" t="n">
         <v>0.98</v>
       </c>
-      <c r="E55" s="3" t="n">
+      <c r="E55" s="4" t="n">
         <v>1.03</v>
       </c>
-      <c r="F55" s="3" t="inlineStr"/>
-      <c r="G55" s="3" t="inlineStr"/>
-      <c r="H55" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" s="5" t="inlineStr"/>
-      <c r="J55" s="2" t="n">
+      <c r="F55" s="4" t="inlineStr"/>
+      <c r="G55" s="4" t="inlineStr"/>
+      <c r="H55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="6" t="inlineStr"/>
+      <c r="J55" s="3" t="n">
         <v>142239</v>
       </c>
-      <c r="K55" s="2" t="n">
+      <c r="K55" s="3" t="n">
         <v>7036</v>
       </c>
     </row>
@@ -2320,34 +2332,34 @@
           <t>folic_acid</t>
         </is>
       </c>
-      <c r="B56" s="2" t="n">
+      <c r="B56" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="C56" s="3" t="n">
+      <c r="C56" s="4" t="n">
         <v>1.02</v>
       </c>
-      <c r="D56" s="3" t="n">
+      <c r="D56" s="4" t="n">
         <v>0.95</v>
       </c>
-      <c r="E56" s="3" t="n">
+      <c r="E56" s="4" t="n">
         <v>1.1</v>
       </c>
-      <c r="F56" s="3" t="n">
+      <c r="F56" s="4" t="n">
         <v>0.83</v>
       </c>
-      <c r="G56" s="3" t="n">
+      <c r="G56" s="4" t="n">
         <v>1.25</v>
       </c>
-      <c r="H56" s="4" t="n">
+      <c r="H56" s="5" t="n">
         <v>49</v>
       </c>
-      <c r="I56" s="5" t="n">
+      <c r="I56" s="6" t="n">
         <v>0.09195795349035596</v>
       </c>
-      <c r="J56" s="2" t="n">
+      <c r="J56" s="3" t="n">
         <v>157607</v>
       </c>
-      <c r="K56" s="2" t="inlineStr"/>
+      <c r="K56" s="3" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2355,34 +2367,34 @@
           <t>multivitamin</t>
         </is>
       </c>
-      <c r="B57" s="2" t="n">
+      <c r="B57" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C57" s="3" t="n">
+      <c r="C57" s="4" t="n">
         <v>1.02</v>
       </c>
-      <c r="D57" s="3" t="n">
+      <c r="D57" s="4" t="n">
         <v>0.96</v>
       </c>
-      <c r="E57" s="3" t="n">
+      <c r="E57" s="4" t="n">
         <v>1.09</v>
       </c>
-      <c r="F57" s="3" t="n">
+      <c r="F57" s="4" t="n">
         <v>0.9</v>
       </c>
-      <c r="G57" s="3" t="n">
+      <c r="G57" s="4" t="n">
         <v>1.17</v>
       </c>
-      <c r="H57" s="4" t="n">
+      <c r="H57" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="I57" s="5" t="n">
+      <c r="I57" s="6" t="n">
         <v>0.2764130406639589</v>
       </c>
-      <c r="J57" s="2" t="n">
+      <c r="J57" s="3" t="n">
         <v>397821</v>
       </c>
-      <c r="K57" s="2" t="n">
+      <c r="K57" s="3" t="n">
         <v>7673</v>
       </c>
     </row>
@@ -2392,34 +2404,34 @@
           <t>ultra_processed_food_intake</t>
         </is>
       </c>
-      <c r="B58" s="2" t="n">
+      <c r="B58" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C58" s="3" t="n">
+      <c r="C58" s="4" t="n">
         <v>1.02</v>
       </c>
-      <c r="D58" s="3" t="n">
+      <c r="D58" s="4" t="n">
         <v>0.95</v>
       </c>
-      <c r="E58" s="3" t="n">
+      <c r="E58" s="4" t="n">
         <v>1.1</v>
       </c>
-      <c r="F58" s="3" t="n">
+      <c r="F58" s="4" t="n">
         <v>0.86</v>
       </c>
-      <c r="G58" s="3" t="n">
+      <c r="G58" s="4" t="n">
         <v>1.22</v>
       </c>
-      <c r="H58" s="4" t="n">
+      <c r="H58" s="5" t="n">
         <v>38.1</v>
       </c>
-      <c r="I58" s="5" t="n">
-        <v>0.4142673366090832</v>
-      </c>
-      <c r="J58" s="2" t="n">
+      <c r="I58" s="6" t="n">
+        <v>0.4142673366090839</v>
+      </c>
+      <c r="J58" s="3" t="n">
         <v>248736</v>
       </c>
-      <c r="K58" s="2" t="n">
+      <c r="K58" s="3" t="n">
         <v>13760</v>
       </c>
     </row>
@@ -2429,28 +2441,28 @@
           <t>vitamin_k1</t>
         </is>
       </c>
-      <c r="B59" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C59" s="3" t="n">
+      <c r="B59" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" s="4" t="n">
         <v>1.02</v>
       </c>
-      <c r="D59" s="3" t="n">
+      <c r="D59" s="4" t="n">
         <v>0.7</v>
       </c>
-      <c r="E59" s="3" t="n">
+      <c r="E59" s="4" t="n">
         <v>1.48</v>
       </c>
-      <c r="F59" s="3" t="inlineStr"/>
-      <c r="G59" s="3" t="inlineStr"/>
-      <c r="H59" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" s="5" t="inlineStr"/>
-      <c r="J59" s="2" t="n">
+      <c r="F59" s="4" t="inlineStr"/>
+      <c r="G59" s="4" t="inlineStr"/>
+      <c r="H59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="6" t="inlineStr"/>
+      <c r="J59" s="3" t="n">
         <v>11319</v>
       </c>
-      <c r="K59" s="2" t="n">
+      <c r="K59" s="3" t="n">
         <v>268</v>
       </c>
     </row>
@@ -2460,34 +2472,34 @@
           <t>omega_3_fatty_acids</t>
         </is>
       </c>
-      <c r="B60" s="2" t="n">
+      <c r="B60" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="C60" s="3" t="n">
+      <c r="C60" s="4" t="n">
         <v>1.03</v>
       </c>
-      <c r="D60" s="3" t="n">
+      <c r="D60" s="4" t="n">
         <v>0.95</v>
       </c>
-      <c r="E60" s="3" t="n">
+      <c r="E60" s="4" t="n">
         <v>1.11</v>
       </c>
-      <c r="F60" s="3" t="n">
+      <c r="F60" s="4" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="G60" s="3" t="n">
+      <c r="G60" s="4" t="n">
         <v>1.3</v>
       </c>
-      <c r="H60" s="4" t="n">
+      <c r="H60" s="5" t="n">
         <v>75.59999999999999</v>
       </c>
-      <c r="I60" s="5" t="n">
+      <c r="I60" s="6" t="n">
         <v>0.8028884184138012</v>
       </c>
-      <c r="J60" s="2" t="n">
+      <c r="J60" s="3" t="n">
         <v>435151</v>
       </c>
-      <c r="K60" s="2" t="n">
+      <c r="K60" s="3" t="n">
         <v>22287</v>
       </c>
     </row>
@@ -2497,28 +2509,28 @@
           <t>saw_palmetto</t>
         </is>
       </c>
-      <c r="B61" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C61" s="3" t="n">
+      <c r="B61" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" s="4" t="n">
         <v>1.03</v>
       </c>
-      <c r="D61" s="3" t="n">
+      <c r="D61" s="4" t="n">
         <v>0.9</v>
       </c>
-      <c r="E61" s="3" t="n">
+      <c r="E61" s="4" t="n">
         <v>1.19</v>
       </c>
-      <c r="F61" s="3" t="inlineStr"/>
-      <c r="G61" s="3" t="inlineStr"/>
-      <c r="H61" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" s="5" t="inlineStr"/>
-      <c r="J61" s="2" t="n">
+      <c r="F61" s="4" t="inlineStr"/>
+      <c r="G61" s="4" t="inlineStr"/>
+      <c r="H61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="6" t="inlineStr"/>
+      <c r="J61" s="3" t="n">
         <v>35239</v>
       </c>
-      <c r="K61" s="2" t="n">
+      <c r="K61" s="3" t="n">
         <v>1602</v>
       </c>
     </row>
@@ -2528,28 +2540,28 @@
           <t>chondroitin</t>
         </is>
       </c>
-      <c r="B62" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C62" s="3" t="n">
+      <c r="B62" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" s="4" t="n">
         <v>1.05</v>
       </c>
-      <c r="D62" s="3" t="n">
+      <c r="D62" s="4" t="n">
         <v>0.9</v>
       </c>
-      <c r="E62" s="3" t="n">
+      <c r="E62" s="4" t="n">
         <v>1.21</v>
       </c>
-      <c r="F62" s="3" t="inlineStr"/>
-      <c r="G62" s="3" t="inlineStr"/>
-      <c r="H62" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" s="5" t="inlineStr"/>
-      <c r="J62" s="2" t="n">
+      <c r="F62" s="4" t="inlineStr"/>
+      <c r="G62" s="4" t="inlineStr"/>
+      <c r="H62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="6" t="inlineStr"/>
+      <c r="J62" s="3" t="n">
         <v>35239</v>
       </c>
-      <c r="K62" s="2" t="n">
+      <c r="K62" s="3" t="n">
         <v>1602</v>
       </c>
     </row>
@@ -2559,28 +2571,28 @@
           <t>copper</t>
         </is>
       </c>
-      <c r="B63" s="2" t="n">
+      <c r="B63" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C63" s="3" t="n">
+      <c r="C63" s="4" t="n">
         <v>1.05</v>
       </c>
-      <c r="D63" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E63" s="3" t="n">
+      <c r="D63" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" s="4" t="n">
         <v>1.11</v>
       </c>
-      <c r="F63" s="3" t="inlineStr"/>
-      <c r="G63" s="3" t="inlineStr"/>
-      <c r="H63" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" s="5" t="inlineStr"/>
-      <c r="J63" s="2" t="n">
+      <c r="F63" s="4" t="inlineStr"/>
+      <c r="G63" s="4" t="inlineStr"/>
+      <c r="H63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="6" t="inlineStr"/>
+      <c r="J63" s="3" t="n">
         <v>43360</v>
       </c>
-      <c r="K63" s="2" t="n">
+      <c r="K63" s="3" t="n">
         <v>6174</v>
       </c>
     </row>
@@ -2590,34 +2602,34 @@
           <t>iron</t>
         </is>
       </c>
-      <c r="B64" s="2" t="n">
+      <c r="B64" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C64" s="3" t="n">
+      <c r="C64" s="4" t="n">
         <v>1.05</v>
       </c>
-      <c r="D64" s="3" t="n">
+      <c r="D64" s="4" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="E64" s="3" t="n">
+      <c r="E64" s="4" t="n">
         <v>1.16</v>
       </c>
-      <c r="F64" s="3" t="n">
+      <c r="F64" s="4" t="n">
         <v>0.78</v>
       </c>
-      <c r="G64" s="3" t="n">
+      <c r="G64" s="4" t="n">
         <v>1.41</v>
       </c>
-      <c r="H64" s="4" t="n">
+      <c r="H64" s="5" t="n">
         <v>77.7</v>
       </c>
-      <c r="I64" s="5" t="n">
+      <c r="I64" s="6" t="n">
         <v>0.8981574513904264</v>
       </c>
-      <c r="J64" s="2" t="n">
+      <c r="J64" s="3" t="n">
         <v>184031</v>
       </c>
-      <c r="K64" s="2" t="n">
+      <c r="K64" s="3" t="n">
         <v>11578</v>
       </c>
     </row>
@@ -2627,34 +2639,34 @@
           <t>magnesium</t>
         </is>
       </c>
-      <c r="B65" s="2" t="n">
+      <c r="B65" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C65" s="3" t="n">
+      <c r="C65" s="4" t="n">
         <v>1.05</v>
       </c>
-      <c r="D65" s="3" t="n">
+      <c r="D65" s="4" t="n">
         <v>0.88</v>
       </c>
-      <c r="E65" s="3" t="n">
+      <c r="E65" s="4" t="n">
         <v>1.25</v>
       </c>
-      <c r="F65" s="3" t="n">
+      <c r="F65" s="4" t="n">
         <v>0.16</v>
       </c>
-      <c r="G65" s="3" t="n">
+      <c r="G65" s="4" t="n">
         <v>6.88</v>
       </c>
-      <c r="H65" s="4" t="n">
+      <c r="H65" s="5" t="n">
         <v>69.59999999999999</v>
       </c>
-      <c r="I65" s="5" t="n">
-        <v>0.5539761826694968</v>
-      </c>
-      <c r="J65" s="2" t="n">
+      <c r="I65" s="6" t="n">
+        <v>0.5539761826694971</v>
+      </c>
+      <c r="J65" s="3" t="n">
         <v>44056</v>
       </c>
-      <c r="K65" s="2" t="n">
+      <c r="K65" s="3" t="n">
         <v>6498</v>
       </c>
     </row>
@@ -2664,34 +2676,34 @@
           <t>glucosamine</t>
         </is>
       </c>
-      <c r="B66" s="2" t="n">
+      <c r="B66" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C66" s="3" t="n">
+      <c r="C66" s="4" t="n">
         <v>1.06</v>
       </c>
-      <c r="D66" s="3" t="n">
+      <c r="D66" s="4" t="n">
         <v>1.01</v>
       </c>
-      <c r="E66" s="3" t="n">
+      <c r="E66" s="4" t="n">
         <v>1.11</v>
       </c>
-      <c r="F66" s="3" t="n">
+      <c r="F66" s="4" t="n">
         <v>0.78</v>
       </c>
-      <c r="G66" s="3" t="n">
+      <c r="G66" s="4" t="n">
         <v>1.43</v>
       </c>
-      <c r="H66" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" s="5" t="n">
-        <v>0.01558217739312319</v>
-      </c>
-      <c r="J66" s="2" t="n">
+      <c r="H66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" s="6" t="n">
+        <v>0.01558217739312316</v>
+      </c>
+      <c r="J66" s="3" t="n">
         <v>265129</v>
       </c>
-      <c r="K66" s="2" t="n">
+      <c r="K66" s="3" t="n">
         <v>16136</v>
       </c>
     </row>
@@ -2701,28 +2713,28 @@
           <t>butyric_acid</t>
         </is>
       </c>
-      <c r="B67" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C67" s="3" t="n">
+      <c r="B67" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" s="4" t="n">
         <v>1.08</v>
       </c>
-      <c r="D67" s="3" t="n">
+      <c r="D67" s="4" t="n">
         <v>1.01</v>
       </c>
-      <c r="E67" s="3" t="n">
+      <c r="E67" s="4" t="n">
         <v>1.15</v>
       </c>
-      <c r="F67" s="3" t="inlineStr"/>
-      <c r="G67" s="3" t="inlineStr"/>
-      <c r="H67" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" s="5" t="inlineStr"/>
-      <c r="J67" s="2" t="n">
+      <c r="F67" s="4" t="inlineStr"/>
+      <c r="G67" s="4" t="inlineStr"/>
+      <c r="H67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="6" t="inlineStr"/>
+      <c r="J67" s="3" t="n">
         <v>142239</v>
       </c>
-      <c r="K67" s="2" t="inlineStr"/>
+      <c r="K67" s="3" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2730,28 +2742,28 @@
           <t>sugar_sweetened_beverage_intake</t>
         </is>
       </c>
-      <c r="B68" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C68" s="3" t="n">
+      <c r="B68" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C68" s="4" t="n">
         <v>1.09</v>
       </c>
-      <c r="D68" s="3" t="n">
+      <c r="D68" s="4" t="n">
         <v>0.93</v>
       </c>
-      <c r="E68" s="3" t="n">
+      <c r="E68" s="4" t="n">
         <v>1.28</v>
       </c>
-      <c r="F68" s="3" t="inlineStr"/>
-      <c r="G68" s="3" t="inlineStr"/>
-      <c r="H68" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" s="5" t="inlineStr"/>
-      <c r="J68" s="2" t="n">
+      <c r="F68" s="4" t="inlineStr"/>
+      <c r="G68" s="4" t="inlineStr"/>
+      <c r="H68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" s="6" t="inlineStr"/>
+      <c r="J68" s="3" t="n">
         <v>21533</v>
       </c>
-      <c r="K68" s="2" t="n">
+      <c r="K68" s="3" t="n">
         <v>291</v>
       </c>
     </row>
@@ -2761,28 +2773,28 @@
           <t>vitamin_b2</t>
         </is>
       </c>
-      <c r="B69" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C69" s="3" t="n">
+      <c r="B69" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C69" s="4" t="n">
         <v>1.11</v>
       </c>
-      <c r="D69" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E69" s="3" t="n">
+      <c r="D69" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" s="4" t="n">
         <v>1.23</v>
       </c>
-      <c r="F69" s="3" t="inlineStr"/>
-      <c r="G69" s="3" t="inlineStr"/>
-      <c r="H69" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" s="5" t="inlineStr"/>
-      <c r="J69" s="2" t="n">
+      <c r="F69" s="4" t="inlineStr"/>
+      <c r="G69" s="4" t="inlineStr"/>
+      <c r="H69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="6" t="inlineStr"/>
+      <c r="J69" s="3" t="n">
         <v>1595</v>
       </c>
-      <c r="K69" s="2" t="n">
+      <c r="K69" s="3" t="n">
         <v>561</v>
       </c>
     </row>
@@ -2792,34 +2804,34 @@
           <t>whole_grain_intake</t>
         </is>
       </c>
-      <c r="B70" s="2" t="n">
+      <c r="B70" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C70" s="3" t="n">
+      <c r="C70" s="4" t="n">
         <v>1.11</v>
       </c>
-      <c r="D70" s="3" t="n">
+      <c r="D70" s="4" t="n">
         <v>0.97</v>
       </c>
-      <c r="E70" s="3" t="n">
+      <c r="E70" s="4" t="n">
         <v>1.26</v>
       </c>
-      <c r="F70" s="3" t="n">
+      <c r="F70" s="4" t="n">
         <v>0.24</v>
       </c>
-      <c r="G70" s="3" t="n">
+      <c r="G70" s="4" t="n">
         <v>5.08</v>
       </c>
-      <c r="H70" s="4" t="n">
+      <c r="H70" s="5" t="n">
         <v>83.3</v>
       </c>
-      <c r="I70" s="5" t="n">
+      <c r="I70" s="6" t="n">
         <v>0.1158775811071888</v>
       </c>
-      <c r="J70" s="2" t="n">
+      <c r="J70" s="3" t="n">
         <v>79458</v>
       </c>
-      <c r="K70" s="2" t="n">
+      <c r="K70" s="3" t="n">
         <v>7209</v>
       </c>
     </row>
@@ -2829,28 +2841,28 @@
           <t>phosphorus</t>
         </is>
       </c>
-      <c r="B71" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C71" s="3" t="n">
+      <c r="B71" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C71" s="4" t="n">
         <v>1.12</v>
       </c>
-      <c r="D71" s="3" t="n">
+      <c r="D71" s="4" t="n">
         <v>1.03</v>
       </c>
-      <c r="E71" s="3" t="n">
+      <c r="E71" s="4" t="n">
         <v>1.23</v>
       </c>
-      <c r="F71" s="3" t="inlineStr"/>
-      <c r="G71" s="3" t="inlineStr"/>
-      <c r="H71" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" s="5" t="inlineStr"/>
-      <c r="J71" s="2" t="n">
+      <c r="F71" s="4" t="inlineStr"/>
+      <c r="G71" s="4" t="inlineStr"/>
+      <c r="H71" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="6" t="inlineStr"/>
+      <c r="J71" s="3" t="n">
         <v>47885</v>
       </c>
-      <c r="K71" s="2" t="n">
+      <c r="K71" s="3" t="n">
         <v>5861</v>
       </c>
     </row>
@@ -2860,34 +2872,34 @@
           <t>vitamin_b12</t>
         </is>
       </c>
-      <c r="B72" s="2" t="n">
+      <c r="B72" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C72" s="3" t="n">
+      <c r="C72" s="4" t="n">
         <v>1.12</v>
       </c>
-      <c r="D72" s="3" t="n">
+      <c r="D72" s="4" t="n">
         <v>0.97</v>
       </c>
-      <c r="E72" s="3" t="n">
+      <c r="E72" s="4" t="n">
         <v>1.28</v>
       </c>
-      <c r="F72" s="3" t="n">
+      <c r="F72" s="4" t="n">
         <v>0.73</v>
       </c>
-      <c r="G72" s="3" t="n">
+      <c r="G72" s="4" t="n">
         <v>1.71</v>
       </c>
-      <c r="H72" s="4" t="n">
+      <c r="H72" s="5" t="n">
         <v>64.5</v>
       </c>
-      <c r="I72" s="5" t="n">
-        <v>0.01145019300160749</v>
-      </c>
-      <c r="J72" s="2" t="n">
+      <c r="I72" s="6" t="n">
+        <v>0.0114501930016075</v>
+      </c>
+      <c r="J72" s="3" t="n">
         <v>5961</v>
       </c>
-      <c r="K72" s="2" t="n">
+      <c r="K72" s="3" t="n">
         <v>2681</v>
       </c>
     </row>
@@ -2897,34 +2909,34 @@
           <t>processed_meat_intake</t>
         </is>
       </c>
-      <c r="B73" s="2" t="n">
+      <c r="B73" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="C73" s="3" t="n">
+      <c r="C73" s="4" t="n">
         <v>1.13</v>
       </c>
-      <c r="D73" s="3" t="n">
+      <c r="D73" s="4" t="n">
         <v>1.05</v>
       </c>
-      <c r="E73" s="3" t="n">
+      <c r="E73" s="4" t="n">
         <v>1.21</v>
       </c>
-      <c r="F73" s="3" t="n">
+      <c r="F73" s="4" t="n">
         <v>0.93</v>
       </c>
-      <c r="G73" s="3" t="n">
+      <c r="G73" s="4" t="n">
         <v>1.36</v>
       </c>
-      <c r="H73" s="4" t="n">
+      <c r="H73" s="5" t="n">
         <v>71.2</v>
       </c>
-      <c r="I73" s="5" t="n">
-        <v>0.002637956795546261</v>
-      </c>
-      <c r="J73" s="2" t="n">
+      <c r="I73" s="6" t="n">
+        <v>0.002637956795546257</v>
+      </c>
+      <c r="J73" s="3" t="n">
         <v>1091655</v>
       </c>
-      <c r="K73" s="2" t="n">
+      <c r="K73" s="3" t="n">
         <v>65703</v>
       </c>
     </row>
@@ -2934,34 +2946,34 @@
           <t>vitamin_d</t>
         </is>
       </c>
-      <c r="B74" s="2" t="n">
+      <c r="B74" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="C74" s="3" t="n">
+      <c r="C74" s="4" t="n">
         <v>1.13</v>
       </c>
-      <c r="D74" s="3" t="n">
+      <c r="D74" s="4" t="n">
         <v>1.07</v>
       </c>
-      <c r="E74" s="3" t="n">
+      <c r="E74" s="4" t="n">
         <v>1.19</v>
       </c>
-      <c r="F74" s="3" t="n">
+      <c r="F74" s="4" t="n">
         <v>0.92</v>
       </c>
-      <c r="G74" s="3" t="n">
+      <c r="G74" s="4" t="n">
         <v>1.38</v>
       </c>
-      <c r="H74" s="4" t="n">
+      <c r="H74" s="5" t="n">
         <v>72.8</v>
       </c>
-      <c r="I74" s="5" t="n">
-        <v>0.1064622161384289</v>
-      </c>
-      <c r="J74" s="2" t="n">
+      <c r="I74" s="6" t="n">
+        <v>0.1064622161384286</v>
+      </c>
+      <c r="J74" s="3" t="n">
         <v>551351</v>
       </c>
-      <c r="K74" s="2" t="inlineStr"/>
+      <c r="K74" s="3" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2969,34 +2981,34 @@
           <t>antioxidants</t>
         </is>
       </c>
-      <c r="B75" s="2" t="n">
+      <c r="B75" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C75" s="3" t="n">
+      <c r="C75" s="4" t="n">
         <v>1.15</v>
       </c>
-      <c r="D75" s="3" t="n">
+      <c r="D75" s="4" t="n">
         <v>0.87</v>
       </c>
-      <c r="E75" s="3" t="n">
+      <c r="E75" s="4" t="n">
         <v>1.5</v>
       </c>
-      <c r="F75" s="3" t="n">
+      <c r="F75" s="4" t="n">
         <v>0.04</v>
       </c>
-      <c r="G75" s="3" t="n">
+      <c r="G75" s="4" t="n">
         <v>33.17</v>
       </c>
-      <c r="H75" s="4" t="n">
+      <c r="H75" s="5" t="n">
         <v>90.3</v>
       </c>
-      <c r="I75" s="5" t="n">
+      <c r="I75" s="6" t="n">
         <v>0.1648989938761477</v>
       </c>
-      <c r="J75" s="2" t="n">
+      <c r="J75" s="3" t="n">
         <v>56601</v>
       </c>
-      <c r="K75" s="2" t="n">
+      <c r="K75" s="3" t="n">
         <v>7271</v>
       </c>
     </row>
@@ -3006,34 +3018,34 @@
           <t>vitamin_a</t>
         </is>
       </c>
-      <c r="B76" s="2" t="n">
+      <c r="B76" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="C76" s="3" t="n">
+      <c r="C76" s="4" t="n">
         <v>1.15</v>
       </c>
-      <c r="D76" s="3" t="n">
+      <c r="D76" s="4" t="n">
         <v>0.93</v>
       </c>
-      <c r="E76" s="3" t="n">
+      <c r="E76" s="4" t="n">
         <v>1.42</v>
       </c>
-      <c r="F76" s="3" t="n">
+      <c r="F76" s="4" t="n">
         <v>0.54</v>
       </c>
-      <c r="G76" s="3" t="n">
+      <c r="G76" s="4" t="n">
         <v>2.43</v>
       </c>
-      <c r="H76" s="4" t="n">
+      <c r="H76" s="5" t="n">
         <v>88.40000000000001</v>
       </c>
-      <c r="I76" s="5" t="n">
-        <v>0.9490649069662659</v>
-      </c>
-      <c r="J76" s="2" t="n">
+      <c r="I76" s="6" t="n">
+        <v>0.9490649069662661</v>
+      </c>
+      <c r="J76" s="3" t="n">
         <v>70012</v>
       </c>
-      <c r="K76" s="2" t="n">
+      <c r="K76" s="3" t="n">
         <v>17837</v>
       </c>
     </row>
@@ -3043,34 +3055,34 @@
           <t>calcium</t>
         </is>
       </c>
-      <c r="B77" s="2" t="n">
+      <c r="B77" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="C77" s="3" t="n">
+      <c r="C77" s="4" t="n">
         <v>1.18</v>
       </c>
-      <c r="D77" s="3" t="n">
+      <c r="D77" s="4" t="n">
         <v>1.1</v>
       </c>
-      <c r="E77" s="3" t="n">
+      <c r="E77" s="4" t="n">
         <v>1.28</v>
       </c>
-      <c r="F77" s="3" t="n">
+      <c r="F77" s="4" t="n">
         <v>0.86</v>
       </c>
-      <c r="G77" s="3" t="n">
+      <c r="G77" s="4" t="n">
         <v>1.62</v>
       </c>
-      <c r="H77" s="4" t="n">
+      <c r="H77" s="5" t="n">
         <v>80.7</v>
       </c>
-      <c r="I77" s="5" t="n">
-        <v>0.006727675406670032</v>
-      </c>
-      <c r="J77" s="2" t="n">
+      <c r="I77" s="6" t="n">
+        <v>0.006727675406670044</v>
+      </c>
+      <c r="J77" s="3" t="n">
         <v>1049042</v>
       </c>
-      <c r="K77" s="2" t="inlineStr"/>
+      <c r="K77" s="3" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3078,34 +3090,34 @@
           <t>zinc</t>
         </is>
       </c>
-      <c r="B78" s="2" t="n">
+      <c r="B78" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="C78" s="3" t="n">
+      <c r="C78" s="4" t="n">
         <v>1.18</v>
       </c>
-      <c r="D78" s="3" t="n">
+      <c r="D78" s="4" t="n">
         <v>0.9</v>
       </c>
-      <c r="E78" s="3" t="n">
+      <c r="E78" s="4" t="n">
         <v>1.54</v>
       </c>
-      <c r="F78" s="3" t="n">
+      <c r="F78" s="4" t="n">
         <v>0.46</v>
       </c>
-      <c r="G78" s="3" t="n">
+      <c r="G78" s="4" t="n">
         <v>3.04</v>
       </c>
-      <c r="H78" s="4" t="n">
+      <c r="H78" s="5" t="n">
         <v>79.90000000000001</v>
       </c>
-      <c r="I78" s="5" t="n">
+      <c r="I78" s="6" t="n">
         <v>0.5711938735931297</v>
       </c>
-      <c r="J78" s="2" t="n">
+      <c r="J78" s="3" t="n">
         <v>96718</v>
       </c>
-      <c r="K78" s="2" t="n">
+      <c r="K78" s="3" t="n">
         <v>7983</v>
       </c>
     </row>
@@ -3115,34 +3127,34 @@
           <t>coenzyme_q10</t>
         </is>
       </c>
-      <c r="B79" s="2" t="n">
+      <c r="B79" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C79" s="3" t="n">
+      <c r="C79" s="4" t="n">
         <v>1.19</v>
       </c>
-      <c r="D79" s="3" t="n">
+      <c r="D79" s="4" t="n">
         <v>0.79</v>
       </c>
-      <c r="E79" s="3" t="n">
+      <c r="E79" s="4" t="n">
         <v>1.79</v>
       </c>
-      <c r="F79" s="3" t="n">
+      <c r="F79" s="4" t="n">
         <v>0.01</v>
       </c>
-      <c r="G79" s="3" t="n">
+      <c r="G79" s="4" t="n">
         <v>119.97</v>
       </c>
-      <c r="H79" s="4" t="n">
+      <c r="H79" s="5" t="n">
         <v>69.40000000000001</v>
       </c>
-      <c r="I79" s="5" t="n">
-        <v>0.3692661628018609</v>
-      </c>
-      <c r="J79" s="2" t="n">
+      <c r="I79" s="6" t="n">
+        <v>0.3692661628018608</v>
+      </c>
+      <c r="J79" s="3" t="n">
         <v>36416</v>
       </c>
-      <c r="K79" s="2" t="n">
+      <c r="K79" s="3" t="n">
         <v>2065</v>
       </c>
     </row>
@@ -3152,34 +3164,34 @@
           <t>alcohol</t>
         </is>
       </c>
-      <c r="B80" s="2" t="n">
+      <c r="B80" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="C80" s="3" t="n">
+      <c r="C80" s="4" t="n">
         <v>1.2</v>
       </c>
-      <c r="D80" s="3" t="n">
+      <c r="D80" s="4" t="n">
         <v>1.1</v>
       </c>
-      <c r="E80" s="3" t="n">
+      <c r="E80" s="4" t="n">
         <v>1.3</v>
       </c>
-      <c r="F80" s="3" t="n">
+      <c r="F80" s="4" t="n">
         <v>0.86</v>
       </c>
-      <c r="G80" s="3" t="n">
+      <c r="G80" s="4" t="n">
         <v>1.66</v>
       </c>
-      <c r="H80" s="4" t="n">
+      <c r="H80" s="5" t="n">
         <v>86.59999999999999</v>
       </c>
-      <c r="I80" s="5" t="n">
-        <v>0.00552361906352278</v>
-      </c>
-      <c r="J80" s="2" t="n">
+      <c r="I80" s="6" t="n">
+        <v>0.005523619063522757</v>
+      </c>
+      <c r="J80" s="3" t="n">
         <v>1934957</v>
       </c>
-      <c r="K80" s="2" t="inlineStr"/>
+      <c r="K80" s="3" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3187,34 +3199,34 @@
           <t>dairy</t>
         </is>
       </c>
-      <c r="B81" s="2" t="n">
+      <c r="B81" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="C81" s="3" t="n">
+      <c r="C81" s="4" t="n">
         <v>1.22</v>
       </c>
-      <c r="D81" s="3" t="n">
+      <c r="D81" s="4" t="n">
         <v>1.12</v>
       </c>
-      <c r="E81" s="3" t="n">
+      <c r="E81" s="4" t="n">
         <v>1.34</v>
       </c>
-      <c r="F81" s="3" t="n">
+      <c r="F81" s="4" t="n">
         <v>0.83</v>
       </c>
-      <c r="G81" s="3" t="n">
+      <c r="G81" s="4" t="n">
         <v>1.79</v>
       </c>
-      <c r="H81" s="4" t="n">
+      <c r="H81" s="5" t="n">
         <v>82.7</v>
       </c>
-      <c r="I81" s="5" t="n">
-        <v>0.09941545468620654</v>
-      </c>
-      <c r="J81" s="2" t="n">
+      <c r="I81" s="6" t="n">
+        <v>0.09941545468620652</v>
+      </c>
+      <c r="J81" s="3" t="n">
         <v>739672</v>
       </c>
-      <c r="K81" s="2" t="n">
+      <c r="K81" s="3" t="n">
         <v>33998</v>
       </c>
     </row>
@@ -3224,28 +3236,28 @@
           <t>glutamine</t>
         </is>
       </c>
-      <c r="B82" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C82" s="3" t="n">
+      <c r="B82" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C82" s="4" t="n">
         <v>1.25</v>
       </c>
-      <c r="D82" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E82" s="3" t="n">
+      <c r="D82" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" s="4" t="n">
         <v>1.56</v>
       </c>
-      <c r="F82" s="3" t="inlineStr"/>
-      <c r="G82" s="3" t="inlineStr"/>
-      <c r="H82" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I82" s="5" t="inlineStr"/>
-      <c r="J82" s="2" t="n">
+      <c r="F82" s="4" t="inlineStr"/>
+      <c r="G82" s="4" t="inlineStr"/>
+      <c r="H82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" s="6" t="inlineStr"/>
+      <c r="J82" s="3" t="n">
         <v>342</v>
       </c>
-      <c r="K82" s="2" t="n">
+      <c r="K82" s="3" t="n">
         <v>171</v>
       </c>
     </row>
@@ -3255,34 +3267,34 @@
           <t>yogurt</t>
         </is>
       </c>
-      <c r="B83" s="2" t="n">
+      <c r="B83" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C83" s="3" t="n">
+      <c r="C83" s="4" t="n">
         <v>1.25</v>
       </c>
-      <c r="D83" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E83" s="3" t="n">
+      <c r="D83" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" s="4" t="n">
         <v>1.56</v>
       </c>
-      <c r="F83" s="3" t="n">
+      <c r="F83" s="4" t="n">
         <v>0.12</v>
       </c>
-      <c r="G83" s="3" t="n">
+      <c r="G83" s="4" t="n">
         <v>12.86</v>
       </c>
-      <c r="H83" s="4" t="n">
+      <c r="H83" s="5" t="n">
         <v>50.3</v>
       </c>
-      <c r="I83" s="5" t="n">
-        <v>0.2572200177327541</v>
-      </c>
-      <c r="J83" s="2" t="n">
+      <c r="I83" s="6" t="n">
+        <v>0.257220017732754</v>
+      </c>
+      <c r="J83" s="3" t="n">
         <v>201324</v>
       </c>
-      <c r="K83" s="2" t="n">
+      <c r="K83" s="3" t="n">
         <v>7680</v>
       </c>
     </row>
@@ -3292,28 +3304,28 @@
           <t>betaine</t>
         </is>
       </c>
-      <c r="B84" s="2" t="n">
+      <c r="B84" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C84" s="3" t="n">
+      <c r="C84" s="4" t="n">
         <v>1.3</v>
       </c>
-      <c r="D84" s="3" t="n">
+      <c r="D84" s="4" t="n">
         <v>0.73</v>
       </c>
-      <c r="E84" s="3" t="n">
+      <c r="E84" s="4" t="n">
         <v>2.32</v>
       </c>
-      <c r="F84" s="3" t="inlineStr"/>
-      <c r="G84" s="3" t="inlineStr"/>
-      <c r="H84" s="4" t="n">
+      <c r="F84" s="4" t="inlineStr"/>
+      <c r="G84" s="4" t="inlineStr"/>
+      <c r="H84" s="5" t="n">
         <v>72</v>
       </c>
-      <c r="I84" s="5" t="inlineStr"/>
-      <c r="J84" s="2" t="n">
+      <c r="I84" s="6" t="inlineStr"/>
+      <c r="J84" s="3" t="n">
         <v>48588</v>
       </c>
-      <c r="K84" s="2" t="n">
+      <c r="K84" s="3" t="n">
         <v>868</v>
       </c>
     </row>
@@ -3323,34 +3335,34 @@
           <t>alpha_linolenic_acid</t>
         </is>
       </c>
-      <c r="B85" s="2" t="n">
+      <c r="B85" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C85" s="3" t="n">
+      <c r="C85" s="4" t="n">
         <v>1.31</v>
       </c>
-      <c r="D85" s="3" t="n">
+      <c r="D85" s="4" t="n">
         <v>1.08</v>
       </c>
-      <c r="E85" s="3" t="n">
+      <c r="E85" s="4" t="n">
         <v>1.58</v>
       </c>
-      <c r="F85" s="3" t="n">
+      <c r="F85" s="4" t="n">
         <v>0.75</v>
       </c>
-      <c r="G85" s="3" t="n">
+      <c r="G85" s="4" t="n">
         <v>2.28</v>
       </c>
-      <c r="H85" s="4" t="n">
+      <c r="H85" s="5" t="n">
         <v>85.2</v>
       </c>
-      <c r="I85" s="5" t="n">
-        <v>0.02434834414134598</v>
-      </c>
-      <c r="J85" s="2" t="n">
+      <c r="I85" s="6" t="n">
+        <v>0.024348344141346</v>
+      </c>
+      <c r="J85" s="3" t="n">
         <v>557816</v>
       </c>
-      <c r="K85" s="2" t="n">
+      <c r="K85" s="3" t="n">
         <v>13151</v>
       </c>
     </row>
@@ -3360,28 +3372,28 @@
           <t>creatine</t>
         </is>
       </c>
-      <c r="B86" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C86" s="3" t="n">
+      <c r="B86" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C86" s="4" t="n">
         <v>1.31</v>
       </c>
-      <c r="D86" s="3" t="n">
+      <c r="D86" s="4" t="n">
         <v>1.03</v>
       </c>
-      <c r="E86" s="3" t="n">
+      <c r="E86" s="4" t="n">
         <v>1.63</v>
       </c>
-      <c r="F86" s="3" t="inlineStr"/>
-      <c r="G86" s="3" t="inlineStr"/>
-      <c r="H86" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" s="5" t="inlineStr"/>
-      <c r="J86" s="2" t="n">
+      <c r="F86" s="4" t="inlineStr"/>
+      <c r="G86" s="4" t="inlineStr"/>
+      <c r="H86" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="6" t="inlineStr"/>
+      <c r="J86" s="3" t="n">
         <v>342</v>
       </c>
-      <c r="K86" s="2" t="n">
+      <c r="K86" s="3" t="n">
         <v>171</v>
       </c>
     </row>
@@ -3391,28 +3403,28 @@
           <t>l_valine</t>
         </is>
       </c>
-      <c r="B87" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C87" s="3" t="n">
+      <c r="B87" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C87" s="4" t="n">
         <v>1.31</v>
       </c>
-      <c r="D87" s="3" t="n">
+      <c r="D87" s="4" t="n">
         <v>1.06</v>
       </c>
-      <c r="E87" s="3" t="n">
+      <c r="E87" s="4" t="n">
         <v>1.6</v>
       </c>
-      <c r="F87" s="3" t="inlineStr"/>
-      <c r="G87" s="3" t="inlineStr"/>
-      <c r="H87" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" s="5" t="inlineStr"/>
-      <c r="J87" s="2" t="n">
+      <c r="F87" s="4" t="inlineStr"/>
+      <c r="G87" s="4" t="inlineStr"/>
+      <c r="H87" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="6" t="inlineStr"/>
+      <c r="J87" s="3" t="n">
         <v>342</v>
       </c>
-      <c r="K87" s="2" t="n">
+      <c r="K87" s="3" t="n">
         <v>171</v>
       </c>
     </row>
@@ -3422,28 +3434,28 @@
           <t>l_tyrosine</t>
         </is>
       </c>
-      <c r="B88" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C88" s="3" t="n">
+      <c r="B88" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C88" s="4" t="n">
         <v>1.33</v>
       </c>
-      <c r="D88" s="3" t="n">
+      <c r="D88" s="4" t="n">
         <v>1.05</v>
       </c>
-      <c r="E88" s="3" t="n">
+      <c r="E88" s="4" t="n">
         <v>1.66</v>
       </c>
-      <c r="F88" s="3" t="inlineStr"/>
-      <c r="G88" s="3" t="inlineStr"/>
-      <c r="H88" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" s="5" t="inlineStr"/>
-      <c r="J88" s="2" t="n">
+      <c r="F88" s="4" t="inlineStr"/>
+      <c r="G88" s="4" t="inlineStr"/>
+      <c r="H88" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="6" t="inlineStr"/>
+      <c r="J88" s="3" t="n">
         <v>342</v>
       </c>
-      <c r="K88" s="2" t="n">
+      <c r="K88" s="3" t="n">
         <v>171</v>
       </c>
     </row>
@@ -3453,28 +3465,28 @@
           <t>mineral_supplements</t>
         </is>
       </c>
-      <c r="B89" s="2" t="n">
+      <c r="B89" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C89" s="3" t="n">
+      <c r="C89" s="4" t="n">
         <v>1.33</v>
       </c>
-      <c r="D89" s="3" t="n">
+      <c r="D89" s="4" t="n">
         <v>0.79</v>
       </c>
-      <c r="E89" s="3" t="n">
+      <c r="E89" s="4" t="n">
         <v>2.26</v>
       </c>
-      <c r="F89" s="3" t="inlineStr"/>
-      <c r="G89" s="3" t="inlineStr"/>
-      <c r="H89" s="4" t="n">
+      <c r="F89" s="4" t="inlineStr"/>
+      <c r="G89" s="4" t="inlineStr"/>
+      <c r="H89" s="5" t="n">
         <v>80.09999999999999</v>
       </c>
-      <c r="I89" s="5" t="inlineStr"/>
-      <c r="J89" s="2" t="n">
+      <c r="I89" s="6" t="inlineStr"/>
+      <c r="J89" s="3" t="n">
         <v>57251</v>
       </c>
-      <c r="K89" s="2" t="n">
+      <c r="K89" s="3" t="n">
         <v>1958</v>
       </c>
     </row>
@@ -3484,28 +3496,28 @@
           <t>chocolate</t>
         </is>
       </c>
-      <c r="B90" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C90" s="3" t="n">
+      <c r="B90" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C90" s="4" t="n">
         <v>1.35</v>
       </c>
-      <c r="D90" s="3" t="n">
+      <c r="D90" s="4" t="n">
         <v>1.1</v>
       </c>
-      <c r="E90" s="3" t="n">
+      <c r="E90" s="4" t="n">
         <v>1.64</v>
       </c>
-      <c r="F90" s="3" t="inlineStr"/>
-      <c r="G90" s="3" t="inlineStr"/>
-      <c r="H90" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" s="5" t="inlineStr"/>
-      <c r="J90" s="2" t="n">
+      <c r="F90" s="4" t="inlineStr"/>
+      <c r="G90" s="4" t="inlineStr"/>
+      <c r="H90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="6" t="inlineStr"/>
+      <c r="J90" s="3" t="n">
         <v>2611</v>
       </c>
-      <c r="K90" s="2" t="n">
+      <c r="K90" s="3" t="n">
         <v>1499</v>
       </c>
     </row>
@@ -3515,28 +3527,28 @@
           <t>western_pattern_diet</t>
         </is>
       </c>
-      <c r="B91" s="2" t="n">
+      <c r="B91" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C91" s="3" t="n">
+      <c r="C91" s="4" t="n">
         <v>1.35</v>
       </c>
-      <c r="D91" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E91" s="3" t="n">
+      <c r="D91" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" s="4" t="n">
         <v>1.82</v>
       </c>
-      <c r="F91" s="3" t="inlineStr"/>
-      <c r="G91" s="3" t="inlineStr"/>
-      <c r="H91" s="4" t="n">
+      <c r="F91" s="4" t="inlineStr"/>
+      <c r="G91" s="4" t="inlineStr"/>
+      <c r="H91" s="5" t="n">
         <v>57.1</v>
       </c>
-      <c r="I91" s="5" t="inlineStr"/>
-      <c r="J91" s="2" t="n">
+      <c r="I91" s="6" t="inlineStr"/>
+      <c r="J91" s="3" t="n">
         <v>44462</v>
       </c>
-      <c r="K91" s="2" t="n">
+      <c r="K91" s="3" t="n">
         <v>1702</v>
       </c>
     </row>
@@ -3546,34 +3558,34 @@
           <t>fermented_foods</t>
         </is>
       </c>
-      <c r="B92" s="2" t="n">
+      <c r="B92" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C92" s="3" t="n">
+      <c r="C92" s="4" t="n">
         <v>1.37</v>
       </c>
-      <c r="D92" s="3" t="n">
+      <c r="D92" s="4" t="n">
         <v>0.76</v>
       </c>
-      <c r="E92" s="3" t="n">
+      <c r="E92" s="4" t="n">
         <v>2.45</v>
       </c>
-      <c r="F92" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G92" s="3" t="n">
+      <c r="F92" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" s="4" t="n">
         <v>664.3099999999999</v>
       </c>
-      <c r="H92" s="4" t="n">
+      <c r="H92" s="5" t="n">
         <v>62</v>
       </c>
-      <c r="I92" s="5" t="n">
-        <v>0.1814798483236069</v>
-      </c>
-      <c r="J92" s="2" t="n">
+      <c r="I92" s="6" t="n">
+        <v>0.1814798483236068</v>
+      </c>
+      <c r="J92" s="3" t="n">
         <v>3460</v>
       </c>
-      <c r="K92" s="2" t="n">
+      <c r="K92" s="3" t="n">
         <v>339</v>
       </c>
     </row>
@@ -3583,34 +3595,34 @@
           <t>polyunsaturated_fat_pufa</t>
         </is>
       </c>
-      <c r="B93" s="2" t="n">
+      <c r="B93" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C93" s="3" t="n">
+      <c r="C93" s="4" t="n">
         <v>1.37</v>
       </c>
-      <c r="D93" s="3" t="n">
+      <c r="D93" s="4" t="n">
         <v>0.87</v>
       </c>
-      <c r="E93" s="3" t="n">
+      <c r="E93" s="4" t="n">
         <v>2.17</v>
       </c>
-      <c r="F93" s="3" t="n">
+      <c r="F93" s="4" t="n">
         <v>0.27</v>
       </c>
-      <c r="G93" s="3" t="n">
+      <c r="G93" s="4" t="n">
         <v>7.05</v>
       </c>
-      <c r="H93" s="4" t="n">
+      <c r="H93" s="5" t="n">
         <v>88.7</v>
       </c>
-      <c r="I93" s="5" t="n">
-        <v>0.5930181744853599</v>
-      </c>
-      <c r="J93" s="2" t="n">
+      <c r="I93" s="6" t="n">
+        <v>0.5930181744853598</v>
+      </c>
+      <c r="J93" s="3" t="n">
         <v>64788</v>
       </c>
-      <c r="K93" s="2" t="inlineStr"/>
+      <c r="K93" s="3" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3618,34 +3630,34 @@
           <t>choline</t>
         </is>
       </c>
-      <c r="B94" s="2" t="n">
+      <c r="B94" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C94" s="3" t="n">
+      <c r="C94" s="4" t="n">
         <v>1.38</v>
       </c>
-      <c r="D94" s="3" t="n">
+      <c r="D94" s="4" t="n">
         <v>0.92</v>
       </c>
-      <c r="E94" s="3" t="n">
+      <c r="E94" s="4" t="n">
         <v>2.07</v>
       </c>
-      <c r="F94" s="3" t="n">
+      <c r="F94" s="4" t="n">
         <v>0.01</v>
       </c>
-      <c r="G94" s="3" t="n">
+      <c r="G94" s="4" t="n">
         <v>148.22</v>
       </c>
-      <c r="H94" s="4" t="n">
+      <c r="H94" s="5" t="n">
         <v>77</v>
       </c>
-      <c r="I94" s="5" t="n">
-        <v>0.03888700959299778</v>
-      </c>
-      <c r="J94" s="2" t="n">
+      <c r="I94" s="6" t="n">
+        <v>0.03888700959299785</v>
+      </c>
+      <c r="J94" s="3" t="n">
         <v>8815</v>
       </c>
-      <c r="K94" s="2" t="n">
+      <c r="K94" s="3" t="n">
         <v>1545</v>
       </c>
     </row>
@@ -3655,28 +3667,28 @@
           <t>gamma_linolenic_acid</t>
         </is>
       </c>
-      <c r="B95" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C95" s="3" t="n">
+      <c r="B95" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C95" s="4" t="n">
         <v>1.41</v>
       </c>
-      <c r="D95" s="3" t="n">
+      <c r="D95" s="4" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="E95" s="3" t="n">
+      <c r="E95" s="4" t="n">
         <v>2.12</v>
       </c>
-      <c r="F95" s="3" t="inlineStr"/>
-      <c r="G95" s="3" t="inlineStr"/>
-      <c r="H95" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" s="5" t="inlineStr"/>
-      <c r="J95" s="2" t="n">
+      <c r="F95" s="4" t="inlineStr"/>
+      <c r="G95" s="4" t="inlineStr"/>
+      <c r="H95" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="6" t="inlineStr"/>
+      <c r="J95" s="3" t="n">
         <v>952</v>
       </c>
-      <c r="K95" s="2" t="n">
+      <c r="K95" s="3" t="n">
         <v>476</v>
       </c>
     </row>
@@ -3686,28 +3698,28 @@
           <t>dihomo_gamma_linolenic_acid</t>
         </is>
       </c>
-      <c r="B96" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C96" s="3" t="n">
+      <c r="B96" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C96" s="4" t="n">
         <v>1.54</v>
       </c>
-      <c r="D96" s="3" t="n">
+      <c r="D96" s="4" t="n">
         <v>1.03</v>
       </c>
-      <c r="E96" s="3" t="n">
+      <c r="E96" s="4" t="n">
         <v>2.3</v>
       </c>
-      <c r="F96" s="3" t="inlineStr"/>
-      <c r="G96" s="3" t="inlineStr"/>
-      <c r="H96" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" s="5" t="inlineStr"/>
-      <c r="J96" s="2" t="n">
+      <c r="F96" s="4" t="inlineStr"/>
+      <c r="G96" s="4" t="inlineStr"/>
+      <c r="H96" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="6" t="inlineStr"/>
+      <c r="J96" s="3" t="n">
         <v>952</v>
       </c>
-      <c r="K96" s="2" t="n">
+      <c r="K96" s="3" t="n">
         <v>476</v>
       </c>
     </row>
@@ -3717,34 +3729,34 @@
           <t>monounsaturated_fat_mufa</t>
         </is>
       </c>
-      <c r="B97" s="2" t="n">
+      <c r="B97" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C97" s="3" t="n">
+      <c r="C97" s="4" t="n">
         <v>1.57</v>
       </c>
-      <c r="D97" s="3" t="n">
+      <c r="D97" s="4" t="n">
         <v>1.23</v>
       </c>
-      <c r="E97" s="3" t="n">
+      <c r="E97" s="4" t="n">
         <v>1.99</v>
       </c>
-      <c r="F97" s="3" t="n">
+      <c r="F97" s="4" t="n">
         <v>0.74</v>
       </c>
-      <c r="G97" s="3" t="n">
+      <c r="G97" s="4" t="n">
         <v>3.31</v>
       </c>
-      <c r="H97" s="4" t="n">
+      <c r="H97" s="5" t="n">
         <v>86.40000000000001</v>
       </c>
-      <c r="I97" s="5" t="n">
+      <c r="I97" s="6" t="n">
         <v>0.01420460899877199</v>
       </c>
-      <c r="J97" s="2" t="n">
+      <c r="J97" s="3" t="n">
         <v>56815</v>
       </c>
-      <c r="K97" s="2" t="inlineStr"/>
+      <c r="K97" s="3" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3752,34 +3764,34 @@
           <t>red_meat</t>
         </is>
       </c>
-      <c r="B98" s="2" t="n">
+      <c r="B98" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="C98" s="3" t="n">
+      <c r="C98" s="4" t="n">
         <v>1.6</v>
       </c>
-      <c r="D98" s="3" t="n">
+      <c r="D98" s="4" t="n">
         <v>1.22</v>
       </c>
-      <c r="E98" s="3" t="n">
+      <c r="E98" s="4" t="n">
         <v>2.1</v>
       </c>
-      <c r="F98" s="3" t="n">
+      <c r="F98" s="4" t="n">
         <v>0.57</v>
       </c>
-      <c r="G98" s="3" t="n">
+      <c r="G98" s="4" t="n">
         <v>4.51</v>
       </c>
-      <c r="H98" s="4" t="n">
+      <c r="H98" s="5" t="n">
         <v>89.59999999999999</v>
       </c>
-      <c r="I98" s="5" t="n">
-        <v>0.01959176169058002</v>
-      </c>
-      <c r="J98" s="2" t="n">
+      <c r="I98" s="6" t="n">
+        <v>0.01959176169058001</v>
+      </c>
+      <c r="J98" s="3" t="n">
         <v>974550</v>
       </c>
-      <c r="K98" s="2" t="n">
+      <c r="K98" s="3" t="n">
         <v>57630</v>
       </c>
     </row>
@@ -3789,28 +3801,28 @@
           <t>phosphatidylcholine</t>
         </is>
       </c>
-      <c r="B99" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C99" s="3" t="n">
+      <c r="B99" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C99" s="4" t="n">
         <v>1.78</v>
       </c>
-      <c r="D99" s="3" t="n">
+      <c r="D99" s="4" t="n">
         <v>1.06</v>
       </c>
-      <c r="E99" s="3" t="n">
+      <c r="E99" s="4" t="n">
         <v>2.87</v>
       </c>
-      <c r="F99" s="3" t="inlineStr"/>
-      <c r="G99" s="3" t="inlineStr"/>
-      <c r="H99" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I99" s="5" t="inlineStr"/>
-      <c r="J99" s="2" t="n">
+      <c r="F99" s="4" t="inlineStr"/>
+      <c r="G99" s="4" t="inlineStr"/>
+      <c r="H99" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" s="6" t="inlineStr"/>
+      <c r="J99" s="3" t="n">
         <v>310</v>
       </c>
-      <c r="K99" s="2" t="n">
+      <c r="K99" s="3" t="n">
         <v>41</v>
       </c>
     </row>
@@ -3820,28 +3832,28 @@
           <t>glycine</t>
         </is>
       </c>
-      <c r="B100" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C100" s="3" t="n">
+      <c r="B100" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C100" s="4" t="n">
         <v>1.84</v>
       </c>
-      <c r="D100" s="3" t="n">
+      <c r="D100" s="4" t="n">
         <v>1.18</v>
       </c>
-      <c r="E100" s="3" t="n">
+      <c r="E100" s="4" t="n">
         <v>2.72</v>
       </c>
-      <c r="F100" s="3" t="inlineStr"/>
-      <c r="G100" s="3" t="inlineStr"/>
-      <c r="H100" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I100" s="5" t="inlineStr"/>
-      <c r="J100" s="2" t="n">
+      <c r="F100" s="4" t="inlineStr"/>
+      <c r="G100" s="4" t="inlineStr"/>
+      <c r="H100" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" s="6" t="inlineStr"/>
+      <c r="J100" s="3" t="n">
         <v>666</v>
       </c>
-      <c r="K100" s="2" t="n">
+      <c r="K100" s="3" t="n">
         <v>333</v>
       </c>
     </row>
@@ -3851,28 +3863,28 @@
           <t>carnitine</t>
         </is>
       </c>
-      <c r="B101" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C101" s="3" t="n">
+      <c r="B101" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C101" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D101" s="3" t="n">
+      <c r="D101" s="4" t="n">
         <v>1.13</v>
       </c>
-      <c r="E101" s="3" t="n">
+      <c r="E101" s="4" t="n">
         <v>3.56</v>
       </c>
-      <c r="F101" s="3" t="inlineStr"/>
-      <c r="G101" s="3" t="inlineStr"/>
-      <c r="H101" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I101" s="5" t="inlineStr"/>
-      <c r="J101" s="2" t="n">
+      <c r="F101" s="4" t="inlineStr"/>
+      <c r="G101" s="4" t="inlineStr"/>
+      <c r="H101" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" s="6" t="inlineStr"/>
+      <c r="J101" s="3" t="n">
         <v>692</v>
       </c>
-      <c r="K101" s="2" t="n">
+      <c r="K101" s="3" t="n">
         <v>173</v>
       </c>
     </row>
@@ -3882,28 +3894,28 @@
           <t>pickled_vegetables</t>
         </is>
       </c>
-      <c r="B102" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C102" s="3" t="n">
+      <c r="B102" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C102" s="4" t="n">
         <v>4.58</v>
       </c>
-      <c r="D102" s="3" t="n">
+      <c r="D102" s="4" t="n">
         <v>2.97</v>
       </c>
-      <c r="E102" s="3" t="n">
+      <c r="E102" s="4" t="n">
         <v>5.94</v>
       </c>
-      <c r="F102" s="3" t="inlineStr"/>
-      <c r="G102" s="3" t="inlineStr"/>
-      <c r="H102" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I102" s="5" t="inlineStr"/>
-      <c r="J102" s="2" t="n">
+      <c r="F102" s="4" t="inlineStr"/>
+      <c r="G102" s="4" t="inlineStr"/>
+      <c r="H102" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" s="6" t="inlineStr"/>
+      <c r="J102" s="3" t="n">
         <v>404</v>
       </c>
-      <c r="K102" s="2" t="n">
+      <c r="K102" s="3" t="n">
         <v>130</v>
       </c>
     </row>

--- a/summary/no/exposures_meta_analysis_prostate_cancer_combined.xlsx
+++ b/summary/no/exposures_meta_analysis_prostate_cancer_combined.xlsx
@@ -23,16 +23,13 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -52,7 +49,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -60,22 +57,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -464,57 +452,57 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Exposure</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>number studies</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Pooled RR</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>lower CI RR</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>upper CI RR</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>lower PI RR</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>upper PI RR</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>I^2 (%)</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eggers p-value</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>total N</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>total Cases</t>
         </is>
@@ -526,28 +514,28 @@
           <t>vitamin_b1</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="4" t="n">
+      <c r="B2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>0.03</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="3" t="n">
         <v>0.01</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E2" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="F2" s="4" t="inlineStr"/>
-      <c r="G2" s="4" t="inlineStr"/>
-      <c r="H2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="6" t="inlineStr"/>
-      <c r="J2" s="3" t="n">
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="5" t="inlineStr"/>
+      <c r="J2" s="2" t="n">
         <v>204</v>
       </c>
-      <c r="K2" s="3" t="n">
+      <c r="K2" s="2" t="n">
         <v>102</v>
       </c>
     </row>
@@ -557,28 +545,28 @@
           <t>natto</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="4" t="n">
+      <c r="B3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>0.28</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="3" t="n">
         <v>0.06</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="F3" s="4" t="inlineStr"/>
-      <c r="G3" s="4" t="inlineStr"/>
-      <c r="H3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="6" t="inlineStr"/>
-      <c r="J3" s="3" t="n">
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5" t="inlineStr"/>
+      <c r="J3" s="2" t="n">
         <v>280</v>
       </c>
-      <c r="K3" s="3" t="n">
+      <c r="K3" s="2" t="n">
         <v>140</v>
       </c>
     </row>
@@ -588,28 +576,28 @@
           <t>papaya</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="4" t="n">
+      <c r="B4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="3" t="n">
         <v>0.15</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="3" t="n">
         <v>0.97</v>
       </c>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="6" t="inlineStr"/>
-      <c r="J4" s="3" t="n">
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="2" t="n">
         <v>105</v>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="K4" s="2" t="n">
         <v>35</v>
       </c>
     </row>
@@ -619,28 +607,28 @@
           <t>inositol</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="4" t="n">
+      <c r="B5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="3" t="n">
         <v>0.39</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="3" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="6" t="inlineStr"/>
-      <c r="J5" s="3" t="n">
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5" t="inlineStr"/>
+      <c r="J5" s="2" t="n">
         <v>400</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="2" t="n">
         <v>100</v>
       </c>
     </row>
@@ -650,28 +638,28 @@
           <t>early_time_restricted_eating</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="4" t="n">
+      <c r="B6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>0.57</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="6" t="inlineStr"/>
-      <c r="J6" s="3" t="n">
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="2" t="n">
         <v>1455</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="2" t="n">
         <v>607</v>
       </c>
     </row>
@@ -681,34 +669,34 @@
           <t>soy</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B7" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="3" t="n">
         <v>0.41</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="3" t="n">
         <v>0.89</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F7" s="3" t="n">
         <v>0.17</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="3" t="n">
         <v>2.09</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="H7" s="4" t="n">
         <v>78.90000000000001</v>
       </c>
-      <c r="I7" s="6" t="n">
-        <v>0.1010785350953813</v>
-      </c>
-      <c r="J7" s="3" t="n">
+      <c r="I7" s="5" t="n">
+        <v>0.1010785350953814</v>
+      </c>
+      <c r="J7" s="2" t="n">
         <v>85059</v>
       </c>
-      <c r="K7" s="3" t="n">
+      <c r="K7" s="2" t="n">
         <v>5399</v>
       </c>
     </row>
@@ -718,34 +706,34 @@
           <t>green_tea</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C8" s="3" t="n">
         <v>0.62</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="3" t="n">
         <v>0.43</v>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E8" s="3" t="n">
         <v>0.89</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="F8" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G8" s="3" t="n">
         <v>1.92</v>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="H8" s="4" t="n">
         <v>72.7</v>
       </c>
-      <c r="I8" s="6" t="n">
-        <v>0.1767576153047416</v>
-      </c>
-      <c r="J8" s="3" t="n">
+      <c r="I8" s="5" t="n">
+        <v>0.1767576153047418</v>
+      </c>
+      <c r="J8" s="2" t="n">
         <v>99090</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="2" t="n">
         <v>1577</v>
       </c>
     </row>
@@ -755,34 +743,34 @@
           <t>insoluble_dietary_fiber_intake</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
+      <c r="B9" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C9" s="3" t="n">
         <v>0.62</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="3" t="n">
         <v>0.38</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="F9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="4" t="n">
+      <c r="F9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3" t="n">
         <v>206.11</v>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="H9" s="4" t="n">
         <v>74.90000000000001</v>
       </c>
-      <c r="I9" s="6" t="n">
+      <c r="I9" s="5" t="n">
         <v>0.1151715356999109</v>
       </c>
-      <c r="J9" s="3" t="n">
+      <c r="J9" s="2" t="n">
         <v>101084</v>
       </c>
-      <c r="K9" s="3" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -790,28 +778,28 @@
           <t>low_fat_diet</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" s="4" t="n">
+      <c r="B10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>0.62</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="3" t="n">
         <v>0.33</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E10" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="F10" s="4" t="inlineStr"/>
-      <c r="G10" s="4" t="inlineStr"/>
-      <c r="H10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="6" t="inlineStr"/>
-      <c r="J10" s="3" t="n">
+      <c r="F10" s="3" t="inlineStr"/>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="2" t="n">
         <v>1170</v>
       </c>
-      <c r="K10" s="3" t="n">
+      <c r="K10" s="2" t="n">
         <v>390</v>
       </c>
     </row>
@@ -821,28 +809,28 @@
           <t>vitamin_k2</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="4" t="n">
+      <c r="B11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>0.65</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="3" t="n">
         <v>0.39</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" s="3" t="n">
         <v>1.06</v>
       </c>
-      <c r="F11" s="4" t="inlineStr"/>
-      <c r="G11" s="4" t="inlineStr"/>
-      <c r="H11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="6" t="inlineStr"/>
-      <c r="J11" s="3" t="n">
+      <c r="F11" s="3" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="2" t="n">
         <v>11319</v>
       </c>
-      <c r="K11" s="3" t="n">
+      <c r="K11" s="2" t="n">
         <v>268</v>
       </c>
     </row>
@@ -852,34 +840,34 @@
           <t>zeaxanthin</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C12" s="4" t="n">
+      <c r="C12" s="3" t="n">
         <v>0.66</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="E12" s="3" t="n">
         <v>1.08</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="F12" s="3" t="n">
         <v>0.09</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="G12" s="3" t="n">
         <v>4.89</v>
       </c>
-      <c r="H12" s="5" t="n">
+      <c r="H12" s="4" t="n">
         <v>62.9</v>
       </c>
-      <c r="I12" s="6" t="n">
-        <v>0.8236639670954942</v>
-      </c>
-      <c r="J12" s="3" t="n">
+      <c r="I12" s="5" t="n">
+        <v>0.8236639670954935</v>
+      </c>
+      <c r="J12" s="2" t="n">
         <v>2106</v>
       </c>
-      <c r="K12" s="3" t="n">
+      <c r="K12" s="2" t="n">
         <v>808</v>
       </c>
     </row>
@@ -889,28 +877,28 @@
           <t>quercetin</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="4" t="n">
+      <c r="B13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>0.67</v>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="3" t="n">
         <v>0.48</v>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E13" s="3" t="n">
         <v>0.93</v>
       </c>
-      <c r="F13" s="4" t="inlineStr"/>
-      <c r="G13" s="4" t="inlineStr"/>
-      <c r="H13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="3" t="n">
+      <c r="F13" s="3" t="inlineStr"/>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="2" t="n">
         <v>971</v>
       </c>
-      <c r="K13" s="3" t="n">
+      <c r="K13" s="2" t="n">
         <v>433</v>
       </c>
     </row>
@@ -920,28 +908,28 @@
           <t>vegan_diet</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" s="4" t="n">
+      <c r="B14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>0.67</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="3" t="n">
         <v>0.51</v>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="E14" s="3" t="n">
         <v>0.86</v>
       </c>
-      <c r="F14" s="4" t="inlineStr"/>
-      <c r="G14" s="4" t="inlineStr"/>
-      <c r="H14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="3" t="n">
+      <c r="F14" s="3" t="inlineStr"/>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="2" t="n">
         <v>26346</v>
       </c>
-      <c r="K14" s="3" t="n">
+      <c r="K14" s="2" t="n">
         <v>1079</v>
       </c>
     </row>
@@ -951,28 +939,28 @@
           <t>pyruvate</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" s="4" t="n">
+      <c r="B15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>0.68</v>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D15" s="3" t="n">
         <v>0.52</v>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="E15" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="F15" s="4" t="inlineStr"/>
-      <c r="G15" s="4" t="inlineStr"/>
-      <c r="H15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="3" t="n">
+      <c r="F15" s="3" t="inlineStr"/>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="2" t="n">
         <v>666</v>
       </c>
-      <c r="K15" s="3" t="n">
+      <c r="K15" s="2" t="n">
         <v>333</v>
       </c>
     </row>
@@ -982,34 +970,34 @@
           <t>garlic</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
+      <c r="B16" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C16" s="4" t="n">
+      <c r="C16" s="3" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" s="3" t="n">
         <v>0.42</v>
       </c>
-      <c r="E16" s="4" t="n">
+      <c r="E16" s="3" t="n">
         <v>1.13</v>
       </c>
-      <c r="F16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="4" t="n">
+      <c r="F16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3" t="n">
         <v>265.07</v>
       </c>
-      <c r="H16" s="5" t="n">
+      <c r="H16" s="4" t="n">
         <v>85</v>
       </c>
-      <c r="I16" s="6" t="n">
+      <c r="I16" s="5" t="n">
         <v>0.2044018200861738</v>
       </c>
-      <c r="J16" s="3" t="n">
+      <c r="J16" s="2" t="n">
         <v>36604</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="2" t="n">
         <v>2168</v>
       </c>
     </row>
@@ -1019,28 +1007,28 @@
           <t>vegetarian_diet</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" s="4" t="n">
+      <c r="B17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" s="3" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="E17" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="F17" s="4" t="inlineStr"/>
-      <c r="G17" s="4" t="inlineStr"/>
-      <c r="H17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="6" t="inlineStr"/>
-      <c r="J17" s="3" t="n">
+      <c r="F17" s="3" t="inlineStr"/>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="2" t="n">
         <v>217937</v>
       </c>
-      <c r="K17" s="3" t="n">
+      <c r="K17" s="2" t="n">
         <v>9501</v>
       </c>
     </row>
@@ -1050,34 +1038,34 @@
           <t>linoleic_acid</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n">
+      <c r="B18" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="C18" s="4" t="n">
+      <c r="C18" s="3" t="n">
         <v>0.71</v>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D18" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="E18" s="4" t="n">
+      <c r="E18" s="3" t="n">
         <v>0.99</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="F18" s="3" t="n">
         <v>0.26</v>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="G18" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="H18" s="5" t="n">
+      <c r="H18" s="4" t="n">
         <v>70.5</v>
       </c>
-      <c r="I18" s="6" t="n">
-        <v>0.4789848163683069</v>
-      </c>
-      <c r="J18" s="3" t="n">
+      <c r="I18" s="5" t="n">
+        <v>0.4789848163683078</v>
+      </c>
+      <c r="J18" s="2" t="n">
         <v>8735</v>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="K18" s="2" t="n">
         <v>3057</v>
       </c>
     </row>
@@ -1087,34 +1075,34 @@
           <t>genistein</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n">
+      <c r="B19" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="C19" s="4" t="n">
+      <c r="C19" s="3" t="n">
         <v>0.72</v>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="D19" s="3" t="n">
         <v>0.54</v>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="E19" s="3" t="n">
         <v>0.95</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="F19" s="3" t="n">
         <v>0.31</v>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="G19" s="3" t="n">
         <v>1.67</v>
       </c>
-      <c r="H19" s="5" t="n">
+      <c r="H19" s="4" t="n">
         <v>67.8</v>
       </c>
-      <c r="I19" s="6" t="n">
-        <v>0.04176805723275343</v>
-      </c>
-      <c r="J19" s="3" t="n">
+      <c r="I19" s="5" t="n">
+        <v>0.04176805723275333</v>
+      </c>
+      <c r="J19" s="2" t="n">
         <v>91302</v>
       </c>
-      <c r="K19" s="3" t="n">
+      <c r="K19" s="2" t="n">
         <v>3818</v>
       </c>
     </row>
@@ -1124,28 +1112,28 @@
           <t>vitamin_k</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
+      <c r="B20" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C20" s="4" t="n">
+      <c r="C20" s="3" t="n">
         <v>0.73</v>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="D20" s="3" t="n">
         <v>0.58</v>
       </c>
-      <c r="E20" s="4" t="n">
+      <c r="E20" s="3" t="n">
         <v>0.92</v>
       </c>
-      <c r="F20" s="4" t="inlineStr"/>
-      <c r="G20" s="4" t="inlineStr"/>
-      <c r="H20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="3" t="n">
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="2" t="n">
         <v>12063</v>
       </c>
-      <c r="K20" s="3" t="n">
+      <c r="K20" s="2" t="n">
         <v>518</v>
       </c>
     </row>
@@ -1155,34 +1143,34 @@
           <t>tomato</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n">
+      <c r="B21" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="C21" s="4" t="n">
+      <c r="C21" s="3" t="n">
         <v>0.74</v>
       </c>
-      <c r="D21" s="4" t="n">
+      <c r="D21" s="3" t="n">
         <v>0.64</v>
       </c>
-      <c r="E21" s="4" t="n">
+      <c r="E21" s="3" t="n">
         <v>0.85</v>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="F21" s="3" t="n">
         <v>0.47</v>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="G21" s="3" t="n">
         <v>1.16</v>
       </c>
-      <c r="H21" s="5" t="n">
+      <c r="H21" s="4" t="n">
         <v>78.09999999999999</v>
       </c>
-      <c r="I21" s="6" t="n">
-        <v>2.045420729252859e-05</v>
-      </c>
-      <c r="J21" s="3" t="n">
+      <c r="I21" s="5" t="n">
+        <v>2.045420729252854e-05</v>
+      </c>
+      <c r="J21" s="2" t="n">
         <v>1057923</v>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="K21" s="2" t="n">
         <v>67108</v>
       </c>
     </row>
@@ -1192,34 +1180,34 @@
           <t>melatonin</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n">
+      <c r="B22" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C22" s="4" t="n">
+      <c r="C22" s="3" t="n">
         <v>0.75</v>
       </c>
-      <c r="D22" s="4" t="n">
+      <c r="D22" s="3" t="n">
         <v>0.45</v>
       </c>
-      <c r="E22" s="4" t="n">
+      <c r="E22" s="3" t="n">
         <v>1.23</v>
       </c>
-      <c r="F22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="4" t="n">
+      <c r="F22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3" t="n">
         <v>196.29</v>
       </c>
-      <c r="H22" s="5" t="n">
+      <c r="H22" s="4" t="n">
         <v>73</v>
       </c>
-      <c r="I22" s="6" t="n">
-        <v>0.0645864721910966</v>
-      </c>
-      <c r="J22" s="3" t="n">
+      <c r="I22" s="5" t="n">
+        <v>0.06458647219109648</v>
+      </c>
+      <c r="J22" s="2" t="n">
         <v>4618</v>
       </c>
-      <c r="K22" s="3" t="n">
+      <c r="K22" s="2" t="n">
         <v>1414</v>
       </c>
     </row>
@@ -1229,34 +1217,34 @@
           <t>tea</t>
         </is>
       </c>
-      <c r="B23" s="3" t="n">
+      <c r="B23" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="C23" s="4" t="n">
+      <c r="C23" s="3" t="n">
         <v>0.75</v>
       </c>
-      <c r="D23" s="4" t="n">
+      <c r="D23" s="3" t="n">
         <v>0.64</v>
       </c>
-      <c r="E23" s="4" t="n">
+      <c r="E23" s="3" t="n">
         <v>0.89</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="F23" s="3" t="n">
         <v>0.45</v>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="G23" s="3" t="n">
         <v>1.27</v>
       </c>
-      <c r="H23" s="5" t="n">
+      <c r="H23" s="4" t="n">
         <v>84.90000000000001</v>
       </c>
-      <c r="I23" s="6" t="n">
-        <v>0.0499620846835085</v>
-      </c>
-      <c r="J23" s="3" t="n">
+      <c r="I23" s="5" t="n">
+        <v>0.04996208468350868</v>
+      </c>
+      <c r="J23" s="2" t="n">
         <v>314398</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="2" t="n">
         <v>15389</v>
       </c>
     </row>
@@ -1266,28 +1254,28 @@
           <t>citrulline</t>
         </is>
       </c>
-      <c r="B24" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C24" s="4" t="n">
+      <c r="B24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>0.76</v>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="D24" s="3" t="n">
         <v>0.65</v>
       </c>
-      <c r="E24" s="4" t="n">
+      <c r="E24" s="3" t="n">
         <v>0.88</v>
       </c>
-      <c r="F24" s="4" t="inlineStr"/>
-      <c r="G24" s="4" t="inlineStr"/>
-      <c r="H24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="6" t="inlineStr"/>
-      <c r="J24" s="3" t="n">
+      <c r="F24" s="3" t="inlineStr"/>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="2" t="n">
         <v>2154</v>
       </c>
-      <c r="K24" s="3" t="n">
+      <c r="K24" s="2" t="n">
         <v>1077</v>
       </c>
     </row>
@@ -1297,28 +1285,28 @@
           <t>potassium</t>
         </is>
       </c>
-      <c r="B25" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" s="4" t="n">
+      <c r="B25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>0.77</v>
       </c>
-      <c r="D25" s="4" t="n">
+      <c r="D25" s="3" t="n">
         <v>0.55</v>
       </c>
-      <c r="E25" s="4" t="n">
+      <c r="E25" s="3" t="n">
         <v>1.08</v>
       </c>
-      <c r="F25" s="4" t="inlineStr"/>
-      <c r="G25" s="4" t="inlineStr"/>
-      <c r="H25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="3" t="n">
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="2" t="n">
         <v>656</v>
       </c>
-      <c r="K25" s="3" t="n">
+      <c r="K25" s="2" t="n">
         <v>328</v>
       </c>
     </row>
@@ -1328,34 +1316,34 @@
           <t>selenium</t>
         </is>
       </c>
-      <c r="B26" s="3" t="n">
+      <c r="B26" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="C26" s="4" t="n">
+      <c r="C26" s="3" t="n">
         <v>0.77</v>
       </c>
-      <c r="D26" s="4" t="n">
+      <c r="D26" s="3" t="n">
         <v>0.67</v>
       </c>
-      <c r="E26" s="4" t="n">
+      <c r="E26" s="3" t="n">
         <v>0.89</v>
       </c>
-      <c r="F26" s="4" t="n">
+      <c r="F26" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="G26" s="3" t="n">
         <v>1.48</v>
       </c>
-      <c r="H26" s="5" t="n">
+      <c r="H26" s="4" t="n">
         <v>84.90000000000001</v>
       </c>
-      <c r="I26" s="6" t="n">
-        <v>0.0008136772771022829</v>
-      </c>
-      <c r="J26" s="3" t="n">
+      <c r="I26" s="5" t="n">
+        <v>0.0008136772771022815</v>
+      </c>
+      <c r="J26" s="2" t="n">
         <v>382643</v>
       </c>
-      <c r="K26" s="3" t="n">
+      <c r="K26" s="2" t="n">
         <v>29947</v>
       </c>
     </row>
@@ -1365,28 +1353,28 @@
           <t>iodine</t>
         </is>
       </c>
-      <c r="B27" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" s="4" t="n">
+      <c r="B27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>0.78</v>
       </c>
-      <c r="D27" s="4" t="n">
+      <c r="D27" s="3" t="n">
         <v>0.55</v>
       </c>
-      <c r="E27" s="4" t="n">
+      <c r="E27" s="3" t="n">
         <v>1.09</v>
       </c>
-      <c r="F27" s="4" t="inlineStr"/>
-      <c r="G27" s="4" t="inlineStr"/>
-      <c r="H27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="3" t="n">
+      <c r="F27" s="3" t="inlineStr"/>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="2" t="n">
         <v>656</v>
       </c>
-      <c r="K27" s="3" t="n">
+      <c r="K27" s="2" t="n">
         <v>328</v>
       </c>
     </row>
@@ -1396,28 +1384,28 @@
           <t>time_restricted_eating</t>
         </is>
       </c>
-      <c r="B28" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C28" s="4" t="n">
+      <c r="B28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>0.79</v>
       </c>
-      <c r="D28" s="4" t="n">
+      <c r="D28" s="3" t="n">
         <v>0.57</v>
       </c>
-      <c r="E28" s="4" t="n">
+      <c r="E28" s="3" t="n">
         <v>1.06</v>
       </c>
-      <c r="F28" s="4" t="inlineStr"/>
-      <c r="G28" s="4" t="inlineStr"/>
-      <c r="H28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" s="6" t="inlineStr"/>
-      <c r="J28" s="3" t="n">
+      <c r="F28" s="3" t="inlineStr"/>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="5" t="inlineStr"/>
+      <c r="J28" s="2" t="n">
         <v>1455</v>
       </c>
-      <c r="K28" s="3" t="n">
+      <c r="K28" s="2" t="n">
         <v>607</v>
       </c>
     </row>
@@ -1427,28 +1415,28 @@
           <t>oleic_acid</t>
         </is>
       </c>
-      <c r="B29" s="3" t="n">
+      <c r="B29" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C29" s="4" t="n">
+      <c r="C29" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="D29" s="4" t="n">
+      <c r="D29" s="3" t="n">
         <v>0.24</v>
       </c>
-      <c r="E29" s="4" t="n">
+      <c r="E29" s="3" t="n">
         <v>2.64</v>
       </c>
-      <c r="F29" s="4" t="inlineStr"/>
-      <c r="G29" s="4" t="inlineStr"/>
-      <c r="H29" s="5" t="n">
+      <c r="F29" s="3" t="inlineStr"/>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="4" t="n">
         <v>82</v>
       </c>
-      <c r="I29" s="6" t="inlineStr"/>
-      <c r="J29" s="3" t="n">
+      <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="2" t="n">
         <v>58714</v>
       </c>
-      <c r="K29" s="3" t="n">
+      <c r="K29" s="2" t="n">
         <v>851</v>
       </c>
     </row>
@@ -1458,28 +1446,28 @@
           <t>mushrooms</t>
         </is>
       </c>
-      <c r="B30" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" s="4" t="n">
+      <c r="B30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>0.84</v>
       </c>
-      <c r="D30" s="4" t="n">
+      <c r="D30" s="3" t="n">
         <v>0.71</v>
       </c>
-      <c r="E30" s="4" t="n">
+      <c r="E30" s="3" t="n">
         <v>0.98</v>
       </c>
-      <c r="F30" s="4" t="inlineStr"/>
-      <c r="G30" s="4" t="inlineStr"/>
-      <c r="H30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="6" t="inlineStr"/>
-      <c r="J30" s="3" t="n">
+      <c r="F30" s="3" t="inlineStr"/>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="5" t="inlineStr"/>
+      <c r="J30" s="2" t="n">
         <v>36499</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="2" t="n">
         <v>1204</v>
       </c>
     </row>
@@ -1489,34 +1477,34 @@
           <t>lycopene</t>
         </is>
       </c>
-      <c r="B31" s="3" t="n">
+      <c r="B31" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="C31" s="4" t="n">
+      <c r="C31" s="3" t="n">
         <v>0.85</v>
       </c>
-      <c r="D31" s="4" t="n">
+      <c r="D31" s="3" t="n">
         <v>0.78</v>
       </c>
-      <c r="E31" s="4" t="n">
+      <c r="E31" s="3" t="n">
         <v>0.93</v>
       </c>
-      <c r="F31" s="4" t="n">
+      <c r="F31" s="3" t="n">
         <v>0.62</v>
       </c>
-      <c r="G31" s="4" t="n">
+      <c r="G31" s="3" t="n">
         <v>1.15</v>
       </c>
-      <c r="H31" s="5" t="n">
+      <c r="H31" s="4" t="n">
         <v>71.40000000000001</v>
       </c>
-      <c r="I31" s="6" t="n">
-        <v>0.0008787392868700854</v>
-      </c>
-      <c r="J31" s="3" t="n">
+      <c r="I31" s="5" t="n">
+        <v>0.0008787392868700852</v>
+      </c>
+      <c r="J31" s="2" t="n">
         <v>321509</v>
       </c>
-      <c r="K31" s="3" t="n">
+      <c r="K31" s="2" t="n">
         <v>28185</v>
       </c>
     </row>
@@ -1526,34 +1514,34 @@
           <t>vitamin_c</t>
         </is>
       </c>
-      <c r="B32" s="3" t="n">
+      <c r="B32" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="C32" s="4" t="n">
+      <c r="C32" s="3" t="n">
         <v>0.87</v>
       </c>
-      <c r="D32" s="4" t="n">
+      <c r="D32" s="3" t="n">
         <v>0.75</v>
       </c>
-      <c r="E32" s="4" t="n">
+      <c r="E32" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="F32" s="4" t="n">
+      <c r="F32" s="3" t="n">
         <v>0.51</v>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="G32" s="3" t="n">
         <v>1.49</v>
       </c>
-      <c r="H32" s="5" t="n">
+      <c r="H32" s="4" t="n">
         <v>79.09999999999999</v>
       </c>
-      <c r="I32" s="6" t="n">
-        <v>0.9264859141728312</v>
-      </c>
-      <c r="J32" s="3" t="n">
+      <c r="I32" s="5" t="n">
+        <v>0.926485914172831</v>
+      </c>
+      <c r="J32" s="2" t="n">
         <v>68944</v>
       </c>
-      <c r="K32" s="3" t="n">
+      <c r="K32" s="2" t="n">
         <v>7699</v>
       </c>
     </row>
@@ -1563,28 +1551,28 @@
           <t>fish_oil</t>
         </is>
       </c>
-      <c r="B33" s="3" t="n">
+      <c r="B33" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C33" s="4" t="n">
+      <c r="C33" s="3" t="n">
         <v>0.89</v>
       </c>
-      <c r="D33" s="4" t="n">
+      <c r="D33" s="3" t="n">
         <v>0.68</v>
       </c>
-      <c r="E33" s="4" t="n">
+      <c r="E33" s="3" t="n">
         <v>1.17</v>
       </c>
-      <c r="F33" s="4" t="inlineStr"/>
-      <c r="G33" s="4" t="inlineStr"/>
-      <c r="H33" s="5" t="n">
+      <c r="F33" s="3" t="inlineStr"/>
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="4" t="n">
         <v>47.9</v>
       </c>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="3" t="n">
+      <c r="I33" s="5" t="inlineStr"/>
+      <c r="J33" s="2" t="n">
         <v>37289</v>
       </c>
-      <c r="K33" s="3" t="n">
+      <c r="K33" s="2" t="n">
         <v>1735</v>
       </c>
     </row>
@@ -1594,34 +1582,34 @@
           <t>legumes</t>
         </is>
       </c>
-      <c r="B34" s="3" t="n">
+      <c r="B34" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="C34" s="4" t="n">
+      <c r="C34" s="3" t="n">
         <v>0.89</v>
       </c>
-      <c r="D34" s="4" t="n">
+      <c r="D34" s="3" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="E34" s="4" t="n">
+      <c r="E34" s="3" t="n">
         <v>0.97</v>
       </c>
-      <c r="F34" s="4" t="n">
+      <c r="F34" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="G34" s="4" t="n">
+      <c r="G34" s="3" t="n">
         <v>1.12</v>
       </c>
-      <c r="H34" s="5" t="n">
+      <c r="H34" s="4" t="n">
         <v>62.4</v>
       </c>
-      <c r="I34" s="6" t="n">
-        <v>0.006170430008920973</v>
-      </c>
-      <c r="J34" s="3" t="n">
+      <c r="I34" s="5" t="n">
+        <v>0.00617043000892098</v>
+      </c>
+      <c r="J34" s="2" t="n">
         <v>1155076</v>
       </c>
-      <c r="K34" s="3" t="n">
+      <c r="K34" s="2" t="n">
         <v>79072</v>
       </c>
     </row>
@@ -1631,34 +1619,34 @@
           <t>soluble_dietary_fiber_intake</t>
         </is>
       </c>
-      <c r="B35" s="3" t="n">
+      <c r="B35" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C35" s="4" t="n">
+      <c r="C35" s="3" t="n">
         <v>0.89</v>
       </c>
-      <c r="D35" s="4" t="n">
+      <c r="D35" s="3" t="n">
         <v>0.83</v>
       </c>
-      <c r="E35" s="4" t="n">
+      <c r="E35" s="3" t="n">
         <v>0.96</v>
       </c>
-      <c r="F35" s="4" t="n">
+      <c r="F35" s="3" t="n">
         <v>0.57</v>
       </c>
-      <c r="G35" s="4" t="n">
+      <c r="G35" s="3" t="n">
         <v>1.39</v>
       </c>
-      <c r="H35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" s="6" t="n">
-        <v>0.188399637329524</v>
-      </c>
-      <c r="J35" s="3" t="n">
+      <c r="H35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>0.1883996373295245</v>
+      </c>
+      <c r="J35" s="2" t="n">
         <v>80888</v>
       </c>
-      <c r="K35" s="3" t="n">
+      <c r="K35" s="2" t="n">
         <v>10851</v>
       </c>
     </row>
@@ -1668,34 +1656,34 @@
           <t>vitamin_b6</t>
         </is>
       </c>
-      <c r="B36" s="3" t="n">
+      <c r="B36" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C36" s="4" t="n">
+      <c r="C36" s="3" t="n">
         <v>0.89</v>
       </c>
-      <c r="D36" s="4" t="n">
+      <c r="D36" s="3" t="n">
         <v>0.83</v>
       </c>
-      <c r="E36" s="4" t="n">
+      <c r="E36" s="3" t="n">
         <v>0.96</v>
       </c>
-      <c r="F36" s="4" t="n">
+      <c r="F36" s="3" t="n">
         <v>0.57</v>
       </c>
-      <c r="G36" s="4" t="n">
+      <c r="G36" s="3" t="n">
         <v>1.41</v>
       </c>
-      <c r="H36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" s="6" t="n">
-        <v>0.2443574036478493</v>
-      </c>
-      <c r="J36" s="3" t="n">
+      <c r="H36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>0.2443574036478494</v>
+      </c>
+      <c r="J36" s="2" t="n">
         <v>70879</v>
       </c>
-      <c r="K36" s="3" t="n">
+      <c r="K36" s="2" t="n">
         <v>7656</v>
       </c>
     </row>
@@ -1705,28 +1693,28 @@
           <t>plant_based_diet</t>
         </is>
       </c>
-      <c r="B37" s="3" t="n">
+      <c r="B37" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C37" s="4" t="n">
+      <c r="C37" s="3" t="n">
         <v>0.91</v>
       </c>
-      <c r="D37" s="4" t="n">
+      <c r="D37" s="3" t="n">
         <v>0.84</v>
       </c>
-      <c r="E37" s="4" t="n">
+      <c r="E37" s="3" t="n">
         <v>0.99</v>
       </c>
-      <c r="F37" s="4" t="inlineStr"/>
-      <c r="G37" s="4" t="inlineStr"/>
-      <c r="H37" s="5" t="n">
+      <c r="F37" s="3" t="inlineStr"/>
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="4" t="n">
         <v>39.5</v>
       </c>
-      <c r="I37" s="6" t="inlineStr"/>
-      <c r="J37" s="3" t="n">
+      <c r="I37" s="5" t="inlineStr"/>
+      <c r="J37" s="2" t="n">
         <v>211318</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="2" t="n">
         <v>24516</v>
       </c>
     </row>
@@ -1736,34 +1724,34 @@
           <t>beta_carotene</t>
         </is>
       </c>
-      <c r="B38" s="3" t="n">
+      <c r="B38" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="C38" s="4" t="n">
+      <c r="C38" s="3" t="n">
         <v>0.92</v>
       </c>
-      <c r="D38" s="4" t="n">
+      <c r="D38" s="3" t="n">
         <v>0.76</v>
       </c>
-      <c r="E38" s="4" t="n">
+      <c r="E38" s="3" t="n">
         <v>1.11</v>
       </c>
-      <c r="F38" s="4" t="n">
+      <c r="F38" s="3" t="n">
         <v>0.49</v>
       </c>
-      <c r="G38" s="4" t="n">
+      <c r="G38" s="3" t="n">
         <v>1.73</v>
       </c>
-      <c r="H38" s="5" t="n">
+      <c r="H38" s="4" t="n">
         <v>76</v>
       </c>
-      <c r="I38" s="6" t="n">
-        <v>0.375241327694828</v>
-      </c>
-      <c r="J38" s="3" t="n">
+      <c r="I38" s="5" t="n">
+        <v>0.3752413276948279</v>
+      </c>
+      <c r="J38" s="2" t="n">
         <v>122141</v>
       </c>
-      <c r="K38" s="3" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1771,28 +1759,28 @@
           <t>caffeine</t>
         </is>
       </c>
-      <c r="B39" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C39" s="4" t="n">
+      <c r="B39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>0.92</v>
       </c>
-      <c r="D39" s="4" t="n">
+      <c r="D39" s="3" t="n">
         <v>0.84</v>
       </c>
-      <c r="E39" s="4" t="n">
+      <c r="E39" s="3" t="n">
         <v>1.02</v>
       </c>
-      <c r="F39" s="4" t="inlineStr"/>
-      <c r="G39" s="4" t="inlineStr"/>
-      <c r="H39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="6" t="inlineStr"/>
-      <c r="J39" s="3" t="n">
+      <c r="F39" s="3" t="inlineStr"/>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="5" t="inlineStr"/>
+      <c r="J39" s="2" t="n">
         <v>46667</v>
       </c>
-      <c r="K39" s="3" t="n">
+      <c r="K39" s="2" t="n">
         <v>3037</v>
       </c>
     </row>
@@ -1802,28 +1790,28 @@
           <t>ginseng</t>
         </is>
       </c>
-      <c r="B40" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" s="4" t="n">
+      <c r="B40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>0.92</v>
       </c>
-      <c r="D40" s="4" t="n">
+      <c r="D40" s="3" t="n">
         <v>0.72</v>
       </c>
-      <c r="E40" s="4" t="n">
+      <c r="E40" s="3" t="n">
         <v>1.15</v>
       </c>
-      <c r="F40" s="4" t="inlineStr"/>
-      <c r="G40" s="4" t="inlineStr"/>
-      <c r="H40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" s="6" t="inlineStr"/>
-      <c r="J40" s="3" t="n">
+      <c r="F40" s="3" t="inlineStr"/>
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="5" t="inlineStr"/>
+      <c r="J40" s="2" t="n">
         <v>35239</v>
       </c>
-      <c r="K40" s="3" t="n">
+      <c r="K40" s="2" t="n">
         <v>1602</v>
       </c>
     </row>
@@ -1833,34 +1821,34 @@
           <t>total_dietary_fiber_intake</t>
         </is>
       </c>
-      <c r="B41" s="3" t="n">
+      <c r="B41" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="C41" s="4" t="n">
+      <c r="C41" s="3" t="n">
         <v>0.92</v>
       </c>
-      <c r="D41" s="4" t="n">
+      <c r="D41" s="3" t="n">
         <v>0.86</v>
       </c>
-      <c r="E41" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" s="4" t="n">
+      <c r="E41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="3" t="n">
         <v>0.77</v>
       </c>
-      <c r="G41" s="4" t="n">
+      <c r="G41" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="H41" s="5" t="n">
+      <c r="H41" s="4" t="n">
         <v>42.9</v>
       </c>
-      <c r="I41" s="6" t="n">
-        <v>0.07744276379719461</v>
-      </c>
-      <c r="J41" s="3" t="n">
+      <c r="I41" s="5" t="n">
+        <v>0.0774427637971946</v>
+      </c>
+      <c r="J41" s="2" t="n">
         <v>972077</v>
       </c>
-      <c r="K41" s="3" t="n">
+      <c r="K41" s="2" t="n">
         <v>64899</v>
       </c>
     </row>
@@ -1870,28 +1858,28 @@
           <t>dash_diet</t>
         </is>
       </c>
-      <c r="B42" s="3" t="n">
+      <c r="B42" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C42" s="4" t="n">
+      <c r="C42" s="3" t="n">
         <v>0.93</v>
       </c>
-      <c r="D42" s="4" t="n">
+      <c r="D42" s="3" t="n">
         <v>0.82</v>
       </c>
-      <c r="E42" s="4" t="n">
+      <c r="E42" s="3" t="n">
         <v>1.06</v>
       </c>
-      <c r="F42" s="4" t="inlineStr"/>
-      <c r="G42" s="4" t="inlineStr"/>
-      <c r="H42" s="5" t="n">
+      <c r="F42" s="3" t="inlineStr"/>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="4" t="n">
         <v>73.90000000000001</v>
       </c>
-      <c r="I42" s="6" t="inlineStr"/>
-      <c r="J42" s="3" t="n">
+      <c r="I42" s="5" t="inlineStr"/>
+      <c r="J42" s="2" t="n">
         <v>152714</v>
       </c>
-      <c r="K42" s="3" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1899,28 +1887,28 @@
           <t>ginkgo_biloba</t>
         </is>
       </c>
-      <c r="B43" s="3" t="n">
+      <c r="B43" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C43" s="4" t="n">
+      <c r="C43" s="3" t="n">
         <v>0.93</v>
       </c>
-      <c r="D43" s="4" t="n">
+      <c r="D43" s="3" t="n">
         <v>0.68</v>
       </c>
-      <c r="E43" s="4" t="n">
+      <c r="E43" s="3" t="n">
         <v>1.27</v>
       </c>
-      <c r="F43" s="4" t="inlineStr"/>
-      <c r="G43" s="4" t="inlineStr"/>
-      <c r="H43" s="5" t="n">
+      <c r="F43" s="3" t="inlineStr"/>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="4" t="n">
         <v>46.8</v>
       </c>
-      <c r="I43" s="6" t="inlineStr"/>
-      <c r="J43" s="3" t="n">
+      <c r="I43" s="5" t="inlineStr"/>
+      <c r="J43" s="2" t="n">
         <v>38308</v>
       </c>
-      <c r="K43" s="3" t="n">
+      <c r="K43" s="2" t="n">
         <v>1665</v>
       </c>
     </row>
@@ -1930,34 +1918,34 @@
           <t>docosahexaenoic_acid</t>
         </is>
       </c>
-      <c r="B44" s="3" t="n">
+      <c r="B44" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C44" s="4" t="n">
+      <c r="C44" s="3" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="D44" s="4" t="n">
+      <c r="D44" s="3" t="n">
         <v>0.74</v>
       </c>
-      <c r="E44" s="4" t="n">
+      <c r="E44" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="F44" s="4" t="n">
+      <c r="F44" s="3" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="G44" s="4" t="n">
+      <c r="G44" s="3" t="n">
         <v>12.3</v>
       </c>
-      <c r="H44" s="5" t="n">
+      <c r="H44" s="4" t="n">
         <v>55.4</v>
       </c>
-      <c r="I44" s="6" t="n">
+      <c r="I44" s="5" t="n">
         <v>0.6285558694668995</v>
       </c>
-      <c r="J44" s="3" t="n">
+      <c r="J44" s="2" t="n">
         <v>144141</v>
       </c>
-      <c r="K44" s="3" t="n">
+      <c r="K44" s="2" t="n">
         <v>7729</v>
       </c>
     </row>
@@ -1967,34 +1955,34 @@
           <t>vitamin_e</t>
         </is>
       </c>
-      <c r="B45" s="3" t="n">
+      <c r="B45" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="C45" s="4" t="n">
+      <c r="C45" s="3" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="D45" s="4" t="n">
+      <c r="D45" s="3" t="n">
         <v>0.87</v>
       </c>
-      <c r="E45" s="4" t="n">
+      <c r="E45" s="3" t="n">
         <v>1.02</v>
       </c>
-      <c r="F45" s="4" t="n">
+      <c r="F45" s="3" t="n">
         <v>0.67</v>
       </c>
-      <c r="G45" s="4" t="n">
+      <c r="G45" s="3" t="n">
         <v>1.32</v>
       </c>
-      <c r="H45" s="5" t="n">
+      <c r="H45" s="4" t="n">
         <v>75.90000000000001</v>
       </c>
-      <c r="I45" s="6" t="n">
-        <v>0.1015950190265765</v>
-      </c>
-      <c r="J45" s="3" t="n">
+      <c r="I45" s="5" t="n">
+        <v>0.1015950190265767</v>
+      </c>
+      <c r="J45" s="2" t="n">
         <v>404649</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="2" t="n">
         <v>36660</v>
       </c>
     </row>
@@ -2004,28 +1992,28 @@
           <t>omega_6_fatty_acids</t>
         </is>
       </c>
-      <c r="B46" s="3" t="n">
+      <c r="B46" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C46" s="4" t="n">
+      <c r="C46" s="3" t="n">
         <v>0.96</v>
       </c>
-      <c r="D46" s="4" t="n">
+      <c r="D46" s="3" t="n">
         <v>0.79</v>
       </c>
-      <c r="E46" s="4" t="n">
+      <c r="E46" s="3" t="n">
         <v>1.17</v>
       </c>
-      <c r="F46" s="4" t="inlineStr"/>
-      <c r="G46" s="4" t="inlineStr"/>
-      <c r="H46" s="5" t="n">
+      <c r="F46" s="3" t="inlineStr"/>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="4" t="n">
         <v>40.4</v>
       </c>
-      <c r="I46" s="6" t="inlineStr"/>
-      <c r="J46" s="3" t="n">
+      <c r="I46" s="5" t="inlineStr"/>
+      <c r="J46" s="2" t="n">
         <v>254243</v>
       </c>
-      <c r="K46" s="3" t="n">
+      <c r="K46" s="2" t="n">
         <v>1931</v>
       </c>
     </row>
@@ -2035,28 +2023,28 @@
           <t>plant_protein_intake</t>
         </is>
       </c>
-      <c r="B47" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C47" s="4" t="n">
+      <c r="B47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" s="3" t="n">
         <v>0.98</v>
       </c>
-      <c r="D47" s="4" t="n">
+      <c r="D47" s="3" t="n">
         <v>0.93</v>
       </c>
-      <c r="E47" s="4" t="n">
+      <c r="E47" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="F47" s="4" t="inlineStr"/>
-      <c r="G47" s="4" t="inlineStr"/>
-      <c r="H47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" s="6" t="inlineStr"/>
-      <c r="J47" s="3" t="n">
+      <c r="F47" s="3" t="inlineStr"/>
+      <c r="G47" s="3" t="inlineStr"/>
+      <c r="H47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="5" t="inlineStr"/>
+      <c r="J47" s="2" t="n">
         <v>150671</v>
       </c>
-      <c r="K47" s="3" t="n">
+      <c r="K47" s="2" t="n">
         <v>14238</v>
       </c>
     </row>
@@ -2066,28 +2054,28 @@
           <t>animal_protein_intake</t>
         </is>
       </c>
-      <c r="B48" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C48" s="4" t="n">
+      <c r="B48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" s="3" t="n">
         <v>0.99</v>
       </c>
-      <c r="D48" s="4" t="n">
+      <c r="D48" s="3" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="E48" s="4" t="n">
+      <c r="E48" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="F48" s="4" t="inlineStr"/>
-      <c r="G48" s="4" t="inlineStr"/>
-      <c r="H48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" s="6" t="inlineStr"/>
-      <c r="J48" s="3" t="n">
+      <c r="F48" s="3" t="inlineStr"/>
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="5" t="inlineStr"/>
+      <c r="J48" s="2" t="n">
         <v>159482</v>
       </c>
-      <c r="K48" s="3" t="n">
+      <c r="K48" s="2" t="n">
         <v>17349</v>
       </c>
     </row>
@@ -2097,28 +2085,28 @@
           <t>dietary_protein_intake</t>
         </is>
       </c>
-      <c r="B49" s="3" t="n">
+      <c r="B49" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C49" s="4" t="n">
+      <c r="C49" s="3" t="n">
         <v>0.99</v>
       </c>
-      <c r="D49" s="4" t="n">
+      <c r="D49" s="3" t="n">
         <v>0.89</v>
       </c>
-      <c r="E49" s="4" t="n">
+      <c r="E49" s="3" t="n">
         <v>1.11</v>
       </c>
-      <c r="F49" s="4" t="inlineStr"/>
-      <c r="G49" s="4" t="inlineStr"/>
-      <c r="H49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" s="6" t="inlineStr"/>
-      <c r="J49" s="3" t="n">
+      <c r="F49" s="3" t="inlineStr"/>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="5" t="inlineStr"/>
+      <c r="J49" s="2" t="n">
         <v>109557</v>
       </c>
-      <c r="K49" s="3" t="n">
+      <c r="K49" s="2" t="n">
         <v>3064</v>
       </c>
     </row>
@@ -2128,34 +2116,34 @@
           <t>eggs</t>
         </is>
       </c>
-      <c r="B50" s="3" t="n">
+      <c r="B50" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C50" s="4" t="n">
+      <c r="C50" s="3" t="n">
         <v>0.99</v>
       </c>
-      <c r="D50" s="4" t="n">
+      <c r="D50" s="3" t="n">
         <v>0.96</v>
       </c>
-      <c r="E50" s="4" t="n">
+      <c r="E50" s="3" t="n">
         <v>1.02</v>
       </c>
-      <c r="F50" s="4" t="n">
+      <c r="F50" s="3" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="G50" s="4" t="n">
+      <c r="G50" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="H50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" s="6" t="n">
+      <c r="H50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="5" t="n">
         <v>0.8121269612161565</v>
       </c>
-      <c r="J50" s="3" t="n">
+      <c r="J50" s="2" t="n">
         <v>900752</v>
       </c>
-      <c r="K50" s="3" t="n">
+      <c r="K50" s="2" t="n">
         <v>53381</v>
       </c>
     </row>
@@ -2165,34 +2153,34 @@
           <t>eicosapentaenoic_acid</t>
         </is>
       </c>
-      <c r="B51" s="3" t="n">
+      <c r="B51" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C51" s="4" t="n">
+      <c r="C51" s="3" t="n">
         <v>0.99</v>
       </c>
-      <c r="D51" s="4" t="n">
+      <c r="D51" s="3" t="n">
         <v>0.89</v>
       </c>
-      <c r="E51" s="4" t="n">
+      <c r="E51" s="3" t="n">
         <v>1.11</v>
       </c>
-      <c r="F51" s="4" t="n">
+      <c r="F51" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="G51" s="4" t="n">
+      <c r="G51" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="H51" s="5" t="n">
+      <c r="H51" s="4" t="n">
         <v>65.2</v>
       </c>
-      <c r="I51" s="6" t="n">
-        <v>0.5746798036256722</v>
-      </c>
-      <c r="J51" s="3" t="n">
+      <c r="I51" s="5" t="n">
+        <v>0.5746798036256719</v>
+      </c>
+      <c r="J51" s="2" t="n">
         <v>444156</v>
       </c>
-      <c r="K51" s="3" t="n">
+      <c r="K51" s="2" t="n">
         <v>13552</v>
       </c>
     </row>
@@ -2202,28 +2190,28 @@
           <t>docosapentaenoic_acid_omega_3</t>
         </is>
       </c>
-      <c r="B52" s="3" t="n">
+      <c r="B52" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C52" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D52" s="4" t="n">
+      <c r="C52" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" s="3" t="n">
         <v>0.97</v>
       </c>
-      <c r="E52" s="4" t="n">
+      <c r="E52" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="F52" s="4" t="inlineStr"/>
-      <c r="G52" s="4" t="inlineStr"/>
-      <c r="H52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" s="6" t="inlineStr"/>
-      <c r="J52" s="3" t="n">
+      <c r="F52" s="3" t="inlineStr"/>
+      <c r="G52" s="3" t="inlineStr"/>
+      <c r="H52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="5" t="inlineStr"/>
+      <c r="J52" s="2" t="n">
         <v>143344</v>
       </c>
-      <c r="K52" s="3" t="n">
+      <c r="K52" s="2" t="n">
         <v>7412</v>
       </c>
     </row>
@@ -2233,34 +2221,34 @@
           <t>lutein</t>
         </is>
       </c>
-      <c r="B53" s="3" t="n">
+      <c r="B53" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C53" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D53" s="4" t="n">
+      <c r="C53" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" s="3" t="n">
         <v>0.63</v>
       </c>
-      <c r="E53" s="4" t="n">
+      <c r="E53" s="3" t="n">
         <v>1.61</v>
       </c>
-      <c r="F53" s="4" t="n">
+      <c r="F53" s="3" t="n">
         <v>0.18</v>
       </c>
-      <c r="G53" s="4" t="n">
+      <c r="G53" s="3" t="n">
         <v>5.71</v>
       </c>
-      <c r="H53" s="5" t="n">
+      <c r="H53" s="4" t="n">
         <v>84.2</v>
       </c>
-      <c r="I53" s="6" t="n">
-        <v>0.9535391069907841</v>
-      </c>
-      <c r="J53" s="3" t="n">
+      <c r="I53" s="5" t="n">
+        <v>0.9535391069907844</v>
+      </c>
+      <c r="J53" s="2" t="n">
         <v>3128</v>
       </c>
-      <c r="K53" s="3" t="n">
+      <c r="K53" s="2" t="n">
         <v>1292</v>
       </c>
     </row>
@@ -2270,28 +2258,28 @@
           <t>mediterranean_diet</t>
         </is>
       </c>
-      <c r="B54" s="3" t="n">
+      <c r="B54" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C54" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D54" s="4" t="n">
+      <c r="C54" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="E54" s="4" t="n">
+      <c r="E54" s="3" t="n">
         <v>1.11</v>
       </c>
-      <c r="F54" s="4" t="inlineStr"/>
-      <c r="G54" s="4" t="inlineStr"/>
-      <c r="H54" s="5" t="n">
+      <c r="F54" s="3" t="inlineStr"/>
+      <c r="G54" s="3" t="inlineStr"/>
+      <c r="H54" s="4" t="n">
         <v>69.5</v>
       </c>
-      <c r="I54" s="6" t="inlineStr"/>
-      <c r="J54" s="3" t="n">
+      <c r="I54" s="5" t="inlineStr"/>
+      <c r="J54" s="2" t="n">
         <v>106146</v>
       </c>
-      <c r="K54" s="3" t="n">
+      <c r="K54" s="2" t="n">
         <v>7476</v>
       </c>
     </row>
@@ -2301,28 +2289,28 @@
           <t>gondoic_acid</t>
         </is>
       </c>
-      <c r="B55" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C55" s="4" t="n">
+      <c r="B55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" s="3" t="n">
         <v>1.01</v>
       </c>
-      <c r="D55" s="4" t="n">
+      <c r="D55" s="3" t="n">
         <v>0.98</v>
       </c>
-      <c r="E55" s="4" t="n">
+      <c r="E55" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="F55" s="4" t="inlineStr"/>
-      <c r="G55" s="4" t="inlineStr"/>
-      <c r="H55" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" s="6" t="inlineStr"/>
-      <c r="J55" s="3" t="n">
+      <c r="F55" s="3" t="inlineStr"/>
+      <c r="G55" s="3" t="inlineStr"/>
+      <c r="H55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="5" t="inlineStr"/>
+      <c r="J55" s="2" t="n">
         <v>142239</v>
       </c>
-      <c r="K55" s="3" t="n">
+      <c r="K55" s="2" t="n">
         <v>7036</v>
       </c>
     </row>
@@ -2332,34 +2320,34 @@
           <t>folic_acid</t>
         </is>
       </c>
-      <c r="B56" s="3" t="n">
+      <c r="B56" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="C56" s="4" t="n">
+      <c r="C56" s="3" t="n">
         <v>1.02</v>
       </c>
-      <c r="D56" s="4" t="n">
+      <c r="D56" s="3" t="n">
         <v>0.95</v>
       </c>
-      <c r="E56" s="4" t="n">
+      <c r="E56" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="F56" s="4" t="n">
+      <c r="F56" s="3" t="n">
         <v>0.83</v>
       </c>
-      <c r="G56" s="4" t="n">
+      <c r="G56" s="3" t="n">
         <v>1.25</v>
       </c>
-      <c r="H56" s="5" t="n">
+      <c r="H56" s="4" t="n">
         <v>49</v>
       </c>
-      <c r="I56" s="6" t="n">
+      <c r="I56" s="5" t="n">
         <v>0.09195795349035596</v>
       </c>
-      <c r="J56" s="3" t="n">
+      <c r="J56" s="2" t="n">
         <v>157607</v>
       </c>
-      <c r="K56" s="3" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2367,34 +2355,34 @@
           <t>multivitamin</t>
         </is>
       </c>
-      <c r="B57" s="3" t="n">
+      <c r="B57" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="C57" s="4" t="n">
+      <c r="C57" s="3" t="n">
         <v>1.02</v>
       </c>
-      <c r="D57" s="4" t="n">
+      <c r="D57" s="3" t="n">
         <v>0.96</v>
       </c>
-      <c r="E57" s="4" t="n">
+      <c r="E57" s="3" t="n">
         <v>1.09</v>
       </c>
-      <c r="F57" s="4" t="n">
+      <c r="F57" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="G57" s="4" t="n">
+      <c r="G57" s="3" t="n">
         <v>1.17</v>
       </c>
-      <c r="H57" s="5" t="n">
+      <c r="H57" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="I57" s="6" t="n">
+      <c r="I57" s="5" t="n">
         <v>0.2764130406639589</v>
       </c>
-      <c r="J57" s="3" t="n">
+      <c r="J57" s="2" t="n">
         <v>397821</v>
       </c>
-      <c r="K57" s="3" t="n">
+      <c r="K57" s="2" t="n">
         <v>7673</v>
       </c>
     </row>
@@ -2404,34 +2392,34 @@
           <t>ultra_processed_food_intake</t>
         </is>
       </c>
-      <c r="B58" s="3" t="n">
+      <c r="B58" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="C58" s="4" t="n">
+      <c r="C58" s="3" t="n">
         <v>1.02</v>
       </c>
-      <c r="D58" s="4" t="n">
+      <c r="D58" s="3" t="n">
         <v>0.95</v>
       </c>
-      <c r="E58" s="4" t="n">
+      <c r="E58" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="F58" s="4" t="n">
+      <c r="F58" s="3" t="n">
         <v>0.86</v>
       </c>
-      <c r="G58" s="4" t="n">
+      <c r="G58" s="3" t="n">
         <v>1.22</v>
       </c>
-      <c r="H58" s="5" t="n">
+      <c r="H58" s="4" t="n">
         <v>38.1</v>
       </c>
-      <c r="I58" s="6" t="n">
-        <v>0.4142673366090839</v>
-      </c>
-      <c r="J58" s="3" t="n">
+      <c r="I58" s="5" t="n">
+        <v>0.4142673366090832</v>
+      </c>
+      <c r="J58" s="2" t="n">
         <v>248736</v>
       </c>
-      <c r="K58" s="3" t="n">
+      <c r="K58" s="2" t="n">
         <v>13760</v>
       </c>
     </row>
@@ -2441,28 +2429,28 @@
           <t>vitamin_k1</t>
         </is>
       </c>
-      <c r="B59" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C59" s="4" t="n">
+      <c r="B59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" s="3" t="n">
         <v>1.02</v>
       </c>
-      <c r="D59" s="4" t="n">
+      <c r="D59" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="E59" s="4" t="n">
+      <c r="E59" s="3" t="n">
         <v>1.48</v>
       </c>
-      <c r="F59" s="4" t="inlineStr"/>
-      <c r="G59" s="4" t="inlineStr"/>
-      <c r="H59" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" s="6" t="inlineStr"/>
-      <c r="J59" s="3" t="n">
+      <c r="F59" s="3" t="inlineStr"/>
+      <c r="G59" s="3" t="inlineStr"/>
+      <c r="H59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="5" t="inlineStr"/>
+      <c r="J59" s="2" t="n">
         <v>11319</v>
       </c>
-      <c r="K59" s="3" t="n">
+      <c r="K59" s="2" t="n">
         <v>268</v>
       </c>
     </row>
@@ -2472,34 +2460,34 @@
           <t>omega_3_fatty_acids</t>
         </is>
       </c>
-      <c r="B60" s="3" t="n">
+      <c r="B60" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="C60" s="4" t="n">
+      <c r="C60" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="D60" s="4" t="n">
+      <c r="D60" s="3" t="n">
         <v>0.95</v>
       </c>
-      <c r="E60" s="4" t="n">
+      <c r="E60" s="3" t="n">
         <v>1.11</v>
       </c>
-      <c r="F60" s="4" t="n">
+      <c r="F60" s="3" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="G60" s="4" t="n">
+      <c r="G60" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="H60" s="5" t="n">
+      <c r="H60" s="4" t="n">
         <v>75.59999999999999</v>
       </c>
-      <c r="I60" s="6" t="n">
+      <c r="I60" s="5" t="n">
         <v>0.8028884184138012</v>
       </c>
-      <c r="J60" s="3" t="n">
+      <c r="J60" s="2" t="n">
         <v>435151</v>
       </c>
-      <c r="K60" s="3" t="n">
+      <c r="K60" s="2" t="n">
         <v>22287</v>
       </c>
     </row>
@@ -2509,28 +2497,28 @@
           <t>saw_palmetto</t>
         </is>
       </c>
-      <c r="B61" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C61" s="4" t="n">
+      <c r="B61" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="D61" s="4" t="n">
+      <c r="D61" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="E61" s="4" t="n">
+      <c r="E61" s="3" t="n">
         <v>1.19</v>
       </c>
-      <c r="F61" s="4" t="inlineStr"/>
-      <c r="G61" s="4" t="inlineStr"/>
-      <c r="H61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" s="6" t="inlineStr"/>
-      <c r="J61" s="3" t="n">
+      <c r="F61" s="3" t="inlineStr"/>
+      <c r="G61" s="3" t="inlineStr"/>
+      <c r="H61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="5" t="inlineStr"/>
+      <c r="J61" s="2" t="n">
         <v>35239</v>
       </c>
-      <c r="K61" s="3" t="n">
+      <c r="K61" s="2" t="n">
         <v>1602</v>
       </c>
     </row>
@@ -2540,28 +2528,28 @@
           <t>chondroitin</t>
         </is>
       </c>
-      <c r="B62" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C62" s="4" t="n">
+      <c r="B62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="D62" s="4" t="n">
+      <c r="D62" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="E62" s="4" t="n">
+      <c r="E62" s="3" t="n">
         <v>1.21</v>
       </c>
-      <c r="F62" s="4" t="inlineStr"/>
-      <c r="G62" s="4" t="inlineStr"/>
-      <c r="H62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" s="6" t="inlineStr"/>
-      <c r="J62" s="3" t="n">
+      <c r="F62" s="3" t="inlineStr"/>
+      <c r="G62" s="3" t="inlineStr"/>
+      <c r="H62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="5" t="inlineStr"/>
+      <c r="J62" s="2" t="n">
         <v>35239</v>
       </c>
-      <c r="K62" s="3" t="n">
+      <c r="K62" s="2" t="n">
         <v>1602</v>
       </c>
     </row>
@@ -2571,28 +2559,28 @@
           <t>copper</t>
         </is>
       </c>
-      <c r="B63" s="3" t="n">
+      <c r="B63" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C63" s="4" t="n">
+      <c r="C63" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="D63" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E63" s="4" t="n">
+      <c r="D63" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" s="3" t="n">
         <v>1.11</v>
       </c>
-      <c r="F63" s="4" t="inlineStr"/>
-      <c r="G63" s="4" t="inlineStr"/>
-      <c r="H63" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" s="6" t="inlineStr"/>
-      <c r="J63" s="3" t="n">
+      <c r="F63" s="3" t="inlineStr"/>
+      <c r="G63" s="3" t="inlineStr"/>
+      <c r="H63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="5" t="inlineStr"/>
+      <c r="J63" s="2" t="n">
         <v>43360</v>
       </c>
-      <c r="K63" s="3" t="n">
+      <c r="K63" s="2" t="n">
         <v>6174</v>
       </c>
     </row>
@@ -2602,34 +2590,34 @@
           <t>iron</t>
         </is>
       </c>
-      <c r="B64" s="3" t="n">
+      <c r="B64" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C64" s="4" t="n">
+      <c r="C64" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="D64" s="4" t="n">
+      <c r="D64" s="3" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="E64" s="4" t="n">
+      <c r="E64" s="3" t="n">
         <v>1.16</v>
       </c>
-      <c r="F64" s="4" t="n">
+      <c r="F64" s="3" t="n">
         <v>0.78</v>
       </c>
-      <c r="G64" s="4" t="n">
+      <c r="G64" s="3" t="n">
         <v>1.41</v>
       </c>
-      <c r="H64" s="5" t="n">
+      <c r="H64" s="4" t="n">
         <v>77.7</v>
       </c>
-      <c r="I64" s="6" t="n">
+      <c r="I64" s="5" t="n">
         <v>0.8981574513904264</v>
       </c>
-      <c r="J64" s="3" t="n">
+      <c r="J64" s="2" t="n">
         <v>184031</v>
       </c>
-      <c r="K64" s="3" t="n">
+      <c r="K64" s="2" t="n">
         <v>11578</v>
       </c>
     </row>
@@ -2639,34 +2627,34 @@
           <t>magnesium</t>
         </is>
       </c>
-      <c r="B65" s="3" t="n">
+      <c r="B65" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C65" s="4" t="n">
+      <c r="C65" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="D65" s="4" t="n">
+      <c r="D65" s="3" t="n">
         <v>0.88</v>
       </c>
-      <c r="E65" s="4" t="n">
+      <c r="E65" s="3" t="n">
         <v>1.25</v>
       </c>
-      <c r="F65" s="4" t="n">
+      <c r="F65" s="3" t="n">
         <v>0.16</v>
       </c>
-      <c r="G65" s="4" t="n">
+      <c r="G65" s="3" t="n">
         <v>6.88</v>
       </c>
-      <c r="H65" s="5" t="n">
+      <c r="H65" s="4" t="n">
         <v>69.59999999999999</v>
       </c>
-      <c r="I65" s="6" t="n">
-        <v>0.5539761826694971</v>
-      </c>
-      <c r="J65" s="3" t="n">
+      <c r="I65" s="5" t="n">
+        <v>0.5539761826694968</v>
+      </c>
+      <c r="J65" s="2" t="n">
         <v>44056</v>
       </c>
-      <c r="K65" s="3" t="n">
+      <c r="K65" s="2" t="n">
         <v>6498</v>
       </c>
     </row>
@@ -2676,34 +2664,34 @@
           <t>glucosamine</t>
         </is>
       </c>
-      <c r="B66" s="3" t="n">
+      <c r="B66" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C66" s="4" t="n">
+      <c r="C66" s="3" t="n">
         <v>1.06</v>
       </c>
-      <c r="D66" s="4" t="n">
+      <c r="D66" s="3" t="n">
         <v>1.01</v>
       </c>
-      <c r="E66" s="4" t="n">
+      <c r="E66" s="3" t="n">
         <v>1.11</v>
       </c>
-      <c r="F66" s="4" t="n">
+      <c r="F66" s="3" t="n">
         <v>0.78</v>
       </c>
-      <c r="G66" s="4" t="n">
+      <c r="G66" s="3" t="n">
         <v>1.43</v>
       </c>
-      <c r="H66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" s="6" t="n">
-        <v>0.01558217739312316</v>
-      </c>
-      <c r="J66" s="3" t="n">
+      <c r="H66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" s="5" t="n">
+        <v>0.01558217739312319</v>
+      </c>
+      <c r="J66" s="2" t="n">
         <v>265129</v>
       </c>
-      <c r="K66" s="3" t="n">
+      <c r="K66" s="2" t="n">
         <v>16136</v>
       </c>
     </row>
@@ -2713,28 +2701,28 @@
           <t>butyric_acid</t>
         </is>
       </c>
-      <c r="B67" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C67" s="4" t="n">
+      <c r="B67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" s="3" t="n">
         <v>1.08</v>
       </c>
-      <c r="D67" s="4" t="n">
+      <c r="D67" s="3" t="n">
         <v>1.01</v>
       </c>
-      <c r="E67" s="4" t="n">
+      <c r="E67" s="3" t="n">
         <v>1.15</v>
       </c>
-      <c r="F67" s="4" t="inlineStr"/>
-      <c r="G67" s="4" t="inlineStr"/>
-      <c r="H67" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" s="6" t="inlineStr"/>
-      <c r="J67" s="3" t="n">
+      <c r="F67" s="3" t="inlineStr"/>
+      <c r="G67" s="3" t="inlineStr"/>
+      <c r="H67" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="5" t="inlineStr"/>
+      <c r="J67" s="2" t="n">
         <v>142239</v>
       </c>
-      <c r="K67" s="3" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2742,28 +2730,28 @@
           <t>sugar_sweetened_beverage_intake</t>
         </is>
       </c>
-      <c r="B68" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C68" s="4" t="n">
+      <c r="B68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C68" s="3" t="n">
         <v>1.09</v>
       </c>
-      <c r="D68" s="4" t="n">
+      <c r="D68" s="3" t="n">
         <v>0.93</v>
       </c>
-      <c r="E68" s="4" t="n">
+      <c r="E68" s="3" t="n">
         <v>1.28</v>
       </c>
-      <c r="F68" s="4" t="inlineStr"/>
-      <c r="G68" s="4" t="inlineStr"/>
-      <c r="H68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" s="6" t="inlineStr"/>
-      <c r="J68" s="3" t="n">
+      <c r="F68" s="3" t="inlineStr"/>
+      <c r="G68" s="3" t="inlineStr"/>
+      <c r="H68" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" s="5" t="inlineStr"/>
+      <c r="J68" s="2" t="n">
         <v>21533</v>
       </c>
-      <c r="K68" s="3" t="n">
+      <c r="K68" s="2" t="n">
         <v>291</v>
       </c>
     </row>
@@ -2773,28 +2761,28 @@
           <t>vitamin_b2</t>
         </is>
       </c>
-      <c r="B69" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C69" s="4" t="n">
+      <c r="B69" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C69" s="3" t="n">
         <v>1.11</v>
       </c>
-      <c r="D69" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E69" s="4" t="n">
+      <c r="D69" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" s="3" t="n">
         <v>1.23</v>
       </c>
-      <c r="F69" s="4" t="inlineStr"/>
-      <c r="G69" s="4" t="inlineStr"/>
-      <c r="H69" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" s="6" t="inlineStr"/>
-      <c r="J69" s="3" t="n">
+      <c r="F69" s="3" t="inlineStr"/>
+      <c r="G69" s="3" t="inlineStr"/>
+      <c r="H69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="5" t="inlineStr"/>
+      <c r="J69" s="2" t="n">
         <v>1595</v>
       </c>
-      <c r="K69" s="3" t="n">
+      <c r="K69" s="2" t="n">
         <v>561</v>
       </c>
     </row>
@@ -2804,34 +2792,34 @@
           <t>whole_grain_intake</t>
         </is>
       </c>
-      <c r="B70" s="3" t="n">
+      <c r="B70" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C70" s="4" t="n">
+      <c r="C70" s="3" t="n">
         <v>1.11</v>
       </c>
-      <c r="D70" s="4" t="n">
+      <c r="D70" s="3" t="n">
         <v>0.97</v>
       </c>
-      <c r="E70" s="4" t="n">
+      <c r="E70" s="3" t="n">
         <v>1.26</v>
       </c>
-      <c r="F70" s="4" t="n">
+      <c r="F70" s="3" t="n">
         <v>0.24</v>
       </c>
-      <c r="G70" s="4" t="n">
+      <c r="G70" s="3" t="n">
         <v>5.08</v>
       </c>
-      <c r="H70" s="5" t="n">
+      <c r="H70" s="4" t="n">
         <v>83.3</v>
       </c>
-      <c r="I70" s="6" t="n">
+      <c r="I70" s="5" t="n">
         <v>0.1158775811071888</v>
       </c>
-      <c r="J70" s="3" t="n">
+      <c r="J70" s="2" t="n">
         <v>79458</v>
       </c>
-      <c r="K70" s="3" t="n">
+      <c r="K70" s="2" t="n">
         <v>7209</v>
       </c>
     </row>
@@ -2841,28 +2829,28 @@
           <t>phosphorus</t>
         </is>
       </c>
-      <c r="B71" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C71" s="4" t="n">
+      <c r="B71" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C71" s="3" t="n">
         <v>1.12</v>
       </c>
-      <c r="D71" s="4" t="n">
+      <c r="D71" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="E71" s="4" t="n">
+      <c r="E71" s="3" t="n">
         <v>1.23</v>
       </c>
-      <c r="F71" s="4" t="inlineStr"/>
-      <c r="G71" s="4" t="inlineStr"/>
-      <c r="H71" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" s="6" t="inlineStr"/>
-      <c r="J71" s="3" t="n">
+      <c r="F71" s="3" t="inlineStr"/>
+      <c r="G71" s="3" t="inlineStr"/>
+      <c r="H71" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="5" t="inlineStr"/>
+      <c r="J71" s="2" t="n">
         <v>47885</v>
       </c>
-      <c r="K71" s="3" t="n">
+      <c r="K71" s="2" t="n">
         <v>5861</v>
       </c>
     </row>
@@ -2872,34 +2860,34 @@
           <t>vitamin_b12</t>
         </is>
       </c>
-      <c r="B72" s="3" t="n">
+      <c r="B72" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C72" s="4" t="n">
+      <c r="C72" s="3" t="n">
         <v>1.12</v>
       </c>
-      <c r="D72" s="4" t="n">
+      <c r="D72" s="3" t="n">
         <v>0.97</v>
       </c>
-      <c r="E72" s="4" t="n">
+      <c r="E72" s="3" t="n">
         <v>1.28</v>
       </c>
-      <c r="F72" s="4" t="n">
+      <c r="F72" s="3" t="n">
         <v>0.73</v>
       </c>
-      <c r="G72" s="4" t="n">
+      <c r="G72" s="3" t="n">
         <v>1.71</v>
       </c>
-      <c r="H72" s="5" t="n">
+      <c r="H72" s="4" t="n">
         <v>64.5</v>
       </c>
-      <c r="I72" s="6" t="n">
-        <v>0.0114501930016075</v>
-      </c>
-      <c r="J72" s="3" t="n">
+      <c r="I72" s="5" t="n">
+        <v>0.01145019300160749</v>
+      </c>
+      <c r="J72" s="2" t="n">
         <v>5961</v>
       </c>
-      <c r="K72" s="3" t="n">
+      <c r="K72" s="2" t="n">
         <v>2681</v>
       </c>
     </row>
@@ -2909,34 +2897,34 @@
           <t>processed_meat_intake</t>
         </is>
       </c>
-      <c r="B73" s="3" t="n">
+      <c r="B73" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="C73" s="4" t="n">
+      <c r="C73" s="3" t="n">
         <v>1.13</v>
       </c>
-      <c r="D73" s="4" t="n">
+      <c r="D73" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="E73" s="4" t="n">
+      <c r="E73" s="3" t="n">
         <v>1.21</v>
       </c>
-      <c r="F73" s="4" t="n">
+      <c r="F73" s="3" t="n">
         <v>0.93</v>
       </c>
-      <c r="G73" s="4" t="n">
+      <c r="G73" s="3" t="n">
         <v>1.36</v>
       </c>
-      <c r="H73" s="5" t="n">
+      <c r="H73" s="4" t="n">
         <v>71.2</v>
       </c>
-      <c r="I73" s="6" t="n">
-        <v>0.002637956795546257</v>
-      </c>
-      <c r="J73" s="3" t="n">
+      <c r="I73" s="5" t="n">
+        <v>0.002637956795546261</v>
+      </c>
+      <c r="J73" s="2" t="n">
         <v>1091655</v>
       </c>
-      <c r="K73" s="3" t="n">
+      <c r="K73" s="2" t="n">
         <v>65703</v>
       </c>
     </row>
@@ -2946,34 +2934,34 @@
           <t>vitamin_d</t>
         </is>
       </c>
-      <c r="B74" s="3" t="n">
+      <c r="B74" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="C74" s="4" t="n">
+      <c r="C74" s="3" t="n">
         <v>1.13</v>
       </c>
-      <c r="D74" s="4" t="n">
+      <c r="D74" s="3" t="n">
         <v>1.07</v>
       </c>
-      <c r="E74" s="4" t="n">
+      <c r="E74" s="3" t="n">
         <v>1.19</v>
       </c>
-      <c r="F74" s="4" t="n">
+      <c r="F74" s="3" t="n">
         <v>0.92</v>
       </c>
-      <c r="G74" s="4" t="n">
+      <c r="G74" s="3" t="n">
         <v>1.38</v>
       </c>
-      <c r="H74" s="5" t="n">
+      <c r="H74" s="4" t="n">
         <v>72.8</v>
       </c>
-      <c r="I74" s="6" t="n">
-        <v>0.1064622161384286</v>
-      </c>
-      <c r="J74" s="3" t="n">
+      <c r="I74" s="5" t="n">
+        <v>0.1064622161384289</v>
+      </c>
+      <c r="J74" s="2" t="n">
         <v>551351</v>
       </c>
-      <c r="K74" s="3" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2981,34 +2969,34 @@
           <t>antioxidants</t>
         </is>
       </c>
-      <c r="B75" s="3" t="n">
+      <c r="B75" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C75" s="4" t="n">
+      <c r="C75" s="3" t="n">
         <v>1.15</v>
       </c>
-      <c r="D75" s="4" t="n">
+      <c r="D75" s="3" t="n">
         <v>0.87</v>
       </c>
-      <c r="E75" s="4" t="n">
+      <c r="E75" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="F75" s="4" t="n">
+      <c r="F75" s="3" t="n">
         <v>0.04</v>
       </c>
-      <c r="G75" s="4" t="n">
+      <c r="G75" s="3" t="n">
         <v>33.17</v>
       </c>
-      <c r="H75" s="5" t="n">
+      <c r="H75" s="4" t="n">
         <v>90.3</v>
       </c>
-      <c r="I75" s="6" t="n">
+      <c r="I75" s="5" t="n">
         <v>0.1648989938761477</v>
       </c>
-      <c r="J75" s="3" t="n">
+      <c r="J75" s="2" t="n">
         <v>56601</v>
       </c>
-      <c r="K75" s="3" t="n">
+      <c r="K75" s="2" t="n">
         <v>7271</v>
       </c>
     </row>
@@ -3018,34 +3006,34 @@
           <t>vitamin_a</t>
         </is>
       </c>
-      <c r="B76" s="3" t="n">
+      <c r="B76" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="C76" s="4" t="n">
+      <c r="C76" s="3" t="n">
         <v>1.15</v>
       </c>
-      <c r="D76" s="4" t="n">
+      <c r="D76" s="3" t="n">
         <v>0.93</v>
       </c>
-      <c r="E76" s="4" t="n">
+      <c r="E76" s="3" t="n">
         <v>1.42</v>
       </c>
-      <c r="F76" s="4" t="n">
+      <c r="F76" s="3" t="n">
         <v>0.54</v>
       </c>
-      <c r="G76" s="4" t="n">
+      <c r="G76" s="3" t="n">
         <v>2.43</v>
       </c>
-      <c r="H76" s="5" t="n">
+      <c r="H76" s="4" t="n">
         <v>88.40000000000001</v>
       </c>
-      <c r="I76" s="6" t="n">
-        <v>0.9490649069662661</v>
-      </c>
-      <c r="J76" s="3" t="n">
+      <c r="I76" s="5" t="n">
+        <v>0.9490649069662658</v>
+      </c>
+      <c r="J76" s="2" t="n">
         <v>70012</v>
       </c>
-      <c r="K76" s="3" t="n">
+      <c r="K76" s="2" t="n">
         <v>17837</v>
       </c>
     </row>
@@ -3055,34 +3043,34 @@
           <t>calcium</t>
         </is>
       </c>
-      <c r="B77" s="3" t="n">
+      <c r="B77" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="C77" s="4" t="n">
+      <c r="C77" s="3" t="n">
         <v>1.18</v>
       </c>
-      <c r="D77" s="4" t="n">
+      <c r="D77" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="E77" s="4" t="n">
+      <c r="E77" s="3" t="n">
         <v>1.28</v>
       </c>
-      <c r="F77" s="4" t="n">
+      <c r="F77" s="3" t="n">
         <v>0.86</v>
       </c>
-      <c r="G77" s="4" t="n">
+      <c r="G77" s="3" t="n">
         <v>1.62</v>
       </c>
-      <c r="H77" s="5" t="n">
+      <c r="H77" s="4" t="n">
         <v>80.7</v>
       </c>
-      <c r="I77" s="6" t="n">
-        <v>0.006727675406670044</v>
-      </c>
-      <c r="J77" s="3" t="n">
+      <c r="I77" s="5" t="n">
+        <v>0.006727675406670032</v>
+      </c>
+      <c r="J77" s="2" t="n">
         <v>1049042</v>
       </c>
-      <c r="K77" s="3" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3090,34 +3078,34 @@
           <t>zinc</t>
         </is>
       </c>
-      <c r="B78" s="3" t="n">
+      <c r="B78" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="C78" s="4" t="n">
+      <c r="C78" s="3" t="n">
         <v>1.18</v>
       </c>
-      <c r="D78" s="4" t="n">
+      <c r="D78" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="E78" s="4" t="n">
+      <c r="E78" s="3" t="n">
         <v>1.54</v>
       </c>
-      <c r="F78" s="4" t="n">
+      <c r="F78" s="3" t="n">
         <v>0.46</v>
       </c>
-      <c r="G78" s="4" t="n">
+      <c r="G78" s="3" t="n">
         <v>3.04</v>
       </c>
-      <c r="H78" s="5" t="n">
+      <c r="H78" s="4" t="n">
         <v>79.90000000000001</v>
       </c>
-      <c r="I78" s="6" t="n">
+      <c r="I78" s="5" t="n">
         <v>0.5711938735931297</v>
       </c>
-      <c r="J78" s="3" t="n">
+      <c r="J78" s="2" t="n">
         <v>96718</v>
       </c>
-      <c r="K78" s="3" t="n">
+      <c r="K78" s="2" t="n">
         <v>7983</v>
       </c>
     </row>
@@ -3127,34 +3115,34 @@
           <t>coenzyme_q10</t>
         </is>
       </c>
-      <c r="B79" s="3" t="n">
+      <c r="B79" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C79" s="4" t="n">
+      <c r="C79" s="3" t="n">
         <v>1.19</v>
       </c>
-      <c r="D79" s="4" t="n">
+      <c r="D79" s="3" t="n">
         <v>0.79</v>
       </c>
-      <c r="E79" s="4" t="n">
+      <c r="E79" s="3" t="n">
         <v>1.79</v>
       </c>
-      <c r="F79" s="4" t="n">
+      <c r="F79" s="3" t="n">
         <v>0.01</v>
       </c>
-      <c r="G79" s="4" t="n">
+      <c r="G79" s="3" t="n">
         <v>119.97</v>
       </c>
-      <c r="H79" s="5" t="n">
+      <c r="H79" s="4" t="n">
         <v>69.40000000000001</v>
       </c>
-      <c r="I79" s="6" t="n">
-        <v>0.3692661628018608</v>
-      </c>
-      <c r="J79" s="3" t="n">
+      <c r="I79" s="5" t="n">
+        <v>0.3692661628018609</v>
+      </c>
+      <c r="J79" s="2" t="n">
         <v>36416</v>
       </c>
-      <c r="K79" s="3" t="n">
+      <c r="K79" s="2" t="n">
         <v>2065</v>
       </c>
     </row>
@@ -3164,34 +3152,34 @@
           <t>alcohol</t>
         </is>
       </c>
-      <c r="B80" s="3" t="n">
+      <c r="B80" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="C80" s="4" t="n">
+      <c r="C80" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="D80" s="4" t="n">
+      <c r="D80" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="E80" s="4" t="n">
+      <c r="E80" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="F80" s="4" t="n">
+      <c r="F80" s="3" t="n">
         <v>0.86</v>
       </c>
-      <c r="G80" s="4" t="n">
+      <c r="G80" s="3" t="n">
         <v>1.66</v>
       </c>
-      <c r="H80" s="5" t="n">
+      <c r="H80" s="4" t="n">
         <v>86.59999999999999</v>
       </c>
-      <c r="I80" s="6" t="n">
-        <v>0.005523619063522757</v>
-      </c>
-      <c r="J80" s="3" t="n">
+      <c r="I80" s="5" t="n">
+        <v>0.005523619063522766</v>
+      </c>
+      <c r="J80" s="2" t="n">
         <v>1934957</v>
       </c>
-      <c r="K80" s="3" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3199,34 +3187,34 @@
           <t>dairy</t>
         </is>
       </c>
-      <c r="B81" s="3" t="n">
+      <c r="B81" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="C81" s="4" t="n">
+      <c r="C81" s="3" t="n">
         <v>1.22</v>
       </c>
-      <c r="D81" s="4" t="n">
+      <c r="D81" s="3" t="n">
         <v>1.12</v>
       </c>
-      <c r="E81" s="4" t="n">
+      <c r="E81" s="3" t="n">
         <v>1.34</v>
       </c>
-      <c r="F81" s="4" t="n">
+      <c r="F81" s="3" t="n">
         <v>0.83</v>
       </c>
-      <c r="G81" s="4" t="n">
+      <c r="G81" s="3" t="n">
         <v>1.79</v>
       </c>
-      <c r="H81" s="5" t="n">
+      <c r="H81" s="4" t="n">
         <v>82.7</v>
       </c>
-      <c r="I81" s="6" t="n">
-        <v>0.09941545468620652</v>
-      </c>
-      <c r="J81" s="3" t="n">
+      <c r="I81" s="5" t="n">
+        <v>0.09941545468620654</v>
+      </c>
+      <c r="J81" s="2" t="n">
         <v>739672</v>
       </c>
-      <c r="K81" s="3" t="n">
+      <c r="K81" s="2" t="n">
         <v>33998</v>
       </c>
     </row>
@@ -3236,28 +3224,28 @@
           <t>glutamine</t>
         </is>
       </c>
-      <c r="B82" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C82" s="4" t="n">
+      <c r="B82" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C82" s="3" t="n">
         <v>1.25</v>
       </c>
-      <c r="D82" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E82" s="4" t="n">
+      <c r="D82" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" s="3" t="n">
         <v>1.56</v>
       </c>
-      <c r="F82" s="4" t="inlineStr"/>
-      <c r="G82" s="4" t="inlineStr"/>
-      <c r="H82" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I82" s="6" t="inlineStr"/>
-      <c r="J82" s="3" t="n">
+      <c r="F82" s="3" t="inlineStr"/>
+      <c r="G82" s="3" t="inlineStr"/>
+      <c r="H82" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" s="5" t="inlineStr"/>
+      <c r="J82" s="2" t="n">
         <v>342</v>
       </c>
-      <c r="K82" s="3" t="n">
+      <c r="K82" s="2" t="n">
         <v>171</v>
       </c>
     </row>
@@ -3267,34 +3255,34 @@
           <t>yogurt</t>
         </is>
       </c>
-      <c r="B83" s="3" t="n">
+      <c r="B83" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C83" s="4" t="n">
+      <c r="C83" s="3" t="n">
         <v>1.25</v>
       </c>
-      <c r="D83" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E83" s="4" t="n">
+      <c r="D83" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" s="3" t="n">
         <v>1.56</v>
       </c>
-      <c r="F83" s="4" t="n">
+      <c r="F83" s="3" t="n">
         <v>0.12</v>
       </c>
-      <c r="G83" s="4" t="n">
+      <c r="G83" s="3" t="n">
         <v>12.86</v>
       </c>
-      <c r="H83" s="5" t="n">
+      <c r="H83" s="4" t="n">
         <v>50.3</v>
       </c>
-      <c r="I83" s="6" t="n">
-        <v>0.257220017732754</v>
-      </c>
-      <c r="J83" s="3" t="n">
+      <c r="I83" s="5" t="n">
+        <v>0.2572200177327541</v>
+      </c>
+      <c r="J83" s="2" t="n">
         <v>201324</v>
       </c>
-      <c r="K83" s="3" t="n">
+      <c r="K83" s="2" t="n">
         <v>7680</v>
       </c>
     </row>
@@ -3304,28 +3292,28 @@
           <t>betaine</t>
         </is>
       </c>
-      <c r="B84" s="3" t="n">
+      <c r="B84" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C84" s="4" t="n">
+      <c r="C84" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="D84" s="4" t="n">
+      <c r="D84" s="3" t="n">
         <v>0.73</v>
       </c>
-      <c r="E84" s="4" t="n">
+      <c r="E84" s="3" t="n">
         <v>2.32</v>
       </c>
-      <c r="F84" s="4" t="inlineStr"/>
-      <c r="G84" s="4" t="inlineStr"/>
-      <c r="H84" s="5" t="n">
+      <c r="F84" s="3" t="inlineStr"/>
+      <c r="G84" s="3" t="inlineStr"/>
+      <c r="H84" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="I84" s="6" t="inlineStr"/>
-      <c r="J84" s="3" t="n">
+      <c r="I84" s="5" t="inlineStr"/>
+      <c r="J84" s="2" t="n">
         <v>48588</v>
       </c>
-      <c r="K84" s="3" t="n">
+      <c r="K84" s="2" t="n">
         <v>868</v>
       </c>
     </row>
@@ -3335,34 +3323,34 @@
           <t>alpha_linolenic_acid</t>
         </is>
       </c>
-      <c r="B85" s="3" t="n">
+      <c r="B85" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="C85" s="4" t="n">
+      <c r="C85" s="3" t="n">
         <v>1.31</v>
       </c>
-      <c r="D85" s="4" t="n">
+      <c r="D85" s="3" t="n">
         <v>1.08</v>
       </c>
-      <c r="E85" s="4" t="n">
+      <c r="E85" s="3" t="n">
         <v>1.58</v>
       </c>
-      <c r="F85" s="4" t="n">
+      <c r="F85" s="3" t="n">
         <v>0.75</v>
       </c>
-      <c r="G85" s="4" t="n">
+      <c r="G85" s="3" t="n">
         <v>2.28</v>
       </c>
-      <c r="H85" s="5" t="n">
+      <c r="H85" s="4" t="n">
         <v>85.2</v>
       </c>
-      <c r="I85" s="6" t="n">
-        <v>0.024348344141346</v>
-      </c>
-      <c r="J85" s="3" t="n">
+      <c r="I85" s="5" t="n">
+        <v>0.02434834414134598</v>
+      </c>
+      <c r="J85" s="2" t="n">
         <v>557816</v>
       </c>
-      <c r="K85" s="3" t="n">
+      <c r="K85" s="2" t="n">
         <v>13151</v>
       </c>
     </row>
@@ -3372,28 +3360,28 @@
           <t>creatine</t>
         </is>
       </c>
-      <c r="B86" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C86" s="4" t="n">
+      <c r="B86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C86" s="3" t="n">
         <v>1.31</v>
       </c>
-      <c r="D86" s="4" t="n">
+      <c r="D86" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="E86" s="4" t="n">
+      <c r="E86" s="3" t="n">
         <v>1.63</v>
       </c>
-      <c r="F86" s="4" t="inlineStr"/>
-      <c r="G86" s="4" t="inlineStr"/>
-      <c r="H86" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" s="6" t="inlineStr"/>
-      <c r="J86" s="3" t="n">
+      <c r="F86" s="3" t="inlineStr"/>
+      <c r="G86" s="3" t="inlineStr"/>
+      <c r="H86" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="5" t="inlineStr"/>
+      <c r="J86" s="2" t="n">
         <v>342</v>
       </c>
-      <c r="K86" s="3" t="n">
+      <c r="K86" s="2" t="n">
         <v>171</v>
       </c>
     </row>
@@ -3403,28 +3391,28 @@
           <t>l_valine</t>
         </is>
       </c>
-      <c r="B87" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C87" s="4" t="n">
+      <c r="B87" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C87" s="3" t="n">
         <v>1.31</v>
       </c>
-      <c r="D87" s="4" t="n">
+      <c r="D87" s="3" t="n">
         <v>1.06</v>
       </c>
-      <c r="E87" s="4" t="n">
+      <c r="E87" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="F87" s="4" t="inlineStr"/>
-      <c r="G87" s="4" t="inlineStr"/>
-      <c r="H87" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" s="6" t="inlineStr"/>
-      <c r="J87" s="3" t="n">
+      <c r="F87" s="3" t="inlineStr"/>
+      <c r="G87" s="3" t="inlineStr"/>
+      <c r="H87" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="5" t="inlineStr"/>
+      <c r="J87" s="2" t="n">
         <v>342</v>
       </c>
-      <c r="K87" s="3" t="n">
+      <c r="K87" s="2" t="n">
         <v>171</v>
       </c>
     </row>
@@ -3434,28 +3422,28 @@
           <t>l_tyrosine</t>
         </is>
       </c>
-      <c r="B88" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C88" s="4" t="n">
+      <c r="B88" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C88" s="3" t="n">
         <v>1.33</v>
       </c>
-      <c r="D88" s="4" t="n">
+      <c r="D88" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="E88" s="4" t="n">
+      <c r="E88" s="3" t="n">
         <v>1.66</v>
       </c>
-      <c r="F88" s="4" t="inlineStr"/>
-      <c r="G88" s="4" t="inlineStr"/>
-      <c r="H88" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" s="6" t="inlineStr"/>
-      <c r="J88" s="3" t="n">
+      <c r="F88" s="3" t="inlineStr"/>
+      <c r="G88" s="3" t="inlineStr"/>
+      <c r="H88" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="5" t="inlineStr"/>
+      <c r="J88" s="2" t="n">
         <v>342</v>
       </c>
-      <c r="K88" s="3" t="n">
+      <c r="K88" s="2" t="n">
         <v>171</v>
       </c>
     </row>
@@ -3465,28 +3453,28 @@
           <t>mineral_supplements</t>
         </is>
       </c>
-      <c r="B89" s="3" t="n">
+      <c r="B89" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C89" s="4" t="n">
+      <c r="C89" s="3" t="n">
         <v>1.33</v>
       </c>
-      <c r="D89" s="4" t="n">
+      <c r="D89" s="3" t="n">
         <v>0.79</v>
       </c>
-      <c r="E89" s="4" t="n">
+      <c r="E89" s="3" t="n">
         <v>2.26</v>
       </c>
-      <c r="F89" s="4" t="inlineStr"/>
-      <c r="G89" s="4" t="inlineStr"/>
-      <c r="H89" s="5" t="n">
+      <c r="F89" s="3" t="inlineStr"/>
+      <c r="G89" s="3" t="inlineStr"/>
+      <c r="H89" s="4" t="n">
         <v>80.09999999999999</v>
       </c>
-      <c r="I89" s="6" t="inlineStr"/>
-      <c r="J89" s="3" t="n">
+      <c r="I89" s="5" t="inlineStr"/>
+      <c r="J89" s="2" t="n">
         <v>57251</v>
       </c>
-      <c r="K89" s="3" t="n">
+      <c r="K89" s="2" t="n">
         <v>1958</v>
       </c>
     </row>
@@ -3496,28 +3484,28 @@
           <t>chocolate</t>
         </is>
       </c>
-      <c r="B90" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C90" s="4" t="n">
+      <c r="B90" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C90" s="3" t="n">
         <v>1.35</v>
       </c>
-      <c r="D90" s="4" t="n">
+      <c r="D90" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="E90" s="4" t="n">
+      <c r="E90" s="3" t="n">
         <v>1.64</v>
       </c>
-      <c r="F90" s="4" t="inlineStr"/>
-      <c r="G90" s="4" t="inlineStr"/>
-      <c r="H90" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" s="6" t="inlineStr"/>
-      <c r="J90" s="3" t="n">
+      <c r="F90" s="3" t="inlineStr"/>
+      <c r="G90" s="3" t="inlineStr"/>
+      <c r="H90" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="5" t="inlineStr"/>
+      <c r="J90" s="2" t="n">
         <v>2611</v>
       </c>
-      <c r="K90" s="3" t="n">
+      <c r="K90" s="2" t="n">
         <v>1499</v>
       </c>
     </row>
@@ -3527,28 +3515,28 @@
           <t>western_pattern_diet</t>
         </is>
       </c>
-      <c r="B91" s="3" t="n">
+      <c r="B91" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C91" s="4" t="n">
+      <c r="C91" s="3" t="n">
         <v>1.35</v>
       </c>
-      <c r="D91" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E91" s="4" t="n">
+      <c r="D91" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" s="3" t="n">
         <v>1.82</v>
       </c>
-      <c r="F91" s="4" t="inlineStr"/>
-      <c r="G91" s="4" t="inlineStr"/>
-      <c r="H91" s="5" t="n">
+      <c r="F91" s="3" t="inlineStr"/>
+      <c r="G91" s="3" t="inlineStr"/>
+      <c r="H91" s="4" t="n">
         <v>57.1</v>
       </c>
-      <c r="I91" s="6" t="inlineStr"/>
-      <c r="J91" s="3" t="n">
+      <c r="I91" s="5" t="inlineStr"/>
+      <c r="J91" s="2" t="n">
         <v>44462</v>
       </c>
-      <c r="K91" s="3" t="n">
+      <c r="K91" s="2" t="n">
         <v>1702</v>
       </c>
     </row>
@@ -3558,34 +3546,34 @@
           <t>fermented_foods</t>
         </is>
       </c>
-      <c r="B92" s="3" t="n">
+      <c r="B92" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C92" s="4" t="n">
+      <c r="C92" s="3" t="n">
         <v>1.37</v>
       </c>
-      <c r="D92" s="4" t="n">
+      <c r="D92" s="3" t="n">
         <v>0.76</v>
       </c>
-      <c r="E92" s="4" t="n">
+      <c r="E92" s="3" t="n">
         <v>2.45</v>
       </c>
-      <c r="F92" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G92" s="4" t="n">
+      <c r="F92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" s="3" t="n">
         <v>664.3099999999999</v>
       </c>
-      <c r="H92" s="5" t="n">
+      <c r="H92" s="4" t="n">
         <v>62</v>
       </c>
-      <c r="I92" s="6" t="n">
-        <v>0.1814798483236068</v>
-      </c>
-      <c r="J92" s="3" t="n">
+      <c r="I92" s="5" t="n">
+        <v>0.1814798483236069</v>
+      </c>
+      <c r="J92" s="2" t="n">
         <v>3460</v>
       </c>
-      <c r="K92" s="3" t="n">
+      <c r="K92" s="2" t="n">
         <v>339</v>
       </c>
     </row>
@@ -3595,34 +3583,34 @@
           <t>polyunsaturated_fat_pufa</t>
         </is>
       </c>
-      <c r="B93" s="3" t="n">
+      <c r="B93" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C93" s="4" t="n">
+      <c r="C93" s="3" t="n">
         <v>1.37</v>
       </c>
-      <c r="D93" s="4" t="n">
+      <c r="D93" s="3" t="n">
         <v>0.87</v>
       </c>
-      <c r="E93" s="4" t="n">
+      <c r="E93" s="3" t="n">
         <v>2.17</v>
       </c>
-      <c r="F93" s="4" t="n">
+      <c r="F93" s="3" t="n">
         <v>0.27</v>
       </c>
-      <c r="G93" s="4" t="n">
+      <c r="G93" s="3" t="n">
         <v>7.05</v>
       </c>
-      <c r="H93" s="5" t="n">
+      <c r="H93" s="4" t="n">
         <v>88.7</v>
       </c>
-      <c r="I93" s="6" t="n">
-        <v>0.5930181744853598</v>
-      </c>
-      <c r="J93" s="3" t="n">
+      <c r="I93" s="5" t="n">
+        <v>0.5930181744853599</v>
+      </c>
+      <c r="J93" s="2" t="n">
         <v>64788</v>
       </c>
-      <c r="K93" s="3" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3630,34 +3618,34 @@
           <t>choline</t>
         </is>
       </c>
-      <c r="B94" s="3" t="n">
+      <c r="B94" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C94" s="4" t="n">
+      <c r="C94" s="3" t="n">
         <v>1.38</v>
       </c>
-      <c r="D94" s="4" t="n">
+      <c r="D94" s="3" t="n">
         <v>0.92</v>
       </c>
-      <c r="E94" s="4" t="n">
+      <c r="E94" s="3" t="n">
         <v>2.07</v>
       </c>
-      <c r="F94" s="4" t="n">
+      <c r="F94" s="3" t="n">
         <v>0.01</v>
       </c>
-      <c r="G94" s="4" t="n">
+      <c r="G94" s="3" t="n">
         <v>148.22</v>
       </c>
-      <c r="H94" s="5" t="n">
+      <c r="H94" s="4" t="n">
         <v>77</v>
       </c>
-      <c r="I94" s="6" t="n">
-        <v>0.03888700959299785</v>
-      </c>
-      <c r="J94" s="3" t="n">
+      <c r="I94" s="5" t="n">
+        <v>0.03888700959299778</v>
+      </c>
+      <c r="J94" s="2" t="n">
         <v>8815</v>
       </c>
-      <c r="K94" s="3" t="n">
+      <c r="K94" s="2" t="n">
         <v>1545</v>
       </c>
     </row>
@@ -3667,28 +3655,28 @@
           <t>gamma_linolenic_acid</t>
         </is>
       </c>
-      <c r="B95" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C95" s="4" t="n">
+      <c r="B95" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C95" s="3" t="n">
         <v>1.41</v>
       </c>
-      <c r="D95" s="4" t="n">
+      <c r="D95" s="3" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="E95" s="4" t="n">
+      <c r="E95" s="3" t="n">
         <v>2.12</v>
       </c>
-      <c r="F95" s="4" t="inlineStr"/>
-      <c r="G95" s="4" t="inlineStr"/>
-      <c r="H95" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" s="6" t="inlineStr"/>
-      <c r="J95" s="3" t="n">
+      <c r="F95" s="3" t="inlineStr"/>
+      <c r="G95" s="3" t="inlineStr"/>
+      <c r="H95" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="5" t="inlineStr"/>
+      <c r="J95" s="2" t="n">
         <v>952</v>
       </c>
-      <c r="K95" s="3" t="n">
+      <c r="K95" s="2" t="n">
         <v>476</v>
       </c>
     </row>
@@ -3698,28 +3686,28 @@
           <t>dihomo_gamma_linolenic_acid</t>
         </is>
       </c>
-      <c r="B96" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C96" s="4" t="n">
+      <c r="B96" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C96" s="3" t="n">
         <v>1.54</v>
       </c>
-      <c r="D96" s="4" t="n">
+      <c r="D96" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="E96" s="4" t="n">
+      <c r="E96" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="F96" s="4" t="inlineStr"/>
-      <c r="G96" s="4" t="inlineStr"/>
-      <c r="H96" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" s="6" t="inlineStr"/>
-      <c r="J96" s="3" t="n">
+      <c r="F96" s="3" t="inlineStr"/>
+      <c r="G96" s="3" t="inlineStr"/>
+      <c r="H96" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="5" t="inlineStr"/>
+      <c r="J96" s="2" t="n">
         <v>952</v>
       </c>
-      <c r="K96" s="3" t="n">
+      <c r="K96" s="2" t="n">
         <v>476</v>
       </c>
     </row>
@@ -3729,34 +3717,34 @@
           <t>monounsaturated_fat_mufa</t>
         </is>
       </c>
-      <c r="B97" s="3" t="n">
+      <c r="B97" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="C97" s="4" t="n">
+      <c r="C97" s="3" t="n">
         <v>1.57</v>
       </c>
-      <c r="D97" s="4" t="n">
+      <c r="D97" s="3" t="n">
         <v>1.23</v>
       </c>
-      <c r="E97" s="4" t="n">
+      <c r="E97" s="3" t="n">
         <v>1.99</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="F97" s="3" t="n">
         <v>0.74</v>
       </c>
-      <c r="G97" s="4" t="n">
+      <c r="G97" s="3" t="n">
         <v>3.31</v>
       </c>
-      <c r="H97" s="5" t="n">
+      <c r="H97" s="4" t="n">
         <v>86.40000000000001</v>
       </c>
-      <c r="I97" s="6" t="n">
+      <c r="I97" s="5" t="n">
         <v>0.01420460899877199</v>
       </c>
-      <c r="J97" s="3" t="n">
+      <c r="J97" s="2" t="n">
         <v>56815</v>
       </c>
-      <c r="K97" s="3" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3764,34 +3752,34 @@
           <t>red_meat</t>
         </is>
       </c>
-      <c r="B98" s="3" t="n">
+      <c r="B98" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="C98" s="4" t="n">
+      <c r="C98" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="D98" s="4" t="n">
+      <c r="D98" s="3" t="n">
         <v>1.22</v>
       </c>
-      <c r="E98" s="4" t="n">
+      <c r="E98" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="F98" s="4" t="n">
+      <c r="F98" s="3" t="n">
         <v>0.57</v>
       </c>
-      <c r="G98" s="4" t="n">
+      <c r="G98" s="3" t="n">
         <v>4.51</v>
       </c>
-      <c r="H98" s="5" t="n">
+      <c r="H98" s="4" t="n">
         <v>89.59999999999999</v>
       </c>
-      <c r="I98" s="6" t="n">
-        <v>0.01959176169058001</v>
-      </c>
-      <c r="J98" s="3" t="n">
+      <c r="I98" s="5" t="n">
+        <v>0.01959176169058002</v>
+      </c>
+      <c r="J98" s="2" t="n">
         <v>974550</v>
       </c>
-      <c r="K98" s="3" t="n">
+      <c r="K98" s="2" t="n">
         <v>57630</v>
       </c>
     </row>
@@ -3801,28 +3789,28 @@
           <t>phosphatidylcholine</t>
         </is>
       </c>
-      <c r="B99" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C99" s="4" t="n">
+      <c r="B99" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C99" s="3" t="n">
         <v>1.78</v>
       </c>
-      <c r="D99" s="4" t="n">
+      <c r="D99" s="3" t="n">
         <v>1.06</v>
       </c>
-      <c r="E99" s="4" t="n">
+      <c r="E99" s="3" t="n">
         <v>2.87</v>
       </c>
-      <c r="F99" s="4" t="inlineStr"/>
-      <c r="G99" s="4" t="inlineStr"/>
-      <c r="H99" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I99" s="6" t="inlineStr"/>
-      <c r="J99" s="3" t="n">
+      <c r="F99" s="3" t="inlineStr"/>
+      <c r="G99" s="3" t="inlineStr"/>
+      <c r="H99" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" s="5" t="inlineStr"/>
+      <c r="J99" s="2" t="n">
         <v>310</v>
       </c>
-      <c r="K99" s="3" t="n">
+      <c r="K99" s="2" t="n">
         <v>41</v>
       </c>
     </row>
@@ -3832,28 +3820,28 @@
           <t>glycine</t>
         </is>
       </c>
-      <c r="B100" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C100" s="4" t="n">
+      <c r="B100" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C100" s="3" t="n">
         <v>1.84</v>
       </c>
-      <c r="D100" s="4" t="n">
+      <c r="D100" s="3" t="n">
         <v>1.18</v>
       </c>
-      <c r="E100" s="4" t="n">
+      <c r="E100" s="3" t="n">
         <v>2.72</v>
       </c>
-      <c r="F100" s="4" t="inlineStr"/>
-      <c r="G100" s="4" t="inlineStr"/>
-      <c r="H100" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I100" s="6" t="inlineStr"/>
-      <c r="J100" s="3" t="n">
+      <c r="F100" s="3" t="inlineStr"/>
+      <c r="G100" s="3" t="inlineStr"/>
+      <c r="H100" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" s="5" t="inlineStr"/>
+      <c r="J100" s="2" t="n">
         <v>666</v>
       </c>
-      <c r="K100" s="3" t="n">
+      <c r="K100" s="2" t="n">
         <v>333</v>
       </c>
     </row>
@@ -3863,28 +3851,28 @@
           <t>carnitine</t>
         </is>
       </c>
-      <c r="B101" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C101" s="4" t="n">
+      <c r="B101" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C101" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D101" s="4" t="n">
+      <c r="D101" s="3" t="n">
         <v>1.13</v>
       </c>
-      <c r="E101" s="4" t="n">
+      <c r="E101" s="3" t="n">
         <v>3.56</v>
       </c>
-      <c r="F101" s="4" t="inlineStr"/>
-      <c r="G101" s="4" t="inlineStr"/>
-      <c r="H101" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I101" s="6" t="inlineStr"/>
-      <c r="J101" s="3" t="n">
+      <c r="F101" s="3" t="inlineStr"/>
+      <c r="G101" s="3" t="inlineStr"/>
+      <c r="H101" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" s="5" t="inlineStr"/>
+      <c r="J101" s="2" t="n">
         <v>692</v>
       </c>
-      <c r="K101" s="3" t="n">
+      <c r="K101" s="2" t="n">
         <v>173</v>
       </c>
     </row>
@@ -3894,28 +3882,28 @@
           <t>pickled_vegetables</t>
         </is>
       </c>
-      <c r="B102" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C102" s="4" t="n">
+      <c r="B102" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C102" s="3" t="n">
         <v>4.58</v>
       </c>
-      <c r="D102" s="4" t="n">
+      <c r="D102" s="3" t="n">
         <v>2.97</v>
       </c>
-      <c r="E102" s="4" t="n">
+      <c r="E102" s="3" t="n">
         <v>5.94</v>
       </c>
-      <c r="F102" s="4" t="inlineStr"/>
-      <c r="G102" s="4" t="inlineStr"/>
-      <c r="H102" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I102" s="6" t="inlineStr"/>
-      <c r="J102" s="3" t="n">
+      <c r="F102" s="3" t="inlineStr"/>
+      <c r="G102" s="3" t="inlineStr"/>
+      <c r="H102" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" s="5" t="inlineStr"/>
+      <c r="J102" s="2" t="n">
         <v>404</v>
       </c>
-      <c r="K102" s="3" t="n">
+      <c r="K102" s="2" t="n">
         <v>130</v>
       </c>
     </row>
